--- a/LOUMA phase2.xlsx
+++ b/LOUMA phase2.xlsx
@@ -13,10 +13,12 @@
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
-    <sheet name="Feuil2" sheetId="2" r:id="rId2"/>
-    <sheet name="Feuil3" sheetId="3" r:id="rId3"/>
+    <sheet name="Feuil4" sheetId="4" r:id="rId2"/>
+    <sheet name="Feuil2" sheetId="2" r:id="rId3"/>
+    <sheet name="Feuil3" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Feuil4!$A$2:$E$38</definedName>
     <definedName name="A">Feuil1!$XFD$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
@@ -29,7 +31,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="254" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="321">
   <si>
     <t>DRV</t>
   </si>
@@ -628,13 +630,379 @@
   </si>
   <si>
     <t>Pvt_tdc590060</t>
+  </si>
+  <si>
+    <t>12°30’03.9’’N    15°43’15.4’’W</t>
+  </si>
+  <si>
+    <t>06 GRANDS LOUMA</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Coordonnées GPS </t>
+  </si>
+  <si>
+    <t>JOUR LOUMAS</t>
+  </si>
+  <si>
+    <t>EST</t>
+  </si>
+  <si>
+    <t>NIAKHAR</t>
+  </si>
+  <si>
+    <t>14.473825, -16.402988</t>
+  </si>
+  <si>
+    <t>Lundi</t>
+  </si>
+  <si>
+    <t>18 Km +36 KM</t>
+  </si>
+  <si>
+    <t>NDIENE LAGUENE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">14°30'44.5''N   15°55'28.1''W </t>
+  </si>
+  <si>
+    <t>Mardi</t>
+  </si>
+  <si>
+    <t>65 Km+130 KM</t>
+  </si>
+  <si>
+    <t>SOKONE</t>
+  </si>
+  <si>
+    <t>13.8778012, -16.3728707</t>
+  </si>
+  <si>
+    <t>Mercredi</t>
+  </si>
+  <si>
+    <t>77 Km+154 KM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,99044°N ; 15,11439°O </t>
+  </si>
+  <si>
+    <t>Jeudi</t>
+  </si>
+  <si>
+    <t>165 Km+330 KM</t>
+  </si>
+  <si>
+    <t>DIAMA GADIO</t>
+  </si>
+  <si>
+    <t xml:space="preserve">13,78641°N ; 15,42236°O </t>
+  </si>
+  <si>
+    <t>Samedi</t>
+  </si>
+  <si>
+    <t>147 Km+294 KM</t>
+  </si>
+  <si>
+    <t>COLOBANE MBAR</t>
+  </si>
+  <si>
+    <t>14°3837 N ; 15°4227 O</t>
+  </si>
+  <si>
+    <t>Dimanche</t>
+  </si>
+  <si>
+    <t>86 Km+172 KM</t>
+  </si>
+  <si>
+    <t>NIASSANTE</t>
+  </si>
+  <si>
+    <t>16,0254900, -16,4972290</t>
+  </si>
+  <si>
+    <t> MERCREDI</t>
+  </si>
+  <si>
+    <t> 286 KM * 2 = 572 KM</t>
+  </si>
+  <si>
+    <t>15.477969,-15.866354</t>
+  </si>
+  <si>
+    <t> VENDREDI</t>
+  </si>
+  <si>
+    <t> 85 KM * 2 = 170 KM</t>
+  </si>
+  <si>
+    <t>15.926355,-15.967798</t>
+  </si>
+  <si>
+    <t> 180 KM *2 = 360 KM</t>
+  </si>
+  <si>
+    <t>GASSANE</t>
+  </si>
+  <si>
+    <t>14.8192774;-15.3005457</t>
+  </si>
+  <si>
+    <t> LUNDI</t>
+  </si>
+  <si>
+    <t> 110 KM *2 = 220 KM</t>
+  </si>
+  <si>
+    <t>LABGAR</t>
+  </si>
+  <si>
+    <t>15.8324420;-14.8085243</t>
+  </si>
+  <si>
+    <t> MARDI</t>
+  </si>
+  <si>
+    <t> 70 KM * 2 = 140 KM</t>
+  </si>
+  <si>
+    <t>DOUNDE</t>
+  </si>
+  <si>
+    <t>15.084233283996582000 -12.901286125183105000</t>
+  </si>
+  <si>
+    <t> SAMEDI</t>
+  </si>
+  <si>
+    <t> 310 KM * 2 = 620 KM</t>
+  </si>
+  <si>
+    <t xml:space="preserve">SUD EST </t>
+  </si>
+  <si>
+    <t>PAYAR</t>
+  </si>
+  <si>
+    <t>14°26'10.9"N - 14°29'33.5"W</t>
+  </si>
+  <si>
+    <t> Jeudi</t>
+  </si>
+  <si>
+    <t> 160 KM</t>
+  </si>
+  <si>
+    <t>DAWADI</t>
+  </si>
+  <si>
+    <t>14°07'43.7"N - 13°58'06.4"W</t>
+  </si>
+  <si>
+    <t> Mercredi</t>
+  </si>
+  <si>
+    <t> 83 KM</t>
+  </si>
+  <si>
+    <t>KAHENE</t>
+  </si>
+  <si>
+    <t>13°45'11.7"N - 14°43'44.7"W</t>
+  </si>
+  <si>
+    <t> 114 KM</t>
+  </si>
+  <si>
+    <t>MERETO</t>
+  </si>
+  <si>
+    <t>13°49'08.0"N -14°26'26.7"W</t>
+  </si>
+  <si>
+    <t> Lundi</t>
+  </si>
+  <si>
+    <t>MAKACOLIBANTANG</t>
+  </si>
+  <si>
+    <t>13°40'46.5"N - 14°16'18.5"W</t>
+  </si>
+  <si>
+    <t> 79 km</t>
+  </si>
+  <si>
+    <t>ALTOU FASS / MALEM NIANI</t>
+  </si>
+  <si>
+    <t>13°56'21.4"N - 14°17'53.7"W</t>
+  </si>
+  <si>
+    <t> Mardi</t>
+  </si>
+  <si>
+    <t> 72 KM</t>
+  </si>
+  <si>
+    <t>SUD</t>
+  </si>
+  <si>
+    <t xml:space="preserve">DIANA </t>
+  </si>
+  <si>
+    <t> 140 (70)</t>
+  </si>
+  <si>
+    <t>DJIBANAR</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 12.543907,-15810159</t>
+  </si>
+  <si>
+    <t> 116 (58)</t>
+  </si>
+  <si>
+    <t>DIAOBE</t>
+  </si>
+  <si>
+    <t>12.915496 ,-14.150688</t>
+  </si>
+  <si>
+    <t>  84   (42)</t>
+  </si>
+  <si>
+    <t>BAYENGOU</t>
+  </si>
+  <si>
+    <t>13.207572, -15.145006</t>
+  </si>
+  <si>
+    <t> 124 (62)</t>
+  </si>
+  <si>
+    <t>MANDA DOUANE</t>
+  </si>
+  <si>
+    <t>13.3339667,-13.8229600</t>
+  </si>
+  <si>
+    <t>   64  (32)</t>
+  </si>
+  <si>
+    <t>SARE YOBA</t>
+  </si>
+  <si>
+    <t>12.76538, -15.105637</t>
+  </si>
+  <si>
+    <t>   62  (31)</t>
+  </si>
+  <si>
+    <t>MBAR</t>
+  </si>
+  <si>
+    <t>14°32'16.8''N   15°45'29.9''W</t>
+  </si>
+  <si>
+    <t>54KM</t>
+  </si>
+  <si>
+    <t>SAM YABAL</t>
+  </si>
+  <si>
+    <t>15.207794,-15.899213</t>
+  </si>
+  <si>
+    <t>30 KM</t>
+  </si>
+  <si>
+    <t>BABA GARAGE</t>
+  </si>
+  <si>
+    <t>14°56'24''N 16°29'23''W</t>
+  </si>
+  <si>
+    <t>129 KM</t>
+  </si>
+  <si>
+    <t>DIOURBEL</t>
+  </si>
+  <si>
+    <t>14.650291,-16.234170</t>
+  </si>
+  <si>
+    <t>185 KM</t>
+  </si>
+  <si>
+    <t>SADIO</t>
+  </si>
+  <si>
+    <t>14.819680-15.546418</t>
+  </si>
+  <si>
+    <t>144KM</t>
+  </si>
+  <si>
+    <t>Sandiara</t>
+  </si>
+  <si>
+    <t>14.434948-16.793366</t>
+  </si>
+  <si>
+    <t>89 KM</t>
+  </si>
+  <si>
+    <t>DR2</t>
+  </si>
+  <si>
+    <t>Marché Jeudi</t>
+  </si>
+  <si>
+    <t>14.7828199-17.376013</t>
+  </si>
+  <si>
+    <t>Marché Tivaoune Peulh</t>
+  </si>
+  <si>
+    <t>14°48'35" nord, 17°16'44" ouest</t>
+  </si>
+  <si>
+    <t>Marché Niagal Toubabou Dialaw</t>
+  </si>
+  <si>
+    <t>14°60'55"N - 17°15'14"O</t>
+  </si>
+  <si>
+    <t>Marché rond point daral Rufisque</t>
+  </si>
+  <si>
+    <t>14.71554 -17.270929</t>
+  </si>
+  <si>
+    <t>Marché Mame Thierno Bargny</t>
+  </si>
+  <si>
+    <t>14°41' 22.79" N -17°14'0.60" O</t>
+  </si>
+  <si>
+    <t>Marché Keur Mbaye Fall</t>
+  </si>
+  <si>
+    <t>14°44'23"N - 17°19'14"W</t>
+  </si>
+  <si>
+    <t>Liste des 06 grands Loumas par DR avec coordonnées géographiques PHASE 1</t>
+  </si>
+  <si>
+    <t>Liste des 06 grands Loumas par DR avec coordonnées géographiques PHASE 2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="27">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -790,8 +1158,42 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="12"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color rgb="FF000000"/>
+      <name val="Aptos Narrow"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -983,8 +1385,20 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFBE2D5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="28">
+  <borders count="43">
     <border>
       <left/>
       <right/>
@@ -1335,6 +1749,215 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="medium">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top/>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="medium">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="medium">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="medium">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1380,7 +2003,7 @@
     <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1408,7 +2031,6 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1445,6 +2067,89 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="36" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1768,7 +2473,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="21.81640625" customWidth="1"/>
     <col min="3" max="3" width="24.7265625" customWidth="1"/>
@@ -1776,7 +2481,7 @@
     <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1793,8 +2498,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="27" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="26" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1810,8 +2515,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="28"/>
+    <row r="3" spans="1:7">
+      <c r="A3" s="27"/>
       <c r="B3" s="3" t="s">
         <v>20</v>
       </c>
@@ -1825,8 +2530,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="28"/>
+    <row r="4" spans="1:7">
+      <c r="A4" s="27"/>
       <c r="B4" s="3" t="s">
         <v>21</v>
       </c>
@@ -1840,8 +2545,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="28"/>
+    <row r="5" spans="1:7">
+      <c r="A5" s="27"/>
       <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
@@ -1855,8 +2560,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="28"/>
+    <row r="6" spans="1:7">
+      <c r="A6" s="27"/>
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
@@ -1870,8 +2575,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="28"/>
+    <row r="7" spans="1:7">
+      <c r="A7" s="27"/>
       <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
@@ -1885,8 +2590,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="28" t="s">
+    <row r="8" spans="1:7">
+      <c r="A8" s="27" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1902,8 +2607,8 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="28"/>
+    <row r="9" spans="1:7">
+      <c r="A9" s="27"/>
       <c r="B9" s="3" t="s">
         <v>113</v>
       </c>
@@ -1918,8 +2623,8 @@
       </c>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="28"/>
+    <row r="10" spans="1:7">
+      <c r="A10" s="27"/>
       <c r="B10" s="3" t="s">
         <v>114</v>
       </c>
@@ -1934,8 +2639,8 @@
       </c>
       <c r="G10" s="3"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="28"/>
+    <row r="11" spans="1:7">
+      <c r="A11" s="27"/>
       <c r="B11" s="3" t="s">
         <v>115</v>
       </c>
@@ -1950,8 +2655,8 @@
       </c>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="28"/>
+    <row r="12" spans="1:7">
+      <c r="A12" s="27"/>
       <c r="B12" s="3" t="s">
         <v>116</v>
       </c>
@@ -1966,8 +2671,8 @@
       </c>
       <c r="G12" s="3"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="28"/>
+    <row r="13" spans="1:7">
+      <c r="A13" s="27"/>
       <c r="B13" s="4" t="s">
         <v>117</v>
       </c>
@@ -1982,8 +2687,8 @@
       </c>
       <c r="G13" s="3"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="28" t="s">
+    <row r="14" spans="1:7">
+      <c r="A14" s="27" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -2000,8 +2705,8 @@
       </c>
       <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="28"/>
+    <row r="15" spans="1:7">
+      <c r="A15" s="27"/>
       <c r="B15" s="3" t="s">
         <v>64</v>
       </c>
@@ -2015,8 +2720,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="28"/>
+    <row r="16" spans="1:7">
+      <c r="A16" s="27"/>
       <c r="B16" s="3" t="s">
         <v>65</v>
       </c>
@@ -2030,8 +2735,8 @@
         <v>157</v>
       </c>
     </row>
-    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="28"/>
+    <row r="17" spans="1:5">
+      <c r="A17" s="27"/>
       <c r="B17" s="3" t="s">
         <v>66</v>
       </c>
@@ -2045,8 +2750,8 @@
         <v>155</v>
       </c>
     </row>
-    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="28"/>
+    <row r="18" spans="1:5">
+      <c r="A18" s="27"/>
       <c r="B18" s="3" t="s">
         <v>67</v>
       </c>
@@ -2060,8 +2765,8 @@
         <v>158</v>
       </c>
     </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="28"/>
+    <row r="19" spans="1:5">
+      <c r="A19" s="27"/>
       <c r="B19" s="4" t="s">
         <v>68</v>
       </c>
@@ -2075,8 +2780,8 @@
         <v>159</v>
       </c>
     </row>
-    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="28" t="s">
+    <row r="20" spans="1:5">
+      <c r="A20" s="27" t="s">
         <v>8</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -2092,8 +2797,8 @@
         <v>148</v>
       </c>
     </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="28"/>
+    <row r="21" spans="1:5">
+      <c r="A21" s="27"/>
       <c r="B21" s="3" t="s">
         <v>149</v>
       </c>
@@ -2107,12 +2812,14 @@
         <v>151</v>
       </c>
     </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="28"/>
+    <row r="22" spans="1:5">
+      <c r="A22" s="27"/>
       <c r="B22" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C22" s="23"/>
+      <c r="C22" s="36" t="s">
+        <v>199</v>
+      </c>
       <c r="D22" s="3" t="s">
         <v>13</v>
       </c>
@@ -2120,8 +2827,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="28"/>
+    <row r="23" spans="1:5">
+      <c r="A23" s="27"/>
       <c r="B23" s="3" t="s">
         <v>153</v>
       </c>
@@ -2135,8 +2842,8 @@
         <v>160</v>
       </c>
     </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="28"/>
+    <row r="24" spans="1:5">
+      <c r="A24" s="27"/>
       <c r="B24" s="3" t="s">
         <v>161</v>
       </c>
@@ -2150,8 +2857,8 @@
         <v>163</v>
       </c>
     </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="28"/>
+    <row r="25" spans="1:5">
+      <c r="A25" s="27"/>
       <c r="B25" s="4" t="s">
         <v>164</v>
       </c>
@@ -2165,8 +2872,8 @@
         <v>166</v>
       </c>
     </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="29" t="s">
+    <row r="26" spans="1:5">
+      <c r="A26" s="28" t="s">
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -2182,8 +2889,8 @@
         <v>173</v>
       </c>
     </row>
-    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="30"/>
+    <row r="27" spans="1:5">
+      <c r="A27" s="29"/>
       <c r="B27" s="3" t="s">
         <v>168</v>
       </c>
@@ -2197,8 +2904,8 @@
         <v>174</v>
       </c>
     </row>
-    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="30"/>
+    <row r="28" spans="1:5">
+      <c r="A28" s="29"/>
       <c r="B28" s="3" t="s">
         <v>169</v>
       </c>
@@ -2212,8 +2919,8 @@
         <v>175</v>
       </c>
     </row>
-    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="30"/>
+    <row r="29" spans="1:5">
+      <c r="A29" s="29"/>
       <c r="B29" s="3" t="s">
         <v>170</v>
       </c>
@@ -2227,8 +2934,8 @@
         <v>176</v>
       </c>
     </row>
-    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="30"/>
+    <row r="30" spans="1:5">
+      <c r="A30" s="29"/>
       <c r="B30" s="3" t="s">
         <v>171</v>
       </c>
@@ -2242,8 +2949,8 @@
         <v>177</v>
       </c>
     </row>
-    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="27"/>
+    <row r="31" spans="1:5">
+      <c r="A31" s="26"/>
       <c r="B31" s="4" t="s">
         <v>172</v>
       </c>
@@ -2272,8 +2979,1033 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L38"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <cols>
+    <col min="1" max="1" width="13.90625" customWidth="1"/>
+    <col min="2" max="2" width="12.453125" customWidth="1"/>
+    <col min="3" max="3" width="12.6328125" customWidth="1"/>
+    <col min="4" max="4" width="11.6328125" customWidth="1"/>
+    <col min="5" max="5" width="12.6328125" customWidth="1"/>
+    <col min="9" max="9" width="17.36328125" customWidth="1"/>
+    <col min="10" max="10" width="17.08984375" customWidth="1"/>
+    <col min="11" max="11" width="13.7265625" customWidth="1"/>
+    <col min="12" max="12" width="14.7265625" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" ht="16" thickBot="1">
+      <c r="A1" s="52" t="s">
+        <v>319</v>
+      </c>
+      <c r="B1" s="53"/>
+      <c r="C1" s="53"/>
+      <c r="D1" s="53"/>
+      <c r="E1" s="54"/>
+      <c r="H1" s="62" t="s">
+        <v>320</v>
+      </c>
+      <c r="I1" s="63"/>
+      <c r="J1" s="63"/>
+      <c r="K1" s="63"/>
+      <c r="L1" s="64"/>
+    </row>
+    <row r="2" spans="1:12" ht="31" customHeight="1" thickBot="1">
+      <c r="A2" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" s="38" t="s">
+        <v>201</v>
+      </c>
+      <c r="D2" s="38" t="s">
+        <v>202</v>
+      </c>
+      <c r="E2" s="39" t="s">
+        <v>4</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>0</v>
+      </c>
+      <c r="I2" s="38" t="s">
+        <v>200</v>
+      </c>
+      <c r="J2" s="38" t="s">
+        <v>2</v>
+      </c>
+      <c r="K2" s="38" t="s">
+        <v>3</v>
+      </c>
+      <c r="L2" s="39" t="s">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" ht="24">
+      <c r="A3" s="55" t="s">
+        <v>203</v>
+      </c>
+      <c r="B3" s="40" t="s">
+        <v>204</v>
+      </c>
+      <c r="C3" s="40" t="s">
+        <v>205</v>
+      </c>
+      <c r="D3" s="40" t="s">
+        <v>206</v>
+      </c>
+      <c r="E3" s="41" t="s">
+        <v>207</v>
+      </c>
+      <c r="H3" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="I3" s="61" t="s">
+        <v>19</v>
+      </c>
+      <c r="J3" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" ht="24">
+      <c r="A4" s="56"/>
+      <c r="B4" s="42" t="s">
+        <v>208</v>
+      </c>
+      <c r="C4" s="42" t="s">
+        <v>209</v>
+      </c>
+      <c r="D4" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="E4" s="43" t="s">
+        <v>211</v>
+      </c>
+      <c r="H4" s="27"/>
+      <c r="I4" s="61" t="s">
+        <v>20</v>
+      </c>
+      <c r="J4" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="K4" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L4" s="3" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="24">
+      <c r="A5" s="56"/>
+      <c r="B5" s="42" t="s">
+        <v>212</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>214</v>
+      </c>
+      <c r="E5" s="43" t="s">
+        <v>215</v>
+      </c>
+      <c r="H5" s="27"/>
+      <c r="I5" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" s="3" t="s">
+        <v>27</v>
+      </c>
+      <c r="K5" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="L5" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="24">
+      <c r="A6" s="56"/>
+      <c r="B6" s="42" t="s">
+        <v>19</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>216</v>
+      </c>
+      <c r="D6" s="42" t="s">
+        <v>217</v>
+      </c>
+      <c r="E6" s="43" t="s">
+        <v>218</v>
+      </c>
+      <c r="H6" s="27"/>
+      <c r="I6" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="J6" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="K6" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L6" s="3" t="s">
+        <v>30</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="24">
+      <c r="A7" s="56"/>
+      <c r="B7" s="42" t="s">
+        <v>219</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>220</v>
+      </c>
+      <c r="D7" s="42" t="s">
+        <v>221</v>
+      </c>
+      <c r="E7" s="43" t="s">
+        <v>222</v>
+      </c>
+      <c r="H7" s="27"/>
+      <c r="I7" s="3" t="s">
+        <v>10</v>
+      </c>
+      <c r="J7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="K7" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L7" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" ht="24.5" thickBot="1">
+      <c r="A8" s="57"/>
+      <c r="B8" s="44" t="s">
+        <v>223</v>
+      </c>
+      <c r="C8" s="44" t="s">
+        <v>224</v>
+      </c>
+      <c r="D8" s="44" t="s">
+        <v>225</v>
+      </c>
+      <c r="E8" s="45" t="s">
+        <v>226</v>
+      </c>
+      <c r="H8" s="27"/>
+      <c r="I8" s="4" t="s">
+        <v>12</v>
+      </c>
+      <c r="J8" s="4" t="s">
+        <v>23</v>
+      </c>
+      <c r="K8" s="4" t="s">
+        <v>13</v>
+      </c>
+      <c r="L8" s="4" t="s">
+        <v>29</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" ht="24">
+      <c r="A9" s="58" t="s">
+        <v>6</v>
+      </c>
+      <c r="B9" s="46" t="s">
+        <v>227</v>
+      </c>
+      <c r="C9" s="46" t="s">
+        <v>228</v>
+      </c>
+      <c r="D9" s="47" t="s">
+        <v>229</v>
+      </c>
+      <c r="E9" s="41" t="s">
+        <v>230</v>
+      </c>
+      <c r="H9" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="I9" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>118</v>
+      </c>
+      <c r="K9" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="10" spans="1:12" ht="24">
+      <c r="A10" s="59"/>
+      <c r="B10" s="48" t="s">
+        <v>116</v>
+      </c>
+      <c r="C10" s="48" t="s">
+        <v>231</v>
+      </c>
+      <c r="D10" s="49" t="s">
+        <v>232</v>
+      </c>
+      <c r="E10" s="43" t="s">
+        <v>233</v>
+      </c>
+      <c r="H10" s="27"/>
+      <c r="I10" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="J10" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="K10" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L10" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="11" spans="1:12" ht="24">
+      <c r="A11" s="59"/>
+      <c r="B11" s="48" t="s">
+        <v>117</v>
+      </c>
+      <c r="C11" s="48" t="s">
+        <v>234</v>
+      </c>
+      <c r="D11" s="49" t="s">
+        <v>221</v>
+      </c>
+      <c r="E11" s="43" t="s">
+        <v>235</v>
+      </c>
+      <c r="H11" s="27"/>
+      <c r="I11" s="3" t="s">
+        <v>114</v>
+      </c>
+      <c r="J11" s="3" t="s">
+        <v>120</v>
+      </c>
+      <c r="K11" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L11" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="12" spans="1:12" ht="24">
+      <c r="A12" s="59"/>
+      <c r="B12" s="48" t="s">
+        <v>236</v>
+      </c>
+      <c r="C12" s="48" t="s">
+        <v>237</v>
+      </c>
+      <c r="D12" s="49" t="s">
+        <v>238</v>
+      </c>
+      <c r="E12" s="43" t="s">
+        <v>239</v>
+      </c>
+      <c r="H12" s="27"/>
+      <c r="I12" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="K12" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L12" s="3" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12" ht="24">
+      <c r="A13" s="59"/>
+      <c r="B13" s="48" t="s">
+        <v>240</v>
+      </c>
+      <c r="C13" s="48" t="s">
+        <v>241</v>
+      </c>
+      <c r="D13" s="49" t="s">
+        <v>242</v>
+      </c>
+      <c r="E13" s="43" t="s">
+        <v>243</v>
+      </c>
+      <c r="H13" s="27"/>
+      <c r="I13" s="61" t="s">
+        <v>116</v>
+      </c>
+      <c r="J13" s="3" t="s">
+        <v>122</v>
+      </c>
+      <c r="K13" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L13" s="3" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12" ht="47.5" thickBot="1">
+      <c r="A14" s="60"/>
+      <c r="B14" s="50" t="s">
+        <v>244</v>
+      </c>
+      <c r="C14" s="51" t="s">
+        <v>245</v>
+      </c>
+      <c r="D14" s="50" t="s">
+        <v>246</v>
+      </c>
+      <c r="E14" s="45" t="s">
+        <v>247</v>
+      </c>
+      <c r="H14" s="27"/>
+      <c r="I14" s="61" t="s">
+        <v>117</v>
+      </c>
+      <c r="J14" s="4" t="s">
+        <v>123</v>
+      </c>
+      <c r="K14" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L14" s="3" t="s">
+        <v>129</v>
+      </c>
+    </row>
+    <row r="15" spans="1:12" ht="24">
+      <c r="A15" s="58" t="s">
+        <v>248</v>
+      </c>
+      <c r="B15" s="46" t="s">
+        <v>249</v>
+      </c>
+      <c r="C15" s="46" t="s">
+        <v>250</v>
+      </c>
+      <c r="D15" s="47" t="s">
+        <v>251</v>
+      </c>
+      <c r="E15" s="41" t="s">
+        <v>252</v>
+      </c>
+      <c r="H15" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="I15" s="2" t="s">
+        <v>63</v>
+      </c>
+      <c r="J15" s="2" t="s">
+        <v>70</v>
+      </c>
+      <c r="K15" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="16" spans="1:12" ht="24">
+      <c r="A16" s="59"/>
+      <c r="B16" s="48" t="s">
+        <v>253</v>
+      </c>
+      <c r="C16" s="48" t="s">
+        <v>254</v>
+      </c>
+      <c r="D16" s="49" t="s">
+        <v>255</v>
+      </c>
+      <c r="E16" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="H16" s="27"/>
+      <c r="I16" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="J16" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="K16" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L16" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="17" spans="1:12" ht="24">
+      <c r="A17" s="59"/>
+      <c r="B17" s="48" t="s">
+        <v>257</v>
+      </c>
+      <c r="C17" s="48" t="s">
+        <v>258</v>
+      </c>
+      <c r="D17" s="49" t="s">
+        <v>255</v>
+      </c>
+      <c r="E17" s="43" t="s">
+        <v>259</v>
+      </c>
+      <c r="H17" s="27"/>
+      <c r="I17" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="J17" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="K17" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L17" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12" ht="24">
+      <c r="A18" s="59"/>
+      <c r="B18" s="48" t="s">
+        <v>260</v>
+      </c>
+      <c r="C18" s="48" t="s">
+        <v>261</v>
+      </c>
+      <c r="D18" s="49" t="s">
+        <v>262</v>
+      </c>
+      <c r="E18" s="43" t="s">
+        <v>256</v>
+      </c>
+      <c r="H18" s="27"/>
+      <c r="I18" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="J18" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="K18" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L18" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12" ht="24">
+      <c r="A19" s="59"/>
+      <c r="B19" s="48" t="s">
+        <v>263</v>
+      </c>
+      <c r="C19" s="48" t="s">
+        <v>264</v>
+      </c>
+      <c r="D19" s="49" t="s">
+        <v>251</v>
+      </c>
+      <c r="E19" s="43" t="s">
+        <v>265</v>
+      </c>
+      <c r="H19" s="27"/>
+      <c r="I19" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="J19" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="K19" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="L19" s="3" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="20" spans="1:12" ht="24.5" thickBot="1">
+      <c r="A20" s="60"/>
+      <c r="B20" s="51" t="s">
+        <v>266</v>
+      </c>
+      <c r="C20" s="51" t="s">
+        <v>267</v>
+      </c>
+      <c r="D20" s="50" t="s">
+        <v>268</v>
+      </c>
+      <c r="E20" s="45" t="s">
+        <v>269</v>
+      </c>
+      <c r="H20" s="27"/>
+      <c r="I20" s="4" t="s">
+        <v>68</v>
+      </c>
+      <c r="J20" s="4" t="s">
+        <v>75</v>
+      </c>
+      <c r="K20" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="L20" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="21" spans="1:12" ht="23">
+      <c r="A21" s="58" t="s">
+        <v>270</v>
+      </c>
+      <c r="B21" s="47" t="s">
+        <v>271</v>
+      </c>
+      <c r="C21" s="47" t="s">
+        <v>147</v>
+      </c>
+      <c r="D21" s="47" t="s">
+        <v>16</v>
+      </c>
+      <c r="E21" s="41" t="s">
+        <v>272</v>
+      </c>
+      <c r="H21" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="I21" s="61" t="s">
+        <v>146</v>
+      </c>
+      <c r="J21" s="2" t="s">
+        <v>147</v>
+      </c>
+      <c r="K21" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="L21" s="2" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="22" spans="1:12" ht="23">
+      <c r="A22" s="59"/>
+      <c r="B22" s="49" t="s">
+        <v>273</v>
+      </c>
+      <c r="C22" s="49" t="s">
+        <v>274</v>
+      </c>
+      <c r="D22" s="49" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="43" t="s">
+        <v>275</v>
+      </c>
+      <c r="H22" s="27"/>
+      <c r="I22" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="J22" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="K22" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="L22" s="3" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="23" spans="1:12" ht="23">
+      <c r="A23" s="59"/>
+      <c r="B23" s="49" t="s">
+        <v>276</v>
+      </c>
+      <c r="C23" s="49" t="s">
+        <v>277</v>
+      </c>
+      <c r="D23" s="49" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="43" t="s">
+        <v>278</v>
+      </c>
+      <c r="H23" s="27"/>
+      <c r="I23" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="J23" s="36" t="s">
+        <v>199</v>
+      </c>
+      <c r="K23" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L23" s="3" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="24" spans="1:12" ht="23">
+      <c r="A24" s="59"/>
+      <c r="B24" s="49" t="s">
+        <v>279</v>
+      </c>
+      <c r="C24" s="49" t="s">
+        <v>280</v>
+      </c>
+      <c r="D24" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="E24" s="43" t="s">
+        <v>281</v>
+      </c>
+      <c r="H24" s="27"/>
+      <c r="I24" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="J24" s="3" t="s">
+        <v>154</v>
+      </c>
+      <c r="K24" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L24" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="25" spans="1:12" ht="23">
+      <c r="A25" s="59"/>
+      <c r="B25" s="49" t="s">
+        <v>282</v>
+      </c>
+      <c r="C25" s="49" t="s">
+        <v>283</v>
+      </c>
+      <c r="D25" s="49" t="s">
+        <v>13</v>
+      </c>
+      <c r="E25" s="43" t="s">
+        <v>284</v>
+      </c>
+      <c r="H25" s="27"/>
+      <c r="I25" s="3" t="s">
+        <v>161</v>
+      </c>
+      <c r="J25" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="K25" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L25" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="26" spans="1:12" ht="23.5" thickBot="1">
+      <c r="A26" s="60"/>
+      <c r="B26" s="50" t="s">
+        <v>285</v>
+      </c>
+      <c r="C26" s="50" t="s">
+        <v>286</v>
+      </c>
+      <c r="D26" s="50" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="45" t="s">
+        <v>287</v>
+      </c>
+      <c r="H26" s="27"/>
+      <c r="I26" s="4" t="s">
+        <v>164</v>
+      </c>
+      <c r="J26" s="4" t="s">
+        <v>165</v>
+      </c>
+      <c r="K26" s="4" t="s">
+        <v>69</v>
+      </c>
+      <c r="L26" s="4" t="s">
+        <v>166</v>
+      </c>
+    </row>
+    <row r="27" spans="1:12" ht="24">
+      <c r="A27" s="58" t="s">
+        <v>9</v>
+      </c>
+      <c r="B27" s="47" t="s">
+        <v>288</v>
+      </c>
+      <c r="C27" s="46" t="s">
+        <v>289</v>
+      </c>
+      <c r="D27" s="46" t="s">
+        <v>11</v>
+      </c>
+      <c r="E27" s="41" t="s">
+        <v>290</v>
+      </c>
+      <c r="H27" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="I27" s="2" t="s">
+        <v>167</v>
+      </c>
+      <c r="J27" s="2" t="s">
+        <v>88</v>
+      </c>
+      <c r="K27" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="28" spans="1:12" ht="24">
+      <c r="A28" s="59"/>
+      <c r="B28" s="49" t="s">
+        <v>291</v>
+      </c>
+      <c r="C28" s="48" t="s">
+        <v>292</v>
+      </c>
+      <c r="D28" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E28" s="43" t="s">
+        <v>293</v>
+      </c>
+      <c r="H28" s="29"/>
+      <c r="I28" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="J28" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="K28" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="L28" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="29" spans="1:12" ht="24">
+      <c r="A29" s="59"/>
+      <c r="B29" s="49" t="s">
+        <v>294</v>
+      </c>
+      <c r="C29" s="48" t="s">
+        <v>295</v>
+      </c>
+      <c r="D29" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="E29" s="43" t="s">
+        <v>296</v>
+      </c>
+      <c r="H29" s="29"/>
+      <c r="I29" s="3" t="s">
+        <v>169</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="K29" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="L29" s="3" t="s">
+        <v>175</v>
+      </c>
+    </row>
+    <row r="30" spans="1:12" ht="24">
+      <c r="A30" s="59"/>
+      <c r="B30" s="49" t="s">
+        <v>297</v>
+      </c>
+      <c r="C30" s="48" t="s">
+        <v>298</v>
+      </c>
+      <c r="D30" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="43" t="s">
+        <v>299</v>
+      </c>
+      <c r="H30" s="29"/>
+      <c r="I30" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="J30" s="3" t="s">
+        <v>91</v>
+      </c>
+      <c r="K30" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="L30" s="3" t="s">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="31" spans="1:12" ht="24">
+      <c r="A31" s="59"/>
+      <c r="B31" s="49" t="s">
+        <v>300</v>
+      </c>
+      <c r="C31" s="48" t="s">
+        <v>301</v>
+      </c>
+      <c r="D31" s="48" t="s">
+        <v>69</v>
+      </c>
+      <c r="E31" s="43" t="s">
+        <v>302</v>
+      </c>
+      <c r="H31" s="29"/>
+      <c r="I31" s="3" t="s">
+        <v>171</v>
+      </c>
+      <c r="J31" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="K31" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="L31" s="3" t="s">
+        <v>177</v>
+      </c>
+    </row>
+    <row r="32" spans="1:12" ht="24.5" thickBot="1">
+      <c r="A32" s="60"/>
+      <c r="B32" s="50" t="s">
+        <v>303</v>
+      </c>
+      <c r="C32" s="51" t="s">
+        <v>304</v>
+      </c>
+      <c r="D32" s="51" t="s">
+        <v>16</v>
+      </c>
+      <c r="E32" s="45" t="s">
+        <v>305</v>
+      </c>
+      <c r="H32" s="26"/>
+      <c r="I32" s="4" t="s">
+        <v>172</v>
+      </c>
+      <c r="J32" s="4" t="s">
+        <v>93</v>
+      </c>
+      <c r="K32" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="L32" s="4" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="33" spans="1:5" ht="24">
+      <c r="A33" s="58" t="s">
+        <v>306</v>
+      </c>
+      <c r="B33" s="46" t="s">
+        <v>307</v>
+      </c>
+      <c r="C33" s="46" t="s">
+        <v>308</v>
+      </c>
+      <c r="D33" s="46" t="s">
+        <v>15</v>
+      </c>
+      <c r="E33" s="41"/>
+    </row>
+    <row r="34" spans="1:5" ht="24">
+      <c r="A34" s="59"/>
+      <c r="B34" s="48" t="s">
+        <v>309</v>
+      </c>
+      <c r="C34" s="48" t="s">
+        <v>310</v>
+      </c>
+      <c r="D34" s="48" t="s">
+        <v>13</v>
+      </c>
+      <c r="E34" s="43"/>
+    </row>
+    <row r="35" spans="1:5" ht="35.5">
+      <c r="A35" s="59"/>
+      <c r="B35" s="48" t="s">
+        <v>311</v>
+      </c>
+      <c r="C35" s="48" t="s">
+        <v>312</v>
+      </c>
+      <c r="D35" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E35" s="43"/>
+    </row>
+    <row r="36" spans="1:5" ht="35.5">
+      <c r="A36" s="59"/>
+      <c r="B36" s="48" t="s">
+        <v>313</v>
+      </c>
+      <c r="C36" s="48" t="s">
+        <v>314</v>
+      </c>
+      <c r="D36" s="48" t="s">
+        <v>16</v>
+      </c>
+      <c r="E36" s="43"/>
+    </row>
+    <row r="37" spans="1:5" ht="24">
+      <c r="A37" s="59"/>
+      <c r="B37" s="48" t="s">
+        <v>315</v>
+      </c>
+      <c r="C37" s="48" t="s">
+        <v>316</v>
+      </c>
+      <c r="D37" s="48" t="s">
+        <v>14</v>
+      </c>
+      <c r="E37" s="43"/>
+    </row>
+    <row r="38" spans="1:5" ht="24.5" thickBot="1">
+      <c r="A38" s="60"/>
+      <c r="B38" s="51" t="s">
+        <v>317</v>
+      </c>
+      <c r="C38" s="51" t="s">
+        <v>318</v>
+      </c>
+      <c r="D38" s="51" t="s">
+        <v>69</v>
+      </c>
+      <c r="E38" s="45"/>
+    </row>
+  </sheetData>
+  <autoFilter ref="A2:E38"/>
+  <mergeCells count="13">
+    <mergeCell ref="H1:L1"/>
+    <mergeCell ref="A33:A38"/>
+    <mergeCell ref="H3:H8"/>
+    <mergeCell ref="H9:H14"/>
+    <mergeCell ref="H15:H20"/>
+    <mergeCell ref="H21:H26"/>
+    <mergeCell ref="H27:H32"/>
+    <mergeCell ref="A1:E1"/>
+    <mergeCell ref="A3:A8"/>
+    <mergeCell ref="A9:A14"/>
+    <mergeCell ref="A15:A20"/>
+    <mergeCell ref="A21:A26"/>
+    <mergeCell ref="A27:A32"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="2" max="2" width="23.26953125" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
@@ -2281,7 +4013,7 @@
     <col min="5" max="5" width="20.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:7">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2304,11 +4036,11 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A2" s="29" t="s">
+    <row r="2" spans="1:7">
+      <c r="A2" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="31" t="s">
+      <c r="B2" s="30" t="s">
         <v>48</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2327,9 +4059,9 @@
         <v>777410048</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A3" s="30"/>
-      <c r="B3" s="32"/>
+    <row r="3" spans="1:7">
+      <c r="A3" s="29"/>
+      <c r="B3" s="31"/>
       <c r="C3" s="3" t="s">
         <v>52</v>
       </c>
@@ -2346,9 +4078,9 @@
         <v>787656877</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A4" s="30"/>
-      <c r="B4" s="32"/>
+    <row r="4" spans="1:7">
+      <c r="A4" s="29"/>
+      <c r="B4" s="31"/>
       <c r="C4" s="3" t="s">
         <v>53</v>
       </c>
@@ -2365,9 +4097,9 @@
         <v>776019823</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A5" s="27"/>
-      <c r="B5" s="33"/>
+    <row r="5" spans="1:7">
+      <c r="A5" s="26"/>
+      <c r="B5" s="32"/>
       <c r="C5" s="3" t="s">
         <v>55</v>
       </c>
@@ -2384,11 +4116,11 @@
         <v>782981141</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A6" s="28" t="s">
+    <row r="6" spans="1:7">
+      <c r="A6" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="31" t="s">
+      <c r="B6" s="30" t="s">
         <v>131</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -2407,9 +4139,9 @@
         <v>788255458</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A7" s="28"/>
-      <c r="B7" s="32" t="s">
+    <row r="7" spans="1:7">
+      <c r="A7" s="27"/>
+      <c r="B7" s="31" t="s">
         <v>131</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -2428,9 +4160,9 @@
         <v>789166919</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A8" s="28"/>
-      <c r="B8" s="32"/>
+    <row r="8" spans="1:7">
+      <c r="A8" s="27"/>
+      <c r="B8" s="31"/>
       <c r="C8" s="3" t="s">
         <v>138</v>
       </c>
@@ -2447,9 +4179,9 @@
         <v>789151415</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A9" s="28"/>
-      <c r="B9" s="33"/>
+    <row r="9" spans="1:7">
+      <c r="A9" s="27"/>
+      <c r="B9" s="32"/>
       <c r="C9" s="3" t="s">
         <v>196</v>
       </c>
@@ -2459,18 +4191,18 @@
       <c r="E9" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="F9" s="26">
+      <c r="F9" s="25">
         <v>778113461</v>
       </c>
       <c r="G9" s="3">
         <v>789166945</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A10" s="28" t="s">
+    <row r="10" spans="1:7">
+      <c r="A10" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="31" t="s">
+      <c r="B10" s="30" t="s">
         <v>132</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -2489,9 +4221,9 @@
         <v>781180310</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A11" s="28"/>
-      <c r="B11" s="32"/>
+    <row r="11" spans="1:7">
+      <c r="A11" s="27"/>
+      <c r="B11" s="31"/>
       <c r="C11" s="3" t="s">
         <v>79</v>
       </c>
@@ -2508,9 +4240,9 @@
         <v>781180552</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A12" s="28"/>
-      <c r="B12" s="32"/>
+    <row r="12" spans="1:7">
+      <c r="A12" s="27"/>
+      <c r="B12" s="31"/>
       <c r="C12" s="3" t="s">
         <v>81</v>
       </c>
@@ -2527,9 +4259,9 @@
         <v>787080588</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A13" s="28"/>
-      <c r="B13" s="33"/>
+    <row r="13" spans="1:7">
+      <c r="A13" s="27"/>
+      <c r="B13" s="32"/>
       <c r="C13" s="3" t="s">
         <v>82</v>
       </c>
@@ -2546,11 +4278,11 @@
         <v>789150567</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A14" s="28" t="s">
+    <row r="14" spans="1:7">
+      <c r="A14" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="31" t="s">
+      <c r="B14" s="30" t="s">
         <v>179</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -2569,9 +4301,9 @@
         <v>771545210</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A15" s="28"/>
-      <c r="B15" s="32" t="s">
+    <row r="15" spans="1:7">
+      <c r="A15" s="27"/>
+      <c r="B15" s="31" t="s">
         <v>131</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -2590,9 +4322,9 @@
         <v>773958904</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A16" s="28"/>
-      <c r="B16" s="32"/>
+    <row r="16" spans="1:7">
+      <c r="A16" s="27"/>
+      <c r="B16" s="31"/>
       <c r="C16" s="3" t="s">
         <v>183</v>
       </c>
@@ -2609,9 +4341,9 @@
         <v>776950987</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="28"/>
-      <c r="B17" s="33"/>
+    <row r="17" spans="1:7">
+      <c r="A17" s="27"/>
+      <c r="B17" s="32"/>
       <c r="C17" s="4" t="s">
         <v>185</v>
       </c>
@@ -2628,11 +4360,11 @@
         <v>781825193</v>
       </c>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="30" t="s">
+    <row r="18" spans="1:7">
+      <c r="A18" s="29" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="31" t="s">
+      <c r="B18" s="30" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -2651,9 +4383,9 @@
         <v>786180521</v>
       </c>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="30"/>
-      <c r="B19" s="32"/>
+    <row r="19" spans="1:7">
+      <c r="A19" s="29"/>
+      <c r="B19" s="31"/>
       <c r="C19" s="3" t="s">
         <v>95</v>
       </c>
@@ -2670,9 +4402,9 @@
         <v>786183517</v>
       </c>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="30"/>
-      <c r="B20" s="32"/>
+    <row r="20" spans="1:7">
+      <c r="A20" s="29"/>
+      <c r="B20" s="31"/>
       <c r="C20" s="3" t="s">
         <v>99</v>
       </c>
@@ -2689,9 +4421,9 @@
         <v>772118585</v>
       </c>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="27"/>
-      <c r="B21" s="33"/>
+    <row r="21" spans="1:7">
+      <c r="A21" s="26"/>
+      <c r="B21" s="32"/>
       <c r="C21" s="4" t="s">
         <v>102</v>
       </c>
@@ -2710,33 +4442,33 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="B10:B13"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
   <cols>
     <col min="3" max="3" width="22.36328125" customWidth="1"/>
     <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:4" ht="15" thickBot="1"/>
+    <row r="2" spans="1:4" ht="15" thickBot="1">
       <c r="A2" s="13"/>
       <c r="B2" s="7"/>
       <c r="C2" s="11"/>
@@ -2744,8 +4476,8 @@
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="34" t="s">
+    <row r="3" spans="1:4">
+      <c r="A3" s="33" t="s">
         <v>62</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -2758,8 +4490,8 @@
         <v>776382705</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="34"/>
+    <row r="4" spans="1:4">
+      <c r="A4" s="33"/>
       <c r="B4" s="8" t="s">
         <v>33</v>
       </c>
@@ -2770,8 +4502,8 @@
         <v>777401785</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="34"/>
+    <row r="5" spans="1:4">
+      <c r="A5" s="33"/>
       <c r="B5" s="8" t="s">
         <v>35</v>
       </c>
@@ -2782,8 +4514,8 @@
         <v>772579898</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="35"/>
+    <row r="6" spans="1:4" ht="15" thickBot="1">
+      <c r="A6" s="34"/>
       <c r="B6" s="9" t="s">
         <v>37</v>
       </c>
@@ -2794,8 +4526,8 @@
         <v>781816827</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="34" t="s">
+    <row r="7" spans="1:4">
+      <c r="A7" s="33" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="16" t="s">
@@ -2808,8 +4540,8 @@
         <v>778196895</v>
       </c>
     </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="34"/>
+    <row r="8" spans="1:4">
+      <c r="A8" s="33"/>
       <c r="B8" s="8" t="s">
         <v>33</v>
       </c>
@@ -2820,8 +4552,8 @@
         <v>776372229</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="34"/>
+    <row r="9" spans="1:4">
+      <c r="A9" s="33"/>
       <c r="B9" s="8" t="s">
         <v>35</v>
       </c>
@@ -2832,8 +4564,8 @@
         <v>776665352</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="34"/>
+    <row r="10" spans="1:4" ht="15" thickBot="1">
+      <c r="A10" s="33"/>
       <c r="B10" s="9" t="s">
         <v>37</v>
       </c>
@@ -2844,8 +4576,8 @@
         <v>783441820</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="36" t="s">
+    <row r="11" spans="1:4">
+      <c r="A11" s="35" t="s">
         <v>94</v>
       </c>
       <c r="B11" s="16" t="s">
@@ -2856,8 +4588,8 @@
       </c>
       <c r="D11" s="21"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="34"/>
+    <row r="12" spans="1:4">
+      <c r="A12" s="33"/>
       <c r="B12" s="8" t="s">
         <v>33</v>
       </c>
@@ -2866,8 +4598,8 @@
       </c>
       <c r="D12" s="22"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="34"/>
+    <row r="13" spans="1:4">
+      <c r="A13" s="33"/>
       <c r="B13" s="8" t="s">
         <v>35</v>
       </c>
@@ -2876,8 +4608,8 @@
       </c>
       <c r="D13" s="22"/>
     </row>
-    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="35"/>
+    <row r="14" spans="1:4" ht="15" thickBot="1">
+      <c r="A14" s="34"/>
       <c r="B14" s="9" t="s">
         <v>37</v>
       </c>
@@ -2888,8 +4620,8 @@
         <v>782402937</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="34" t="s">
+    <row r="15" spans="1:4">
+      <c r="A15" s="33" t="s">
         <v>133</v>
       </c>
       <c r="B15" s="16" t="s">
@@ -2902,8 +4634,8 @@
         <v>775699621</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="34"/>
+    <row r="16" spans="1:4">
+      <c r="A16" s="33"/>
       <c r="B16" s="8" t="s">
         <v>33</v>
       </c>
@@ -2914,8 +4646,8 @@
         <v>776440917</v>
       </c>
     </row>
-    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="34"/>
+    <row r="17" spans="1:4">
+      <c r="A17" s="33"/>
       <c r="B17" s="8" t="s">
         <v>35</v>
       </c>
@@ -2926,8 +4658,8 @@
         <v>781287163</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="35"/>
+    <row r="18" spans="1:4" ht="15" thickBot="1">
+      <c r="A18" s="34"/>
       <c r="B18" s="9" t="s">
         <v>37</v>
       </c>
@@ -2938,8 +4670,8 @@
         <v>782352114</v>
       </c>
     </row>
-    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="34" t="s">
+    <row r="19" spans="1:4">
+      <c r="A19" s="33" t="s">
         <v>191</v>
       </c>
       <c r="B19" s="16" t="s">
@@ -2952,8 +4684,8 @@
         <v>773335050</v>
       </c>
     </row>
-    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="34"/>
+    <row r="20" spans="1:4">
+      <c r="A20" s="33"/>
       <c r="B20" s="8" t="s">
         <v>33</v>
       </c>
@@ -2964,8 +4696,8 @@
         <v>776441287</v>
       </c>
     </row>
-    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="34"/>
+    <row r="21" spans="1:4">
+      <c r="A21" s="33"/>
       <c r="B21" s="8" t="s">
         <v>35</v>
       </c>
@@ -2976,15 +4708,15 @@
         <v>775451818</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="35"/>
+    <row r="22" spans="1:4" ht="15" thickBot="1">
+      <c r="A22" s="34"/>
       <c r="B22" s="9" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="24" t="s">
+      <c r="C22" s="23" t="s">
         <v>195</v>
       </c>
-      <c r="D22" s="25">
+      <c r="D22" s="24">
         <v>775277993</v>
       </c>
     </row>

--- a/LOUMA phase2.xlsx
+++ b/LOUMA phase2.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -2038,36 +2038,6 @@
       <alignment horizontal="right" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="22" fillId="36" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -2114,6 +2084,37 @@
     <xf numFmtId="0" fontId="25" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1" readingOrder="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="35" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
     <xf numFmtId="0" fontId="21" fillId="35" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" wrapText="1" readingOrder="1"/>
     </xf>
@@ -2132,24 +2133,23 @@
     <xf numFmtId="0" fontId="23" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="19" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2207,6 +2207,53 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>0</xdr:colOff>
+      <xdr:row>3</xdr:row>
+      <xdr:rowOff>0</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>6</xdr:col>
+      <xdr:colOff>304800</xdr:colOff>
+      <xdr:row>4</xdr:row>
+      <xdr:rowOff>120650</xdr:rowOff>
+    </xdr:to>
+    <xdr:sp macro="" textlink="">
+      <xdr:nvSpPr>
+        <xdr:cNvPr id="1025" name="AutoShape 1" descr="https://webmail.orange-sonatel.com/owa/service.svc/s/GetFileAttachment?id=AAMkADFjZGRkNWUxLTc1NWQtNDhlYi1hNDM4LWVmMGRmMDYyNjUwYQBGAAAAAABACGCI8ciuTo586mafeePBBwDFPHv2ZPxmQryVITZN6edRAAAAAAEMAADFPHv2ZPxmQryVITZN6edRAAAcHhIkAAABEgAQAFQUxJJ0nYhHjai8I9zMl0c%3D&amp;X-OWA-CANARY=f71HJgRWFEi6_l5xXszcptBDLJLHyd0IqQAjUsstfuKX0H6wcdhcApLAUl0JAcyugHBL4xuyOnA.&amp;isImagePreview=True"/>
+        <xdr:cNvSpPr>
+          <a:spLocks noChangeAspect="1" noChangeArrowheads="1"/>
+        </xdr:cNvSpPr>
+      </xdr:nvSpPr>
+      <xdr:spPr bwMode="auto">
+        <a:xfrm>
+          <a:off x="7194550" y="552450"/>
+          <a:ext cx="304800" cy="304800"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+        <a:noFill/>
+        <a:extLst>
+          <a:ext uri="{909E8E84-426E-40DD-AFC4-6F175D3DCCD1}">
+            <a14:hiddenFill xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main">
+              <a:solidFill>
+                <a:srgbClr val="FFFFFF"/>
+              </a:solidFill>
+            </a14:hiddenFill>
+          </a:ext>
+        </a:extLst>
+      </xdr:spPr>
+    </xdr:sp>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -2499,7 +2546,7 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="43" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -2516,7 +2563,7 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="27"/>
+      <c r="A3" s="44"/>
       <c r="B3" s="3" t="s">
         <v>20</v>
       </c>
@@ -2531,7 +2578,7 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="27"/>
+      <c r="A4" s="44"/>
       <c r="B4" s="3" t="s">
         <v>21</v>
       </c>
@@ -2546,7 +2593,7 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="27"/>
+      <c r="A5" s="44"/>
       <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
@@ -2561,7 +2608,7 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="27"/>
+      <c r="A6" s="44"/>
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
@@ -2576,7 +2623,7 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="27"/>
+      <c r="A7" s="44"/>
       <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
@@ -2591,7 +2638,7 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="44" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -2608,7 +2655,7 @@
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="27"/>
+      <c r="A9" s="44"/>
       <c r="B9" s="3" t="s">
         <v>113</v>
       </c>
@@ -2624,7 +2671,7 @@
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="27"/>
+      <c r="A10" s="44"/>
       <c r="B10" s="3" t="s">
         <v>114</v>
       </c>
@@ -2640,7 +2687,7 @@
       <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="27"/>
+      <c r="A11" s="44"/>
       <c r="B11" s="3" t="s">
         <v>115</v>
       </c>
@@ -2656,7 +2703,7 @@
       <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="27"/>
+      <c r="A12" s="44"/>
       <c r="B12" s="3" t="s">
         <v>116</v>
       </c>
@@ -2672,7 +2719,7 @@
       <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="27"/>
+      <c r="A13" s="44"/>
       <c r="B13" s="4" t="s">
         <v>117</v>
       </c>
@@ -2688,7 +2735,7 @@
       <c r="G13" s="3"/>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="44" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -2706,7 +2753,7 @@
       <c r="G14" s="3"/>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="27"/>
+      <c r="A15" s="44"/>
       <c r="B15" s="3" t="s">
         <v>64</v>
       </c>
@@ -2721,7 +2768,7 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="27"/>
+      <c r="A16" s="44"/>
       <c r="B16" s="3" t="s">
         <v>65</v>
       </c>
@@ -2736,7 +2783,7 @@
       </c>
     </row>
     <row r="17" spans="1:5">
-      <c r="A17" s="27"/>
+      <c r="A17" s="44"/>
       <c r="B17" s="3" t="s">
         <v>66</v>
       </c>
@@ -2751,7 +2798,7 @@
       </c>
     </row>
     <row r="18" spans="1:5">
-      <c r="A18" s="27"/>
+      <c r="A18" s="44"/>
       <c r="B18" s="3" t="s">
         <v>67</v>
       </c>
@@ -2766,7 +2813,7 @@
       </c>
     </row>
     <row r="19" spans="1:5">
-      <c r="A19" s="27"/>
+      <c r="A19" s="44"/>
       <c r="B19" s="4" t="s">
         <v>68</v>
       </c>
@@ -2781,7 +2828,7 @@
       </c>
     </row>
     <row r="20" spans="1:5">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="44" t="s">
         <v>8</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -2798,7 +2845,7 @@
       </c>
     </row>
     <row r="21" spans="1:5">
-      <c r="A21" s="27"/>
+      <c r="A21" s="44"/>
       <c r="B21" s="3" t="s">
         <v>149</v>
       </c>
@@ -2813,11 +2860,11 @@
       </c>
     </row>
     <row r="22" spans="1:5">
-      <c r="A22" s="27"/>
+      <c r="A22" s="44"/>
       <c r="B22" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C22" s="36" t="s">
+      <c r="C22" s="26" t="s">
         <v>199</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -2828,7 +2875,7 @@
       </c>
     </row>
     <row r="23" spans="1:5">
-      <c r="A23" s="27"/>
+      <c r="A23" s="44"/>
       <c r="B23" s="3" t="s">
         <v>153</v>
       </c>
@@ -2843,7 +2890,7 @@
       </c>
     </row>
     <row r="24" spans="1:5">
-      <c r="A24" s="27"/>
+      <c r="A24" s="44"/>
       <c r="B24" s="3" t="s">
         <v>161</v>
       </c>
@@ -2858,7 +2905,7 @@
       </c>
     </row>
     <row r="25" spans="1:5">
-      <c r="A25" s="27"/>
+      <c r="A25" s="44"/>
       <c r="B25" s="4" t="s">
         <v>164</v>
       </c>
@@ -2873,7 +2920,7 @@
       </c>
     </row>
     <row r="26" spans="1:5">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="45" t="s">
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -2890,7 +2937,7 @@
       </c>
     </row>
     <row r="27" spans="1:5">
-      <c r="A27" s="29"/>
+      <c r="A27" s="46"/>
       <c r="B27" s="3" t="s">
         <v>168</v>
       </c>
@@ -2905,7 +2952,7 @@
       </c>
     </row>
     <row r="28" spans="1:5">
-      <c r="A28" s="29"/>
+      <c r="A28" s="46"/>
       <c r="B28" s="3" t="s">
         <v>169</v>
       </c>
@@ -2920,7 +2967,7 @@
       </c>
     </row>
     <row r="29" spans="1:5">
-      <c r="A29" s="29"/>
+      <c r="A29" s="46"/>
       <c r="B29" s="3" t="s">
         <v>170</v>
       </c>
@@ -2935,7 +2982,7 @@
       </c>
     </row>
     <row r="30" spans="1:5">
-      <c r="A30" s="29"/>
+      <c r="A30" s="46"/>
       <c r="B30" s="3" t="s">
         <v>171</v>
       </c>
@@ -2950,7 +2997,7 @@
       </c>
     </row>
     <row r="31" spans="1:5">
-      <c r="A31" s="26"/>
+      <c r="A31" s="43"/>
       <c r="B31" s="4" t="s">
         <v>172</v>
       </c>
@@ -2974,6 +3021,7 @@
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
@@ -2994,73 +3042,73 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:12" ht="16" thickBot="1">
-      <c r="A1" s="52" t="s">
+      <c r="A1" s="53" t="s">
         <v>319</v>
       </c>
-      <c r="B1" s="53"/>
-      <c r="C1" s="53"/>
-      <c r="D1" s="53"/>
-      <c r="E1" s="54"/>
-      <c r="H1" s="62" t="s">
+      <c r="B1" s="54"/>
+      <c r="C1" s="54"/>
+      <c r="D1" s="54"/>
+      <c r="E1" s="55"/>
+      <c r="H1" s="47" t="s">
         <v>320</v>
       </c>
-      <c r="I1" s="63"/>
-      <c r="J1" s="63"/>
-      <c r="K1" s="63"/>
-      <c r="L1" s="64"/>
+      <c r="I1" s="48"/>
+      <c r="J1" s="48"/>
+      <c r="K1" s="48"/>
+      <c r="L1" s="49"/>
     </row>
     <row r="2" spans="1:12" ht="31" customHeight="1" thickBot="1">
-      <c r="A2" s="37" t="s">
+      <c r="A2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="B2" s="38" t="s">
+      <c r="B2" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="C2" s="38" t="s">
+      <c r="C2" s="28" t="s">
         <v>201</v>
       </c>
-      <c r="D2" s="38" t="s">
+      <c r="D2" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="E2" s="39" t="s">
+      <c r="E2" s="29" t="s">
         <v>4</v>
       </c>
-      <c r="H2" s="37" t="s">
+      <c r="H2" s="27" t="s">
         <v>0</v>
       </c>
-      <c r="I2" s="38" t="s">
+      <c r="I2" s="28" t="s">
         <v>200</v>
       </c>
-      <c r="J2" s="38" t="s">
+      <c r="J2" s="28" t="s">
         <v>2</v>
       </c>
-      <c r="K2" s="38" t="s">
+      <c r="K2" s="28" t="s">
         <v>3</v>
       </c>
-      <c r="L2" s="39" t="s">
+      <c r="L2" s="29" t="s">
         <v>4</v>
       </c>
     </row>
     <row r="3" spans="1:12" ht="24">
-      <c r="A3" s="55" t="s">
+      <c r="A3" s="56" t="s">
         <v>203</v>
       </c>
-      <c r="B3" s="40" t="s">
+      <c r="B3" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="C3" s="40" t="s">
+      <c r="C3" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="D3" s="40" t="s">
+      <c r="D3" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="E3" s="41" t="s">
+      <c r="E3" s="31" t="s">
         <v>207</v>
       </c>
-      <c r="H3" s="26" t="s">
+      <c r="H3" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="I3" s="61" t="s">
+      <c r="I3" s="42" t="s">
         <v>19</v>
       </c>
       <c r="J3" s="2" t="s">
@@ -3074,21 +3122,21 @@
       </c>
     </row>
     <row r="4" spans="1:12" ht="24">
-      <c r="A4" s="56"/>
-      <c r="B4" s="42" t="s">
+      <c r="A4" s="57"/>
+      <c r="B4" s="32" t="s">
         <v>208</v>
       </c>
-      <c r="C4" s="42" t="s">
+      <c r="C4" s="32" t="s">
         <v>209</v>
       </c>
-      <c r="D4" s="42" t="s">
+      <c r="D4" s="32" t="s">
         <v>210</v>
       </c>
-      <c r="E4" s="43" t="s">
+      <c r="E4" s="33" t="s">
         <v>211</v>
       </c>
-      <c r="H4" s="27"/>
-      <c r="I4" s="61" t="s">
+      <c r="H4" s="44"/>
+      <c r="I4" s="42" t="s">
         <v>20</v>
       </c>
       <c r="J4" s="3" t="s">
@@ -3102,20 +3150,20 @@
       </c>
     </row>
     <row r="5" spans="1:12" ht="24">
-      <c r="A5" s="56"/>
-      <c r="B5" s="42" t="s">
+      <c r="A5" s="57"/>
+      <c r="B5" s="32" t="s">
         <v>212</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="32" t="s">
         <v>213</v>
       </c>
-      <c r="D5" s="42" t="s">
+      <c r="D5" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="E5" s="43" t="s">
+      <c r="E5" s="33" t="s">
         <v>215</v>
       </c>
-      <c r="H5" s="27"/>
+      <c r="H5" s="44"/>
       <c r="I5" s="3" t="s">
         <v>21</v>
       </c>
@@ -3130,20 +3178,20 @@
       </c>
     </row>
     <row r="6" spans="1:12" ht="24">
-      <c r="A6" s="56"/>
-      <c r="B6" s="42" t="s">
+      <c r="A6" s="57"/>
+      <c r="B6" s="32" t="s">
         <v>19</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="32" t="s">
         <v>216</v>
       </c>
-      <c r="D6" s="42" t="s">
+      <c r="D6" s="32" t="s">
         <v>217</v>
       </c>
-      <c r="E6" s="43" t="s">
+      <c r="E6" s="33" t="s">
         <v>218</v>
       </c>
-      <c r="H6" s="27"/>
+      <c r="H6" s="44"/>
       <c r="I6" s="3" t="s">
         <v>18</v>
       </c>
@@ -3158,20 +3206,20 @@
       </c>
     </row>
     <row r="7" spans="1:12" ht="24">
-      <c r="A7" s="56"/>
-      <c r="B7" s="42" t="s">
+      <c r="A7" s="57"/>
+      <c r="B7" s="32" t="s">
         <v>219</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="32" t="s">
         <v>220</v>
       </c>
-      <c r="D7" s="42" t="s">
+      <c r="D7" s="32" t="s">
         <v>221</v>
       </c>
-      <c r="E7" s="43" t="s">
+      <c r="E7" s="33" t="s">
         <v>222</v>
       </c>
-      <c r="H7" s="27"/>
+      <c r="H7" s="44"/>
       <c r="I7" s="3" t="s">
         <v>10</v>
       </c>
@@ -3186,20 +3234,20 @@
       </c>
     </row>
     <row r="8" spans="1:12" ht="24.5" thickBot="1">
-      <c r="A8" s="57"/>
-      <c r="B8" s="44" t="s">
+      <c r="A8" s="58"/>
+      <c r="B8" s="34" t="s">
         <v>223</v>
       </c>
-      <c r="C8" s="44" t="s">
+      <c r="C8" s="34" t="s">
         <v>224</v>
       </c>
-      <c r="D8" s="44" t="s">
+      <c r="D8" s="34" t="s">
         <v>225</v>
       </c>
-      <c r="E8" s="45" t="s">
+      <c r="E8" s="35" t="s">
         <v>226</v>
       </c>
-      <c r="H8" s="27"/>
+      <c r="H8" s="44"/>
       <c r="I8" s="4" t="s">
         <v>12</v>
       </c>
@@ -3214,22 +3262,22 @@
       </c>
     </row>
     <row r="9" spans="1:12" ht="24">
-      <c r="A9" s="58" t="s">
+      <c r="A9" s="50" t="s">
         <v>6</v>
       </c>
-      <c r="B9" s="46" t="s">
+      <c r="B9" s="36" t="s">
         <v>227</v>
       </c>
-      <c r="C9" s="46" t="s">
+      <c r="C9" s="36" t="s">
         <v>228</v>
       </c>
-      <c r="D9" s="47" t="s">
+      <c r="D9" s="37" t="s">
         <v>229</v>
       </c>
-      <c r="E9" s="41" t="s">
+      <c r="E9" s="31" t="s">
         <v>230</v>
       </c>
-      <c r="H9" s="27" t="s">
+      <c r="H9" s="44" t="s">
         <v>6</v>
       </c>
       <c r="I9" s="2" t="s">
@@ -3246,20 +3294,20 @@
       </c>
     </row>
     <row r="10" spans="1:12" ht="24">
-      <c r="A10" s="59"/>
-      <c r="B10" s="48" t="s">
+      <c r="A10" s="51"/>
+      <c r="B10" s="38" t="s">
         <v>116</v>
       </c>
-      <c r="C10" s="48" t="s">
+      <c r="C10" s="38" t="s">
         <v>231</v>
       </c>
-      <c r="D10" s="49" t="s">
+      <c r="D10" s="39" t="s">
         <v>232</v>
       </c>
-      <c r="E10" s="43" t="s">
+      <c r="E10" s="33" t="s">
         <v>233</v>
       </c>
-      <c r="H10" s="27"/>
+      <c r="H10" s="44"/>
       <c r="I10" s="3" t="s">
         <v>113</v>
       </c>
@@ -3274,20 +3322,20 @@
       </c>
     </row>
     <row r="11" spans="1:12" ht="24">
-      <c r="A11" s="59"/>
-      <c r="B11" s="48" t="s">
+      <c r="A11" s="51"/>
+      <c r="B11" s="38" t="s">
         <v>117</v>
       </c>
-      <c r="C11" s="48" t="s">
+      <c r="C11" s="38" t="s">
         <v>234</v>
       </c>
-      <c r="D11" s="49" t="s">
+      <c r="D11" s="39" t="s">
         <v>221</v>
       </c>
-      <c r="E11" s="43" t="s">
+      <c r="E11" s="33" t="s">
         <v>235</v>
       </c>
-      <c r="H11" s="27"/>
+      <c r="H11" s="44"/>
       <c r="I11" s="3" t="s">
         <v>114</v>
       </c>
@@ -3302,20 +3350,20 @@
       </c>
     </row>
     <row r="12" spans="1:12" ht="24">
-      <c r="A12" s="59"/>
-      <c r="B12" s="48" t="s">
+      <c r="A12" s="51"/>
+      <c r="B12" s="38" t="s">
         <v>236</v>
       </c>
-      <c r="C12" s="48" t="s">
+      <c r="C12" s="38" t="s">
         <v>237</v>
       </c>
-      <c r="D12" s="49" t="s">
+      <c r="D12" s="39" t="s">
         <v>238</v>
       </c>
-      <c r="E12" s="43" t="s">
+      <c r="E12" s="33" t="s">
         <v>239</v>
       </c>
-      <c r="H12" s="27"/>
+      <c r="H12" s="44"/>
       <c r="I12" s="3" t="s">
         <v>115</v>
       </c>
@@ -3330,21 +3378,21 @@
       </c>
     </row>
     <row r="13" spans="1:12" ht="24">
-      <c r="A13" s="59"/>
-      <c r="B13" s="48" t="s">
+      <c r="A13" s="51"/>
+      <c r="B13" s="38" t="s">
         <v>240</v>
       </c>
-      <c r="C13" s="48" t="s">
+      <c r="C13" s="38" t="s">
         <v>241</v>
       </c>
-      <c r="D13" s="49" t="s">
+      <c r="D13" s="39" t="s">
         <v>242</v>
       </c>
-      <c r="E13" s="43" t="s">
+      <c r="E13" s="33" t="s">
         <v>243</v>
       </c>
-      <c r="H13" s="27"/>
-      <c r="I13" s="61" t="s">
+      <c r="H13" s="44"/>
+      <c r="I13" s="42" t="s">
         <v>116</v>
       </c>
       <c r="J13" s="3" t="s">
@@ -3358,21 +3406,21 @@
       </c>
     </row>
     <row r="14" spans="1:12" ht="47.5" thickBot="1">
-      <c r="A14" s="60"/>
-      <c r="B14" s="50" t="s">
+      <c r="A14" s="52"/>
+      <c r="B14" s="40" t="s">
         <v>244</v>
       </c>
-      <c r="C14" s="51" t="s">
+      <c r="C14" s="41" t="s">
         <v>245</v>
       </c>
-      <c r="D14" s="50" t="s">
+      <c r="D14" s="40" t="s">
         <v>246</v>
       </c>
-      <c r="E14" s="45" t="s">
+      <c r="E14" s="35" t="s">
         <v>247</v>
       </c>
-      <c r="H14" s="27"/>
-      <c r="I14" s="61" t="s">
+      <c r="H14" s="44"/>
+      <c r="I14" s="42" t="s">
         <v>117</v>
       </c>
       <c r="J14" s="4" t="s">
@@ -3386,22 +3434,22 @@
       </c>
     </row>
     <row r="15" spans="1:12" ht="24">
-      <c r="A15" s="58" t="s">
+      <c r="A15" s="50" t="s">
         <v>248</v>
       </c>
-      <c r="B15" s="46" t="s">
+      <c r="B15" s="36" t="s">
         <v>249</v>
       </c>
-      <c r="C15" s="46" t="s">
+      <c r="C15" s="36" t="s">
         <v>250</v>
       </c>
-      <c r="D15" s="47" t="s">
+      <c r="D15" s="37" t="s">
         <v>251</v>
       </c>
-      <c r="E15" s="41" t="s">
+      <c r="E15" s="31" t="s">
         <v>252</v>
       </c>
-      <c r="H15" s="27" t="s">
+      <c r="H15" s="44" t="s">
         <v>7</v>
       </c>
       <c r="I15" s="2" t="s">
@@ -3418,20 +3466,20 @@
       </c>
     </row>
     <row r="16" spans="1:12" ht="24">
-      <c r="A16" s="59"/>
-      <c r="B16" s="48" t="s">
+      <c r="A16" s="51"/>
+      <c r="B16" s="38" t="s">
         <v>253</v>
       </c>
-      <c r="C16" s="48" t="s">
+      <c r="C16" s="38" t="s">
         <v>254</v>
       </c>
-      <c r="D16" s="49" t="s">
+      <c r="D16" s="39" t="s">
         <v>255</v>
       </c>
-      <c r="E16" s="43" t="s">
+      <c r="E16" s="33" t="s">
         <v>256</v>
       </c>
-      <c r="H16" s="27"/>
+      <c r="H16" s="44"/>
       <c r="I16" s="3" t="s">
         <v>64</v>
       </c>
@@ -3446,20 +3494,20 @@
       </c>
     </row>
     <row r="17" spans="1:12" ht="24">
-      <c r="A17" s="59"/>
-      <c r="B17" s="48" t="s">
+      <c r="A17" s="51"/>
+      <c r="B17" s="38" t="s">
         <v>257</v>
       </c>
-      <c r="C17" s="48" t="s">
+      <c r="C17" s="38" t="s">
         <v>258</v>
       </c>
-      <c r="D17" s="49" t="s">
+      <c r="D17" s="39" t="s">
         <v>255</v>
       </c>
-      <c r="E17" s="43" t="s">
+      <c r="E17" s="33" t="s">
         <v>259</v>
       </c>
-      <c r="H17" s="27"/>
+      <c r="H17" s="44"/>
       <c r="I17" s="3" t="s">
         <v>65</v>
       </c>
@@ -3474,20 +3522,20 @@
       </c>
     </row>
     <row r="18" spans="1:12" ht="24">
-      <c r="A18" s="59"/>
-      <c r="B18" s="48" t="s">
+      <c r="A18" s="51"/>
+      <c r="B18" s="38" t="s">
         <v>260</v>
       </c>
-      <c r="C18" s="48" t="s">
+      <c r="C18" s="38" t="s">
         <v>261</v>
       </c>
-      <c r="D18" s="49" t="s">
+      <c r="D18" s="39" t="s">
         <v>262</v>
       </c>
-      <c r="E18" s="43" t="s">
+      <c r="E18" s="33" t="s">
         <v>256</v>
       </c>
-      <c r="H18" s="27"/>
+      <c r="H18" s="44"/>
       <c r="I18" s="3" t="s">
         <v>66</v>
       </c>
@@ -3502,20 +3550,20 @@
       </c>
     </row>
     <row r="19" spans="1:12" ht="24">
-      <c r="A19" s="59"/>
-      <c r="B19" s="48" t="s">
+      <c r="A19" s="51"/>
+      <c r="B19" s="38" t="s">
         <v>263</v>
       </c>
-      <c r="C19" s="48" t="s">
+      <c r="C19" s="38" t="s">
         <v>264</v>
       </c>
-      <c r="D19" s="49" t="s">
+      <c r="D19" s="39" t="s">
         <v>251</v>
       </c>
-      <c r="E19" s="43" t="s">
+      <c r="E19" s="33" t="s">
         <v>265</v>
       </c>
-      <c r="H19" s="27"/>
+      <c r="H19" s="44"/>
       <c r="I19" s="3" t="s">
         <v>67</v>
       </c>
@@ -3530,20 +3578,20 @@
       </c>
     </row>
     <row r="20" spans="1:12" ht="24.5" thickBot="1">
-      <c r="A20" s="60"/>
-      <c r="B20" s="51" t="s">
+      <c r="A20" s="52"/>
+      <c r="B20" s="41" t="s">
         <v>266</v>
       </c>
-      <c r="C20" s="51" t="s">
+      <c r="C20" s="41" t="s">
         <v>267</v>
       </c>
-      <c r="D20" s="50" t="s">
+      <c r="D20" s="40" t="s">
         <v>268</v>
       </c>
-      <c r="E20" s="45" t="s">
+      <c r="E20" s="35" t="s">
         <v>269</v>
       </c>
-      <c r="H20" s="27"/>
+      <c r="H20" s="44"/>
       <c r="I20" s="4" t="s">
         <v>68</v>
       </c>
@@ -3558,25 +3606,25 @@
       </c>
     </row>
     <row r="21" spans="1:12" ht="23">
-      <c r="A21" s="58" t="s">
+      <c r="A21" s="50" t="s">
         <v>270</v>
       </c>
-      <c r="B21" s="47" t="s">
+      <c r="B21" s="37" t="s">
         <v>271</v>
       </c>
-      <c r="C21" s="47" t="s">
+      <c r="C21" s="37" t="s">
         <v>147</v>
       </c>
-      <c r="D21" s="47" t="s">
+      <c r="D21" s="37" t="s">
         <v>16</v>
       </c>
-      <c r="E21" s="41" t="s">
+      <c r="E21" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="H21" s="27" t="s">
+      <c r="H21" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="I21" s="61" t="s">
+      <c r="I21" s="42" t="s">
         <v>146</v>
       </c>
       <c r="J21" s="2" t="s">
@@ -3590,20 +3638,20 @@
       </c>
     </row>
     <row r="22" spans="1:12" ht="23">
-      <c r="A22" s="59"/>
-      <c r="B22" s="49" t="s">
+      <c r="A22" s="51"/>
+      <c r="B22" s="39" t="s">
         <v>273</v>
       </c>
-      <c r="C22" s="49" t="s">
+      <c r="C22" s="39" t="s">
         <v>274</v>
       </c>
-      <c r="D22" s="49" t="s">
+      <c r="D22" s="39" t="s">
         <v>17</v>
       </c>
-      <c r="E22" s="43" t="s">
+      <c r="E22" s="33" t="s">
         <v>275</v>
       </c>
-      <c r="H22" s="27"/>
+      <c r="H22" s="44"/>
       <c r="I22" s="3" t="s">
         <v>149</v>
       </c>
@@ -3618,24 +3666,24 @@
       </c>
     </row>
     <row r="23" spans="1:12" ht="23">
-      <c r="A23" s="59"/>
-      <c r="B23" s="49" t="s">
+      <c r="A23" s="51"/>
+      <c r="B23" s="39" t="s">
         <v>276</v>
       </c>
-      <c r="C23" s="49" t="s">
+      <c r="C23" s="39" t="s">
         <v>277</v>
       </c>
-      <c r="D23" s="49" t="s">
+      <c r="D23" s="39" t="s">
         <v>14</v>
       </c>
-      <c r="E23" s="43" t="s">
+      <c r="E23" s="33" t="s">
         <v>278</v>
       </c>
-      <c r="H23" s="27"/>
+      <c r="H23" s="44"/>
       <c r="I23" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="J23" s="36" t="s">
+      <c r="J23" s="26" t="s">
         <v>199</v>
       </c>
       <c r="K23" s="3" t="s">
@@ -3646,20 +3694,20 @@
       </c>
     </row>
     <row r="24" spans="1:12" ht="23">
-      <c r="A24" s="59"/>
-      <c r="B24" s="49" t="s">
+      <c r="A24" s="51"/>
+      <c r="B24" s="39" t="s">
         <v>279</v>
       </c>
-      <c r="C24" s="49" t="s">
+      <c r="C24" s="39" t="s">
         <v>280</v>
       </c>
-      <c r="D24" s="49" t="s">
+      <c r="D24" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="E24" s="43" t="s">
+      <c r="E24" s="33" t="s">
         <v>281</v>
       </c>
-      <c r="H24" s="27"/>
+      <c r="H24" s="44"/>
       <c r="I24" s="3" t="s">
         <v>153</v>
       </c>
@@ -3674,20 +3722,20 @@
       </c>
     </row>
     <row r="25" spans="1:12" ht="23">
-      <c r="A25" s="59"/>
-      <c r="B25" s="49" t="s">
+      <c r="A25" s="51"/>
+      <c r="B25" s="39" t="s">
         <v>282</v>
       </c>
-      <c r="C25" s="49" t="s">
+      <c r="C25" s="39" t="s">
         <v>283</v>
       </c>
-      <c r="D25" s="49" t="s">
+      <c r="D25" s="39" t="s">
         <v>13</v>
       </c>
-      <c r="E25" s="43" t="s">
+      <c r="E25" s="33" t="s">
         <v>284</v>
       </c>
-      <c r="H25" s="27"/>
+      <c r="H25" s="44"/>
       <c r="I25" s="3" t="s">
         <v>161</v>
       </c>
@@ -3702,20 +3750,20 @@
       </c>
     </row>
     <row r="26" spans="1:12" ht="23.5" thickBot="1">
-      <c r="A26" s="60"/>
-      <c r="B26" s="50" t="s">
+      <c r="A26" s="52"/>
+      <c r="B26" s="40" t="s">
         <v>285</v>
       </c>
-      <c r="C26" s="50" t="s">
+      <c r="C26" s="40" t="s">
         <v>286</v>
       </c>
-      <c r="D26" s="50" t="s">
+      <c r="D26" s="40" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="45" t="s">
+      <c r="E26" s="35" t="s">
         <v>287</v>
       </c>
-      <c r="H26" s="27"/>
+      <c r="H26" s="44"/>
       <c r="I26" s="4" t="s">
         <v>164</v>
       </c>
@@ -3730,22 +3778,22 @@
       </c>
     </row>
     <row r="27" spans="1:12" ht="24">
-      <c r="A27" s="58" t="s">
+      <c r="A27" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="B27" s="47" t="s">
+      <c r="B27" s="37" t="s">
         <v>288</v>
       </c>
-      <c r="C27" s="46" t="s">
+      <c r="C27" s="36" t="s">
         <v>289</v>
       </c>
-      <c r="D27" s="46" t="s">
+      <c r="D27" s="36" t="s">
         <v>11</v>
       </c>
-      <c r="E27" s="41" t="s">
+      <c r="E27" s="31" t="s">
         <v>290</v>
       </c>
-      <c r="H27" s="28" t="s">
+      <c r="H27" s="45" t="s">
         <v>9</v>
       </c>
       <c r="I27" s="2" t="s">
@@ -3762,20 +3810,20 @@
       </c>
     </row>
     <row r="28" spans="1:12" ht="24">
-      <c r="A28" s="59"/>
-      <c r="B28" s="49" t="s">
+      <c r="A28" s="51"/>
+      <c r="B28" s="39" t="s">
         <v>291</v>
       </c>
-      <c r="C28" s="48" t="s">
+      <c r="C28" s="38" t="s">
         <v>292</v>
       </c>
-      <c r="D28" s="48" t="s">
+      <c r="D28" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="E28" s="43" t="s">
+      <c r="E28" s="33" t="s">
         <v>293</v>
       </c>
-      <c r="H28" s="29"/>
+      <c r="H28" s="46"/>
       <c r="I28" s="3" t="s">
         <v>168</v>
       </c>
@@ -3790,20 +3838,20 @@
       </c>
     </row>
     <row r="29" spans="1:12" ht="24">
-      <c r="A29" s="59"/>
-      <c r="B29" s="49" t="s">
+      <c r="A29" s="51"/>
+      <c r="B29" s="39" t="s">
         <v>294</v>
       </c>
-      <c r="C29" s="48" t="s">
+      <c r="C29" s="38" t="s">
         <v>295</v>
       </c>
-      <c r="D29" s="48" t="s">
+      <c r="D29" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="E29" s="43" t="s">
+      <c r="E29" s="33" t="s">
         <v>296</v>
       </c>
-      <c r="H29" s="29"/>
+      <c r="H29" s="46"/>
       <c r="I29" s="3" t="s">
         <v>169</v>
       </c>
@@ -3818,20 +3866,20 @@
       </c>
     </row>
     <row r="30" spans="1:12" ht="24">
-      <c r="A30" s="59"/>
-      <c r="B30" s="49" t="s">
+      <c r="A30" s="51"/>
+      <c r="B30" s="39" t="s">
         <v>297</v>
       </c>
-      <c r="C30" s="48" t="s">
+      <c r="C30" s="38" t="s">
         <v>298</v>
       </c>
-      <c r="D30" s="48" t="s">
+      <c r="D30" s="38" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="43" t="s">
+      <c r="E30" s="33" t="s">
         <v>299</v>
       </c>
-      <c r="H30" s="29"/>
+      <c r="H30" s="46"/>
       <c r="I30" s="3" t="s">
         <v>170</v>
       </c>
@@ -3846,20 +3894,20 @@
       </c>
     </row>
     <row r="31" spans="1:12" ht="24">
-      <c r="A31" s="59"/>
-      <c r="B31" s="49" t="s">
+      <c r="A31" s="51"/>
+      <c r="B31" s="39" t="s">
         <v>300</v>
       </c>
-      <c r="C31" s="48" t="s">
+      <c r="C31" s="38" t="s">
         <v>301</v>
       </c>
-      <c r="D31" s="48" t="s">
+      <c r="D31" s="38" t="s">
         <v>69</v>
       </c>
-      <c r="E31" s="43" t="s">
+      <c r="E31" s="33" t="s">
         <v>302</v>
       </c>
-      <c r="H31" s="29"/>
+      <c r="H31" s="46"/>
       <c r="I31" s="3" t="s">
         <v>171</v>
       </c>
@@ -3874,20 +3922,20 @@
       </c>
     </row>
     <row r="32" spans="1:12" ht="24.5" thickBot="1">
-      <c r="A32" s="60"/>
-      <c r="B32" s="50" t="s">
+      <c r="A32" s="52"/>
+      <c r="B32" s="40" t="s">
         <v>303</v>
       </c>
-      <c r="C32" s="51" t="s">
+      <c r="C32" s="41" t="s">
         <v>304</v>
       </c>
-      <c r="D32" s="51" t="s">
+      <c r="D32" s="41" t="s">
         <v>16</v>
       </c>
-      <c r="E32" s="45" t="s">
+      <c r="E32" s="35" t="s">
         <v>305</v>
       </c>
-      <c r="H32" s="26"/>
+      <c r="H32" s="43"/>
       <c r="I32" s="4" t="s">
         <v>172</v>
       </c>
@@ -3902,84 +3950,84 @@
       </c>
     </row>
     <row r="33" spans="1:5" ht="24">
-      <c r="A33" s="58" t="s">
+      <c r="A33" s="50" t="s">
         <v>306</v>
       </c>
-      <c r="B33" s="46" t="s">
+      <c r="B33" s="36" t="s">
         <v>307</v>
       </c>
-      <c r="C33" s="46" t="s">
+      <c r="C33" s="36" t="s">
         <v>308</v>
       </c>
-      <c r="D33" s="46" t="s">
+      <c r="D33" s="36" t="s">
         <v>15</v>
       </c>
-      <c r="E33" s="41"/>
+      <c r="E33" s="31"/>
     </row>
     <row r="34" spans="1:5" ht="24">
-      <c r="A34" s="59"/>
-      <c r="B34" s="48" t="s">
+      <c r="A34" s="51"/>
+      <c r="B34" s="38" t="s">
         <v>309</v>
       </c>
-      <c r="C34" s="48" t="s">
+      <c r="C34" s="38" t="s">
         <v>310</v>
       </c>
-      <c r="D34" s="48" t="s">
+      <c r="D34" s="38" t="s">
         <v>13</v>
       </c>
-      <c r="E34" s="43"/>
+      <c r="E34" s="33"/>
     </row>
     <row r="35" spans="1:5" ht="35.5">
-      <c r="A35" s="59"/>
-      <c r="B35" s="48" t="s">
+      <c r="A35" s="51"/>
+      <c r="B35" s="38" t="s">
         <v>311</v>
       </c>
-      <c r="C35" s="48" t="s">
+      <c r="C35" s="38" t="s">
         <v>312</v>
       </c>
-      <c r="D35" s="48" t="s">
+      <c r="D35" s="38" t="s">
         <v>11</v>
       </c>
-      <c r="E35" s="43"/>
+      <c r="E35" s="33"/>
     </row>
     <row r="36" spans="1:5" ht="35.5">
-      <c r="A36" s="59"/>
-      <c r="B36" s="48" t="s">
+      <c r="A36" s="51"/>
+      <c r="B36" s="38" t="s">
         <v>313</v>
       </c>
-      <c r="C36" s="48" t="s">
+      <c r="C36" s="38" t="s">
         <v>314</v>
       </c>
-      <c r="D36" s="48" t="s">
+      <c r="D36" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="E36" s="43"/>
+      <c r="E36" s="33"/>
     </row>
     <row r="37" spans="1:5" ht="24">
-      <c r="A37" s="59"/>
-      <c r="B37" s="48" t="s">
+      <c r="A37" s="51"/>
+      <c r="B37" s="38" t="s">
         <v>315</v>
       </c>
-      <c r="C37" s="48" t="s">
+      <c r="C37" s="38" t="s">
         <v>316</v>
       </c>
-      <c r="D37" s="48" t="s">
+      <c r="D37" s="38" t="s">
         <v>14</v>
       </c>
-      <c r="E37" s="43"/>
+      <c r="E37" s="33"/>
     </row>
     <row r="38" spans="1:5" ht="24.5" thickBot="1">
-      <c r="A38" s="60"/>
-      <c r="B38" s="51" t="s">
+      <c r="A38" s="52"/>
+      <c r="B38" s="41" t="s">
         <v>317</v>
       </c>
-      <c r="C38" s="51" t="s">
+      <c r="C38" s="41" t="s">
         <v>318</v>
       </c>
-      <c r="D38" s="51" t="s">
+      <c r="D38" s="41" t="s">
         <v>69</v>
       </c>
-      <c r="E38" s="45"/>
+      <c r="E38" s="35"/>
     </row>
   </sheetData>
   <autoFilter ref="A2:E38"/>
@@ -4037,10 +4085,10 @@
       </c>
     </row>
     <row r="2" spans="1:7">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="45" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="59" t="s">
         <v>48</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -4060,8 +4108,8 @@
       </c>
     </row>
     <row r="3" spans="1:7">
-      <c r="A3" s="29"/>
-      <c r="B3" s="31"/>
+      <c r="A3" s="46"/>
+      <c r="B3" s="60"/>
       <c r="C3" s="3" t="s">
         <v>52</v>
       </c>
@@ -4079,8 +4127,8 @@
       </c>
     </row>
     <row r="4" spans="1:7">
-      <c r="A4" s="29"/>
-      <c r="B4" s="31"/>
+      <c r="A4" s="46"/>
+      <c r="B4" s="60"/>
       <c r="C4" s="3" t="s">
         <v>53</v>
       </c>
@@ -4098,8 +4146,8 @@
       </c>
     </row>
     <row r="5" spans="1:7">
-      <c r="A5" s="26"/>
-      <c r="B5" s="32"/>
+      <c r="A5" s="43"/>
+      <c r="B5" s="61"/>
       <c r="C5" s="3" t="s">
         <v>55</v>
       </c>
@@ -4117,10 +4165,10 @@
       </c>
     </row>
     <row r="6" spans="1:7">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="44" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="59" t="s">
         <v>131</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -4140,8 +4188,8 @@
       </c>
     </row>
     <row r="7" spans="1:7">
-      <c r="A7" s="27"/>
-      <c r="B7" s="31" t="s">
+      <c r="A7" s="44"/>
+      <c r="B7" s="60" t="s">
         <v>131</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -4161,8 +4209,8 @@
       </c>
     </row>
     <row r="8" spans="1:7">
-      <c r="A8" s="27"/>
-      <c r="B8" s="31"/>
+      <c r="A8" s="44"/>
+      <c r="B8" s="60"/>
       <c r="C8" s="3" t="s">
         <v>138</v>
       </c>
@@ -4180,8 +4228,8 @@
       </c>
     </row>
     <row r="9" spans="1:7">
-      <c r="A9" s="27"/>
-      <c r="B9" s="32"/>
+      <c r="A9" s="44"/>
+      <c r="B9" s="61"/>
       <c r="C9" s="3" t="s">
         <v>196</v>
       </c>
@@ -4199,10 +4247,10 @@
       </c>
     </row>
     <row r="10" spans="1:7">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="44" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="59" t="s">
         <v>132</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -4222,8 +4270,8 @@
       </c>
     </row>
     <row r="11" spans="1:7">
-      <c r="A11" s="27"/>
-      <c r="B11" s="31"/>
+      <c r="A11" s="44"/>
+      <c r="B11" s="60"/>
       <c r="C11" s="3" t="s">
         <v>79</v>
       </c>
@@ -4241,8 +4289,8 @@
       </c>
     </row>
     <row r="12" spans="1:7">
-      <c r="A12" s="27"/>
-      <c r="B12" s="31"/>
+      <c r="A12" s="44"/>
+      <c r="B12" s="60"/>
       <c r="C12" s="3" t="s">
         <v>81</v>
       </c>
@@ -4260,8 +4308,8 @@
       </c>
     </row>
     <row r="13" spans="1:7">
-      <c r="A13" s="27"/>
-      <c r="B13" s="32"/>
+      <c r="A13" s="44"/>
+      <c r="B13" s="61"/>
       <c r="C13" s="3" t="s">
         <v>82</v>
       </c>
@@ -4279,10 +4327,10 @@
       </c>
     </row>
     <row r="14" spans="1:7">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="44" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="59" t="s">
         <v>179</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -4302,8 +4350,8 @@
       </c>
     </row>
     <row r="15" spans="1:7">
-      <c r="A15" s="27"/>
-      <c r="B15" s="31" t="s">
+      <c r="A15" s="44"/>
+      <c r="B15" s="60" t="s">
         <v>131</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -4323,8 +4371,8 @@
       </c>
     </row>
     <row r="16" spans="1:7">
-      <c r="A16" s="27"/>
-      <c r="B16" s="31"/>
+      <c r="A16" s="44"/>
+      <c r="B16" s="60"/>
       <c r="C16" s="3" t="s">
         <v>183</v>
       </c>
@@ -4342,8 +4390,8 @@
       </c>
     </row>
     <row r="17" spans="1:7">
-      <c r="A17" s="27"/>
-      <c r="B17" s="32"/>
+      <c r="A17" s="44"/>
+      <c r="B17" s="61"/>
       <c r="C17" s="4" t="s">
         <v>185</v>
       </c>
@@ -4361,10 +4409,10 @@
       </c>
     </row>
     <row r="18" spans="1:7">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="46" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="59" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -4384,8 +4432,8 @@
       </c>
     </row>
     <row r="19" spans="1:7">
-      <c r="A19" s="29"/>
-      <c r="B19" s="31"/>
+      <c r="A19" s="46"/>
+      <c r="B19" s="60"/>
       <c r="C19" s="3" t="s">
         <v>95</v>
       </c>
@@ -4403,8 +4451,8 @@
       </c>
     </row>
     <row r="20" spans="1:7">
-      <c r="A20" s="29"/>
-      <c r="B20" s="31"/>
+      <c r="A20" s="46"/>
+      <c r="B20" s="60"/>
       <c r="C20" s="3" t="s">
         <v>99</v>
       </c>
@@ -4422,8 +4470,8 @@
       </c>
     </row>
     <row r="21" spans="1:7">
-      <c r="A21" s="26"/>
-      <c r="B21" s="32"/>
+      <c r="A21" s="43"/>
+      <c r="B21" s="61"/>
       <c r="C21" s="4" t="s">
         <v>102</v>
       </c>
@@ -4442,16 +4490,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:B13"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="B14:B17"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -4477,7 +4525,7 @@
       </c>
     </row>
     <row r="3" spans="1:4">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="62" t="s">
         <v>62</v>
       </c>
       <c r="B3" s="8" t="s">
@@ -4491,7 +4539,7 @@
       </c>
     </row>
     <row r="4" spans="1:4">
-      <c r="A4" s="33"/>
+      <c r="A4" s="62"/>
       <c r="B4" s="8" t="s">
         <v>33</v>
       </c>
@@ -4503,7 +4551,7 @@
       </c>
     </row>
     <row r="5" spans="1:4">
-      <c r="A5" s="33"/>
+      <c r="A5" s="62"/>
       <c r="B5" s="8" t="s">
         <v>35</v>
       </c>
@@ -4515,7 +4563,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" thickBot="1">
-      <c r="A6" s="34"/>
+      <c r="A6" s="63"/>
       <c r="B6" s="9" t="s">
         <v>37</v>
       </c>
@@ -4527,7 +4575,7 @@
       </c>
     </row>
     <row r="7" spans="1:4">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="62" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="16" t="s">
@@ -4541,7 +4589,7 @@
       </c>
     </row>
     <row r="8" spans="1:4">
-      <c r="A8" s="33"/>
+      <c r="A8" s="62"/>
       <c r="B8" s="8" t="s">
         <v>33</v>
       </c>
@@ -4553,7 +4601,7 @@
       </c>
     </row>
     <row r="9" spans="1:4">
-      <c r="A9" s="33"/>
+      <c r="A9" s="62"/>
       <c r="B9" s="8" t="s">
         <v>35</v>
       </c>
@@ -4565,7 +4613,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" thickBot="1">
-      <c r="A10" s="33"/>
+      <c r="A10" s="62"/>
       <c r="B10" s="9" t="s">
         <v>37</v>
       </c>
@@ -4577,7 +4625,7 @@
       </c>
     </row>
     <row r="11" spans="1:4">
-      <c r="A11" s="35" t="s">
+      <c r="A11" s="64" t="s">
         <v>94</v>
       </c>
       <c r="B11" s="16" t="s">
@@ -4589,7 +4637,7 @@
       <c r="D11" s="21"/>
     </row>
     <row r="12" spans="1:4">
-      <c r="A12" s="33"/>
+      <c r="A12" s="62"/>
       <c r="B12" s="8" t="s">
         <v>33</v>
       </c>
@@ -4599,7 +4647,7 @@
       <c r="D12" s="22"/>
     </row>
     <row r="13" spans="1:4">
-      <c r="A13" s="33"/>
+      <c r="A13" s="62"/>
       <c r="B13" s="8" t="s">
         <v>35</v>
       </c>
@@ -4609,7 +4657,7 @@
       <c r="D13" s="22"/>
     </row>
     <row r="14" spans="1:4" ht="15" thickBot="1">
-      <c r="A14" s="34"/>
+      <c r="A14" s="63"/>
       <c r="B14" s="9" t="s">
         <v>37</v>
       </c>
@@ -4621,7 +4669,7 @@
       </c>
     </row>
     <row r="15" spans="1:4">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="62" t="s">
         <v>133</v>
       </c>
       <c r="B15" s="16" t="s">
@@ -4635,7 +4683,7 @@
       </c>
     </row>
     <row r="16" spans="1:4">
-      <c r="A16" s="33"/>
+      <c r="A16" s="62"/>
       <c r="B16" s="8" t="s">
         <v>33</v>
       </c>
@@ -4647,7 +4695,7 @@
       </c>
     </row>
     <row r="17" spans="1:4">
-      <c r="A17" s="33"/>
+      <c r="A17" s="62"/>
       <c r="B17" s="8" t="s">
         <v>35</v>
       </c>
@@ -4659,7 +4707,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" thickBot="1">
-      <c r="A18" s="34"/>
+      <c r="A18" s="63"/>
       <c r="B18" s="9" t="s">
         <v>37</v>
       </c>
@@ -4671,7 +4719,7 @@
       </c>
     </row>
     <row r="19" spans="1:4">
-      <c r="A19" s="33" t="s">
+      <c r="A19" s="62" t="s">
         <v>191</v>
       </c>
       <c r="B19" s="16" t="s">
@@ -4685,7 +4733,7 @@
       </c>
     </row>
     <row r="20" spans="1:4">
-      <c r="A20" s="33"/>
+      <c r="A20" s="62"/>
       <c r="B20" s="8" t="s">
         <v>33</v>
       </c>
@@ -4697,7 +4745,7 @@
       </c>
     </row>
     <row r="21" spans="1:4">
-      <c r="A21" s="33"/>
+      <c r="A21" s="62"/>
       <c r="B21" s="8" t="s">
         <v>35</v>
       </c>
@@ -4709,7 +4757,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" thickBot="1">
-      <c r="A22" s="34"/>
+      <c r="A22" s="63"/>
       <c r="B22" s="9" t="s">
         <v>37</v>
       </c>

--- a/LOUMA phase2.xlsx
+++ b/LOUMA phase2.xlsx
@@ -9,17 +9,15 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="1"/>
   </bookViews>
   <sheets>
-    <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
-    <sheet name="Feuil4" sheetId="4" r:id="rId2"/>
-    <sheet name="Feuil2" sheetId="2" r:id="rId3"/>
-    <sheet name="Feuil3" sheetId="3" r:id="rId4"/>
+    <sheet name="Liste LOUMAS" sheetId="1" r:id="rId1"/>
+    <sheet name="Liste VTO" sheetId="2" r:id="rId2"/>
+    <sheet name="Contact" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="1" hidden="1">Feuil4!$A$2:$E$38</definedName>
-    <definedName name="A">Feuil1!$XFD$1</definedName>
+    <definedName name="A">'Liste LOUMAS'!$XFD$1</definedName>
   </definedNames>
   <calcPr calcId="162913"/>
   <extLst>
@@ -31,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="536" uniqueCount="321">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="200">
   <si>
     <t>DRV</t>
   </si>
@@ -633,376 +631,13 @@
   </si>
   <si>
     <t>12°30’03.9’’N    15°43’15.4’’W</t>
-  </si>
-  <si>
-    <t>06 GRANDS LOUMA</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Coordonnées GPS </t>
-  </si>
-  <si>
-    <t>JOUR LOUMAS</t>
-  </si>
-  <si>
-    <t>EST</t>
-  </si>
-  <si>
-    <t>NIAKHAR</t>
-  </si>
-  <si>
-    <t>14.473825, -16.402988</t>
-  </si>
-  <si>
-    <t>Lundi</t>
-  </si>
-  <si>
-    <t>18 Km +36 KM</t>
-  </si>
-  <si>
-    <t>NDIENE LAGUENE</t>
-  </si>
-  <si>
-    <t xml:space="preserve">14°30'44.5''N   15°55'28.1''W </t>
-  </si>
-  <si>
-    <t>Mardi</t>
-  </si>
-  <si>
-    <t>65 Km+130 KM</t>
-  </si>
-  <si>
-    <t>SOKONE</t>
-  </si>
-  <si>
-    <t>13.8778012, -16.3728707</t>
-  </si>
-  <si>
-    <t>Mercredi</t>
-  </si>
-  <si>
-    <t>77 Km+154 KM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13,99044°N ; 15,11439°O </t>
-  </si>
-  <si>
-    <t>Jeudi</t>
-  </si>
-  <si>
-    <t>165 Km+330 KM</t>
-  </si>
-  <si>
-    <t>DIAMA GADIO</t>
-  </si>
-  <si>
-    <t xml:space="preserve">13,78641°N ; 15,42236°O </t>
-  </si>
-  <si>
-    <t>Samedi</t>
-  </si>
-  <si>
-    <t>147 Km+294 KM</t>
-  </si>
-  <si>
-    <t>COLOBANE MBAR</t>
-  </si>
-  <si>
-    <t>14°3837 N ; 15°4227 O</t>
-  </si>
-  <si>
-    <t>Dimanche</t>
-  </si>
-  <si>
-    <t>86 Km+172 KM</t>
-  </si>
-  <si>
-    <t>NIASSANTE</t>
-  </si>
-  <si>
-    <t>16,0254900, -16,4972290</t>
-  </si>
-  <si>
-    <t> MERCREDI</t>
-  </si>
-  <si>
-    <t> 286 KM * 2 = 572 KM</t>
-  </si>
-  <si>
-    <t>15.477969,-15.866354</t>
-  </si>
-  <si>
-    <t> VENDREDI</t>
-  </si>
-  <si>
-    <t> 85 KM * 2 = 170 KM</t>
-  </si>
-  <si>
-    <t>15.926355,-15.967798</t>
-  </si>
-  <si>
-    <t> 180 KM *2 = 360 KM</t>
-  </si>
-  <si>
-    <t>GASSANE</t>
-  </si>
-  <si>
-    <t>14.8192774;-15.3005457</t>
-  </si>
-  <si>
-    <t> LUNDI</t>
-  </si>
-  <si>
-    <t> 110 KM *2 = 220 KM</t>
-  </si>
-  <si>
-    <t>LABGAR</t>
-  </si>
-  <si>
-    <t>15.8324420;-14.8085243</t>
-  </si>
-  <si>
-    <t> MARDI</t>
-  </si>
-  <si>
-    <t> 70 KM * 2 = 140 KM</t>
-  </si>
-  <si>
-    <t>DOUNDE</t>
-  </si>
-  <si>
-    <t>15.084233283996582000 -12.901286125183105000</t>
-  </si>
-  <si>
-    <t> SAMEDI</t>
-  </si>
-  <si>
-    <t> 310 KM * 2 = 620 KM</t>
-  </si>
-  <si>
-    <t xml:space="preserve">SUD EST </t>
-  </si>
-  <si>
-    <t>PAYAR</t>
-  </si>
-  <si>
-    <t>14°26'10.9"N - 14°29'33.5"W</t>
-  </si>
-  <si>
-    <t> Jeudi</t>
-  </si>
-  <si>
-    <t> 160 KM</t>
-  </si>
-  <si>
-    <t>DAWADI</t>
-  </si>
-  <si>
-    <t>14°07'43.7"N - 13°58'06.4"W</t>
-  </si>
-  <si>
-    <t> Mercredi</t>
-  </si>
-  <si>
-    <t> 83 KM</t>
-  </si>
-  <si>
-    <t>KAHENE</t>
-  </si>
-  <si>
-    <t>13°45'11.7"N - 14°43'44.7"W</t>
-  </si>
-  <si>
-    <t> 114 KM</t>
-  </si>
-  <si>
-    <t>MERETO</t>
-  </si>
-  <si>
-    <t>13°49'08.0"N -14°26'26.7"W</t>
-  </si>
-  <si>
-    <t> Lundi</t>
-  </si>
-  <si>
-    <t>MAKACOLIBANTANG</t>
-  </si>
-  <si>
-    <t>13°40'46.5"N - 14°16'18.5"W</t>
-  </si>
-  <si>
-    <t> 79 km</t>
-  </si>
-  <si>
-    <t>ALTOU FASS / MALEM NIANI</t>
-  </si>
-  <si>
-    <t>13°56'21.4"N - 14°17'53.7"W</t>
-  </si>
-  <si>
-    <t> Mardi</t>
-  </si>
-  <si>
-    <t> 72 KM</t>
-  </si>
-  <si>
-    <t>SUD</t>
-  </si>
-  <si>
-    <t xml:space="preserve">DIANA </t>
-  </si>
-  <si>
-    <t> 140 (70)</t>
-  </si>
-  <si>
-    <t>DJIBANAR</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 12.543907,-15810159</t>
-  </si>
-  <si>
-    <t> 116 (58)</t>
-  </si>
-  <si>
-    <t>DIAOBE</t>
-  </si>
-  <si>
-    <t>12.915496 ,-14.150688</t>
-  </si>
-  <si>
-    <t>  84   (42)</t>
-  </si>
-  <si>
-    <t>BAYENGOU</t>
-  </si>
-  <si>
-    <t>13.207572, -15.145006</t>
-  </si>
-  <si>
-    <t> 124 (62)</t>
-  </si>
-  <si>
-    <t>MANDA DOUANE</t>
-  </si>
-  <si>
-    <t>13.3339667,-13.8229600</t>
-  </si>
-  <si>
-    <t>   64  (32)</t>
-  </si>
-  <si>
-    <t>SARE YOBA</t>
-  </si>
-  <si>
-    <t>12.76538, -15.105637</t>
-  </si>
-  <si>
-    <t>   62  (31)</t>
-  </si>
-  <si>
-    <t>MBAR</t>
-  </si>
-  <si>
-    <t>14°32'16.8''N   15°45'29.9''W</t>
-  </si>
-  <si>
-    <t>54KM</t>
-  </si>
-  <si>
-    <t>SAM YABAL</t>
-  </si>
-  <si>
-    <t>15.207794,-15.899213</t>
-  </si>
-  <si>
-    <t>30 KM</t>
-  </si>
-  <si>
-    <t>BABA GARAGE</t>
-  </si>
-  <si>
-    <t>14°56'24''N 16°29'23''W</t>
-  </si>
-  <si>
-    <t>129 KM</t>
-  </si>
-  <si>
-    <t>DIOURBEL</t>
-  </si>
-  <si>
-    <t>14.650291,-16.234170</t>
-  </si>
-  <si>
-    <t>185 KM</t>
-  </si>
-  <si>
-    <t>SADIO</t>
-  </si>
-  <si>
-    <t>14.819680-15.546418</t>
-  </si>
-  <si>
-    <t>144KM</t>
-  </si>
-  <si>
-    <t>Sandiara</t>
-  </si>
-  <si>
-    <t>14.434948-16.793366</t>
-  </si>
-  <si>
-    <t>89 KM</t>
-  </si>
-  <si>
-    <t>DR2</t>
-  </si>
-  <si>
-    <t>Marché Jeudi</t>
-  </si>
-  <si>
-    <t>14.7828199-17.376013</t>
-  </si>
-  <si>
-    <t>Marché Tivaoune Peulh</t>
-  </si>
-  <si>
-    <t>14°48'35" nord, 17°16'44" ouest</t>
-  </si>
-  <si>
-    <t>Marché Niagal Toubabou Dialaw</t>
-  </si>
-  <si>
-    <t>14°60'55"N - 17°15'14"O</t>
-  </si>
-  <si>
-    <t>Marché rond point daral Rufisque</t>
-  </si>
-  <si>
-    <t>14.71554 -17.270929</t>
-  </si>
-  <si>
-    <t>Marché Mame Thierno Bargny</t>
-  </si>
-  <si>
-    <t>14°41' 22.79" N -17°14'0.60" O</t>
-  </si>
-  <si>
-    <t>Marché Keur Mbaye Fall</t>
-  </si>
-  <si>
-    <t>14°44'23"N - 17°19'14"W</t>
-  </si>
-  <si>
-    <t>Liste des 06 grands Loumas par DR avec coordonnées géographiques PHASE 1</t>
-  </si>
-  <si>
-    <t>Liste des 06 grands Loumas par DR avec coordonnées géographiques PHASE 2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="27">
+  <fonts count="20" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1138,15 +773,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <i/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
       <name val="Calibri"/>
@@ -1158,42 +784,8 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="12"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="9"/>
-      <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
-    </font>
   </fonts>
-  <fills count="37">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1385,20 +977,8 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFBE2D5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="43">
+  <borders count="29">
     <border>
       <left/>
       <right/>
@@ -1750,211 +1330,13 @@
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right/>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </top>
       <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="medium">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top/>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="medium">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF000000"/>
-      </left>
-      <right style="medium">
-        <color rgb="FF000000"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF000000"/>
-      </top>
-      <bottom style="medium">
-        <color rgb="FF000000"/>
+        <color indexed="64"/>
       </bottom>
       <diagonal/>
     </border>
@@ -2003,7 +1385,7 @@
     <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="65">
+  <cellXfs count="37">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -2015,13 +1397,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="33" borderId="20" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="33" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="24" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="33" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="33" borderId="21" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -2031,60 +1410,14 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="15" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="14" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="34" borderId="22" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="31" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="32" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="36" borderId="33" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="38" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="40" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="42" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="37" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="39" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="0" borderId="41" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="3" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -2096,42 +1429,6 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="29" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="35" borderId="30" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="34" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="35" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="36" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2150,6 +1447,15 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="28" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="33" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -2520,7 +1826,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G31"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="21.81640625" customWidth="1"/>
     <col min="3" max="3" width="24.7265625" customWidth="1"/>
@@ -2528,7 +1834,7 @@
     <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2545,8 +1851,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="43" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="24" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -2562,8 +1868,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="44"/>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="25"/>
       <c r="B3" s="3" t="s">
         <v>20</v>
       </c>
@@ -2577,8 +1883,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="44"/>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="25"/>
       <c r="B4" s="3" t="s">
         <v>21</v>
       </c>
@@ -2592,8 +1898,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="44"/>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="25"/>
       <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
@@ -2607,8 +1913,8 @@
         <v>30</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="44"/>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="25"/>
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
@@ -2622,8 +1928,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="44"/>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="25"/>
       <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
@@ -2637,8 +1943,8 @@
         <v>29</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="44" t="s">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="25" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -2654,8 +1960,8 @@
         <v>124</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="44"/>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="25"/>
       <c r="B9" s="3" t="s">
         <v>113</v>
       </c>
@@ -2670,8 +1976,8 @@
       </c>
       <c r="G9" s="2"/>
     </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="44"/>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="25"/>
       <c r="B10" s="3" t="s">
         <v>114</v>
       </c>
@@ -2686,8 +1992,8 @@
       </c>
       <c r="G10" s="3"/>
     </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="44"/>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="25"/>
       <c r="B11" s="3" t="s">
         <v>115</v>
       </c>
@@ -2702,8 +2008,8 @@
       </c>
       <c r="G11" s="3"/>
     </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="44"/>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="25"/>
       <c r="B12" s="3" t="s">
         <v>116</v>
       </c>
@@ -2718,8 +2024,8 @@
       </c>
       <c r="G12" s="3"/>
     </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="44"/>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="25"/>
       <c r="B13" s="4" t="s">
         <v>117</v>
       </c>
@@ -2734,8 +2040,8 @@
       </c>
       <c r="G13" s="3"/>
     </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="44" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="25" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -2752,8 +2058,8 @@
       </c>
       <c r="G14" s="3"/>
     </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="44"/>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="25"/>
       <c r="B15" s="3" t="s">
         <v>64</v>
       </c>
@@ -2767,8 +2073,8 @@
         <v>156</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="44"/>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="25"/>
       <c r="B16" s="3" t="s">
         <v>65</v>
       </c>
@@ -2782,8 +2088,8 @@
         <v>157</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
-      <c r="A17" s="44"/>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="25"/>
       <c r="B17" s="3" t="s">
         <v>66</v>
       </c>
@@ -2797,8 +2103,8 @@
         <v>155</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
-      <c r="A18" s="44"/>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="25"/>
       <c r="B18" s="3" t="s">
         <v>67</v>
       </c>
@@ -2812,8 +2118,8 @@
         <v>158</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
-      <c r="A19" s="44"/>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="25"/>
       <c r="B19" s="4" t="s">
         <v>68</v>
       </c>
@@ -2827,8 +2133,8 @@
         <v>159</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
-      <c r="A20" s="44" t="s">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -2844,8 +2150,8 @@
         <v>148</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
-      <c r="A21" s="44"/>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="25"/>
       <c r="B21" s="3" t="s">
         <v>149</v>
       </c>
@@ -2859,12 +2165,12 @@
         <v>151</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
-      <c r="A22" s="44"/>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="25"/>
       <c r="B22" s="3" t="s">
         <v>152</v>
       </c>
-      <c r="C22" s="26" t="s">
+      <c r="C22" s="23" t="s">
         <v>199</v>
       </c>
       <c r="D22" s="3" t="s">
@@ -2874,8 +2180,8 @@
         <v>28</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
-      <c r="A23" s="44"/>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="25"/>
       <c r="B23" s="3" t="s">
         <v>153</v>
       </c>
@@ -2889,8 +2195,8 @@
         <v>160</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
-      <c r="A24" s="44"/>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="25"/>
       <c r="B24" s="3" t="s">
         <v>161</v>
       </c>
@@ -2904,8 +2210,8 @@
         <v>163</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
-      <c r="A25" s="44"/>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="25"/>
       <c r="B25" s="4" t="s">
         <v>164</v>
       </c>
@@ -2919,8 +2225,8 @@
         <v>166</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
-      <c r="A26" s="45" t="s">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="26" t="s">
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -2936,8 +2242,8 @@
         <v>173</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
-      <c r="A27" s="46"/>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="27"/>
       <c r="B27" s="3" t="s">
         <v>168</v>
       </c>
@@ -2951,8 +2257,8 @@
         <v>174</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
-      <c r="A28" s="46"/>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="27"/>
       <c r="B28" s="3" t="s">
         <v>169</v>
       </c>
@@ -2966,8 +2272,8 @@
         <v>175</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
-      <c r="A29" s="46"/>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="27"/>
       <c r="B29" s="3" t="s">
         <v>170</v>
       </c>
@@ -2981,8 +2287,8 @@
         <v>176</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
-      <c r="A30" s="46"/>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="27"/>
       <c r="B30" s="3" t="s">
         <v>171</v>
       </c>
@@ -2996,8 +2302,8 @@
         <v>177</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
-      <c r="A31" s="43"/>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="24"/>
       <c r="B31" s="4" t="s">
         <v>172</v>
       </c>
@@ -3027,1033 +2333,8 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L38"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
-  <cols>
-    <col min="1" max="1" width="13.90625" customWidth="1"/>
-    <col min="2" max="2" width="12.453125" customWidth="1"/>
-    <col min="3" max="3" width="12.6328125" customWidth="1"/>
-    <col min="4" max="4" width="11.6328125" customWidth="1"/>
-    <col min="5" max="5" width="12.6328125" customWidth="1"/>
-    <col min="9" max="9" width="17.36328125" customWidth="1"/>
-    <col min="10" max="10" width="17.08984375" customWidth="1"/>
-    <col min="11" max="11" width="13.7265625" customWidth="1"/>
-    <col min="12" max="12" width="14.7265625" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:12" ht="16" thickBot="1">
-      <c r="A1" s="53" t="s">
-        <v>319</v>
-      </c>
-      <c r="B1" s="54"/>
-      <c r="C1" s="54"/>
-      <c r="D1" s="54"/>
-      <c r="E1" s="55"/>
-      <c r="H1" s="47" t="s">
-        <v>320</v>
-      </c>
-      <c r="I1" s="48"/>
-      <c r="J1" s="48"/>
-      <c r="K1" s="48"/>
-      <c r="L1" s="49"/>
-    </row>
-    <row r="2" spans="1:12" ht="31" customHeight="1" thickBot="1">
-      <c r="A2" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="C2" s="28" t="s">
-        <v>201</v>
-      </c>
-      <c r="D2" s="28" t="s">
-        <v>202</v>
-      </c>
-      <c r="E2" s="29" t="s">
-        <v>4</v>
-      </c>
-      <c r="H2" s="27" t="s">
-        <v>0</v>
-      </c>
-      <c r="I2" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="J2" s="28" t="s">
-        <v>2</v>
-      </c>
-      <c r="K2" s="28" t="s">
-        <v>3</v>
-      </c>
-      <c r="L2" s="29" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" ht="24">
-      <c r="A3" s="56" t="s">
-        <v>203</v>
-      </c>
-      <c r="B3" s="30" t="s">
-        <v>204</v>
-      </c>
-      <c r="C3" s="30" t="s">
-        <v>205</v>
-      </c>
-      <c r="D3" s="30" t="s">
-        <v>206</v>
-      </c>
-      <c r="E3" s="31" t="s">
-        <v>207</v>
-      </c>
-      <c r="H3" s="43" t="s">
-        <v>5</v>
-      </c>
-      <c r="I3" s="42" t="s">
-        <v>19</v>
-      </c>
-      <c r="J3" s="2" t="s">
-        <v>25</v>
-      </c>
-      <c r="K3" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L3" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" ht="24">
-      <c r="A4" s="57"/>
-      <c r="B4" s="32" t="s">
-        <v>208</v>
-      </c>
-      <c r="C4" s="32" t="s">
-        <v>209</v>
-      </c>
-      <c r="D4" s="32" t="s">
-        <v>210</v>
-      </c>
-      <c r="E4" s="33" t="s">
-        <v>211</v>
-      </c>
-      <c r="H4" s="44"/>
-      <c r="I4" s="42" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" s="3" t="s">
-        <v>26</v>
-      </c>
-      <c r="K4" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L4" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" ht="24">
-      <c r="A5" s="57"/>
-      <c r="B5" s="32" t="s">
-        <v>212</v>
-      </c>
-      <c r="C5" s="32" t="s">
-        <v>213</v>
-      </c>
-      <c r="D5" s="32" t="s">
-        <v>214</v>
-      </c>
-      <c r="E5" s="33" t="s">
-        <v>215</v>
-      </c>
-      <c r="H5" s="44"/>
-      <c r="I5" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="J5" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="K5" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="L5" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" ht="24">
-      <c r="A6" s="57"/>
-      <c r="B6" s="32" t="s">
-        <v>19</v>
-      </c>
-      <c r="C6" s="32" t="s">
-        <v>216</v>
-      </c>
-      <c r="D6" s="32" t="s">
-        <v>217</v>
-      </c>
-      <c r="E6" s="33" t="s">
-        <v>218</v>
-      </c>
-      <c r="H6" s="44"/>
-      <c r="I6" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="J6" s="3" t="s">
-        <v>24</v>
-      </c>
-      <c r="K6" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L6" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" ht="24">
-      <c r="A7" s="57"/>
-      <c r="B7" s="32" t="s">
-        <v>219</v>
-      </c>
-      <c r="C7" s="32" t="s">
-        <v>220</v>
-      </c>
-      <c r="D7" s="32" t="s">
-        <v>221</v>
-      </c>
-      <c r="E7" s="33" t="s">
-        <v>222</v>
-      </c>
-      <c r="H7" s="44"/>
-      <c r="I7" s="3" t="s">
-        <v>10</v>
-      </c>
-      <c r="J7" s="3" t="s">
-        <v>22</v>
-      </c>
-      <c r="K7" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L7" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="8" spans="1:12" ht="24.5" thickBot="1">
-      <c r="A8" s="58"/>
-      <c r="B8" s="34" t="s">
-        <v>223</v>
-      </c>
-      <c r="C8" s="34" t="s">
-        <v>224</v>
-      </c>
-      <c r="D8" s="34" t="s">
-        <v>225</v>
-      </c>
-      <c r="E8" s="35" t="s">
-        <v>226</v>
-      </c>
-      <c r="H8" s="44"/>
-      <c r="I8" s="4" t="s">
-        <v>12</v>
-      </c>
-      <c r="J8" s="4" t="s">
-        <v>23</v>
-      </c>
-      <c r="K8" s="4" t="s">
-        <v>13</v>
-      </c>
-      <c r="L8" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="9" spans="1:12" ht="24">
-      <c r="A9" s="50" t="s">
-        <v>6</v>
-      </c>
-      <c r="B9" s="36" t="s">
-        <v>227</v>
-      </c>
-      <c r="C9" s="36" t="s">
-        <v>228</v>
-      </c>
-      <c r="D9" s="37" t="s">
-        <v>229</v>
-      </c>
-      <c r="E9" s="31" t="s">
-        <v>230</v>
-      </c>
-      <c r="H9" s="44" t="s">
-        <v>6</v>
-      </c>
-      <c r="I9" s="2" t="s">
-        <v>112</v>
-      </c>
-      <c r="J9" s="2" t="s">
-        <v>118</v>
-      </c>
-      <c r="K9" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L9" s="2" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="10" spans="1:12" ht="24">
-      <c r="A10" s="51"/>
-      <c r="B10" s="38" t="s">
-        <v>116</v>
-      </c>
-      <c r="C10" s="38" t="s">
-        <v>231</v>
-      </c>
-      <c r="D10" s="39" t="s">
-        <v>232</v>
-      </c>
-      <c r="E10" s="33" t="s">
-        <v>233</v>
-      </c>
-      <c r="H10" s="44"/>
-      <c r="I10" s="3" t="s">
-        <v>113</v>
-      </c>
-      <c r="J10" s="3" t="s">
-        <v>119</v>
-      </c>
-      <c r="K10" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L10" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="11" spans="1:12" ht="24">
-      <c r="A11" s="51"/>
-      <c r="B11" s="38" t="s">
-        <v>117</v>
-      </c>
-      <c r="C11" s="38" t="s">
-        <v>234</v>
-      </c>
-      <c r="D11" s="39" t="s">
-        <v>221</v>
-      </c>
-      <c r="E11" s="33" t="s">
-        <v>235</v>
-      </c>
-      <c r="H11" s="44"/>
-      <c r="I11" s="3" t="s">
-        <v>114</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>120</v>
-      </c>
-      <c r="K11" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L11" s="3" t="s">
-        <v>126</v>
-      </c>
-    </row>
-    <row r="12" spans="1:12" ht="24">
-      <c r="A12" s="51"/>
-      <c r="B12" s="38" t="s">
-        <v>236</v>
-      </c>
-      <c r="C12" s="38" t="s">
-        <v>237</v>
-      </c>
-      <c r="D12" s="39" t="s">
-        <v>238</v>
-      </c>
-      <c r="E12" s="33" t="s">
-        <v>239</v>
-      </c>
-      <c r="H12" s="44"/>
-      <c r="I12" s="3" t="s">
-        <v>115</v>
-      </c>
-      <c r="J12" s="3" t="s">
-        <v>121</v>
-      </c>
-      <c r="K12" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L12" s="3" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="13" spans="1:12" ht="24">
-      <c r="A13" s="51"/>
-      <c r="B13" s="38" t="s">
-        <v>240</v>
-      </c>
-      <c r="C13" s="38" t="s">
-        <v>241</v>
-      </c>
-      <c r="D13" s="39" t="s">
-        <v>242</v>
-      </c>
-      <c r="E13" s="33" t="s">
-        <v>243</v>
-      </c>
-      <c r="H13" s="44"/>
-      <c r="I13" s="42" t="s">
-        <v>116</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>122</v>
-      </c>
-      <c r="K13" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L13" s="3" t="s">
-        <v>128</v>
-      </c>
-    </row>
-    <row r="14" spans="1:12" ht="47.5" thickBot="1">
-      <c r="A14" s="52"/>
-      <c r="B14" s="40" t="s">
-        <v>244</v>
-      </c>
-      <c r="C14" s="41" t="s">
-        <v>245</v>
-      </c>
-      <c r="D14" s="40" t="s">
-        <v>246</v>
-      </c>
-      <c r="E14" s="35" t="s">
-        <v>247</v>
-      </c>
-      <c r="H14" s="44"/>
-      <c r="I14" s="42" t="s">
-        <v>117</v>
-      </c>
-      <c r="J14" s="4" t="s">
-        <v>123</v>
-      </c>
-      <c r="K14" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L14" s="3" t="s">
-        <v>129</v>
-      </c>
-    </row>
-    <row r="15" spans="1:12" ht="24">
-      <c r="A15" s="50" t="s">
-        <v>248</v>
-      </c>
-      <c r="B15" s="36" t="s">
-        <v>249</v>
-      </c>
-      <c r="C15" s="36" t="s">
-        <v>250</v>
-      </c>
-      <c r="D15" s="37" t="s">
-        <v>251</v>
-      </c>
-      <c r="E15" s="31" t="s">
-        <v>252</v>
-      </c>
-      <c r="H15" s="44" t="s">
-        <v>7</v>
-      </c>
-      <c r="I15" s="2" t="s">
-        <v>63</v>
-      </c>
-      <c r="J15" s="2" t="s">
-        <v>70</v>
-      </c>
-      <c r="K15" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L15" s="2" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="16" spans="1:12" ht="24">
-      <c r="A16" s="51"/>
-      <c r="B16" s="38" t="s">
-        <v>253</v>
-      </c>
-      <c r="C16" s="38" t="s">
-        <v>254</v>
-      </c>
-      <c r="D16" s="39" t="s">
-        <v>255</v>
-      </c>
-      <c r="E16" s="33" t="s">
-        <v>256</v>
-      </c>
-      <c r="H16" s="44"/>
-      <c r="I16" s="3" t="s">
-        <v>64</v>
-      </c>
-      <c r="J16" s="3" t="s">
-        <v>71</v>
-      </c>
-      <c r="K16" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L16" s="3" t="s">
-        <v>156</v>
-      </c>
-    </row>
-    <row r="17" spans="1:12" ht="24">
-      <c r="A17" s="51"/>
-      <c r="B17" s="38" t="s">
-        <v>257</v>
-      </c>
-      <c r="C17" s="38" t="s">
-        <v>258</v>
-      </c>
-      <c r="D17" s="39" t="s">
-        <v>255</v>
-      </c>
-      <c r="E17" s="33" t="s">
-        <v>259</v>
-      </c>
-      <c r="H17" s="44"/>
-      <c r="I17" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="J17" s="3" t="s">
-        <v>72</v>
-      </c>
-      <c r="K17" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L17" s="3" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="18" spans="1:12" ht="24">
-      <c r="A18" s="51"/>
-      <c r="B18" s="38" t="s">
-        <v>260</v>
-      </c>
-      <c r="C18" s="38" t="s">
-        <v>261</v>
-      </c>
-      <c r="D18" s="39" t="s">
-        <v>262</v>
-      </c>
-      <c r="E18" s="33" t="s">
-        <v>256</v>
-      </c>
-      <c r="H18" s="44"/>
-      <c r="I18" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="J18" s="3" t="s">
-        <v>73</v>
-      </c>
-      <c r="K18" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L18" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="19" spans="1:12" ht="24">
-      <c r="A19" s="51"/>
-      <c r="B19" s="38" t="s">
-        <v>263</v>
-      </c>
-      <c r="C19" s="38" t="s">
-        <v>264</v>
-      </c>
-      <c r="D19" s="39" t="s">
-        <v>251</v>
-      </c>
-      <c r="E19" s="33" t="s">
-        <v>265</v>
-      </c>
-      <c r="H19" s="44"/>
-      <c r="I19" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="J19" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="K19" s="3" t="s">
-        <v>69</v>
-      </c>
-      <c r="L19" s="3" t="s">
-        <v>158</v>
-      </c>
-    </row>
-    <row r="20" spans="1:12" ht="24.5" thickBot="1">
-      <c r="A20" s="52"/>
-      <c r="B20" s="41" t="s">
-        <v>266</v>
-      </c>
-      <c r="C20" s="41" t="s">
-        <v>267</v>
-      </c>
-      <c r="D20" s="40" t="s">
-        <v>268</v>
-      </c>
-      <c r="E20" s="35" t="s">
-        <v>269</v>
-      </c>
-      <c r="H20" s="44"/>
-      <c r="I20" s="4" t="s">
-        <v>68</v>
-      </c>
-      <c r="J20" s="4" t="s">
-        <v>75</v>
-      </c>
-      <c r="K20" s="4" t="s">
-        <v>16</v>
-      </c>
-      <c r="L20" s="3" t="s">
-        <v>159</v>
-      </c>
-    </row>
-    <row r="21" spans="1:12" ht="23">
-      <c r="A21" s="50" t="s">
-        <v>270</v>
-      </c>
-      <c r="B21" s="37" t="s">
-        <v>271</v>
-      </c>
-      <c r="C21" s="37" t="s">
-        <v>147</v>
-      </c>
-      <c r="D21" s="37" t="s">
-        <v>16</v>
-      </c>
-      <c r="E21" s="31" t="s">
-        <v>272</v>
-      </c>
-      <c r="H21" s="44" t="s">
-        <v>8</v>
-      </c>
-      <c r="I21" s="42" t="s">
-        <v>146</v>
-      </c>
-      <c r="J21" s="2" t="s">
-        <v>147</v>
-      </c>
-      <c r="K21" s="2" t="s">
-        <v>16</v>
-      </c>
-      <c r="L21" s="2" t="s">
-        <v>148</v>
-      </c>
-    </row>
-    <row r="22" spans="1:12" ht="23">
-      <c r="A22" s="51"/>
-      <c r="B22" s="39" t="s">
-        <v>273</v>
-      </c>
-      <c r="C22" s="39" t="s">
-        <v>274</v>
-      </c>
-      <c r="D22" s="39" t="s">
-        <v>17</v>
-      </c>
-      <c r="E22" s="33" t="s">
-        <v>275</v>
-      </c>
-      <c r="H22" s="44"/>
-      <c r="I22" s="3" t="s">
-        <v>149</v>
-      </c>
-      <c r="J22" s="3" t="s">
-        <v>150</v>
-      </c>
-      <c r="K22" s="3" t="s">
-        <v>11</v>
-      </c>
-      <c r="L22" s="3" t="s">
-        <v>151</v>
-      </c>
-    </row>
-    <row r="23" spans="1:12" ht="23">
-      <c r="A23" s="51"/>
-      <c r="B23" s="39" t="s">
-        <v>276</v>
-      </c>
-      <c r="C23" s="39" t="s">
-        <v>277</v>
-      </c>
-      <c r="D23" s="39" t="s">
-        <v>14</v>
-      </c>
-      <c r="E23" s="33" t="s">
-        <v>278</v>
-      </c>
-      <c r="H23" s="44"/>
-      <c r="I23" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="J23" s="26" t="s">
-        <v>199</v>
-      </c>
-      <c r="K23" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L23" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="24" spans="1:12" ht="23">
-      <c r="A24" s="51"/>
-      <c r="B24" s="39" t="s">
-        <v>279</v>
-      </c>
-      <c r="C24" s="39" t="s">
-        <v>280</v>
-      </c>
-      <c r="D24" s="39" t="s">
-        <v>11</v>
-      </c>
-      <c r="E24" s="33" t="s">
-        <v>281</v>
-      </c>
-      <c r="H24" s="44"/>
-      <c r="I24" s="3" t="s">
-        <v>153</v>
-      </c>
-      <c r="J24" s="3" t="s">
-        <v>154</v>
-      </c>
-      <c r="K24" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L24" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="25" spans="1:12" ht="23">
-      <c r="A25" s="51"/>
-      <c r="B25" s="39" t="s">
-        <v>282</v>
-      </c>
-      <c r="C25" s="39" t="s">
-        <v>283</v>
-      </c>
-      <c r="D25" s="39" t="s">
-        <v>13</v>
-      </c>
-      <c r="E25" s="33" t="s">
-        <v>284</v>
-      </c>
-      <c r="H25" s="44"/>
-      <c r="I25" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="J25" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="K25" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L25" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="26" spans="1:12" ht="23.5" thickBot="1">
-      <c r="A26" s="52"/>
-      <c r="B26" s="40" t="s">
-        <v>285</v>
-      </c>
-      <c r="C26" s="40" t="s">
-        <v>286</v>
-      </c>
-      <c r="D26" s="40" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="35" t="s">
-        <v>287</v>
-      </c>
-      <c r="H26" s="44"/>
-      <c r="I26" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="J26" s="4" t="s">
-        <v>165</v>
-      </c>
-      <c r="K26" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="L26" s="4" t="s">
-        <v>166</v>
-      </c>
-    </row>
-    <row r="27" spans="1:12" ht="24">
-      <c r="A27" s="50" t="s">
-        <v>9</v>
-      </c>
-      <c r="B27" s="37" t="s">
-        <v>288</v>
-      </c>
-      <c r="C27" s="36" t="s">
-        <v>289</v>
-      </c>
-      <c r="D27" s="36" t="s">
-        <v>11</v>
-      </c>
-      <c r="E27" s="31" t="s">
-        <v>290</v>
-      </c>
-      <c r="H27" s="45" t="s">
-        <v>9</v>
-      </c>
-      <c r="I27" s="2" t="s">
-        <v>167</v>
-      </c>
-      <c r="J27" s="2" t="s">
-        <v>88</v>
-      </c>
-      <c r="K27" s="2" t="s">
-        <v>11</v>
-      </c>
-      <c r="L27" s="2" t="s">
-        <v>173</v>
-      </c>
-    </row>
-    <row r="28" spans="1:12" ht="24">
-      <c r="A28" s="51"/>
-      <c r="B28" s="39" t="s">
-        <v>291</v>
-      </c>
-      <c r="C28" s="38" t="s">
-        <v>292</v>
-      </c>
-      <c r="D28" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E28" s="33" t="s">
-        <v>293</v>
-      </c>
-      <c r="H28" s="46"/>
-      <c r="I28" s="3" t="s">
-        <v>168</v>
-      </c>
-      <c r="J28" s="3" t="s">
-        <v>89</v>
-      </c>
-      <c r="K28" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="L28" s="3" t="s">
-        <v>174</v>
-      </c>
-    </row>
-    <row r="29" spans="1:12" ht="24">
-      <c r="A29" s="51"/>
-      <c r="B29" s="39" t="s">
-        <v>294</v>
-      </c>
-      <c r="C29" s="38" t="s">
-        <v>295</v>
-      </c>
-      <c r="D29" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E29" s="33" t="s">
-        <v>296</v>
-      </c>
-      <c r="H29" s="46"/>
-      <c r="I29" s="3" t="s">
-        <v>169</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>90</v>
-      </c>
-      <c r="K29" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="L29" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="30" spans="1:12" ht="24">
-      <c r="A30" s="51"/>
-      <c r="B30" s="39" t="s">
-        <v>297</v>
-      </c>
-      <c r="C30" s="38" t="s">
-        <v>298</v>
-      </c>
-      <c r="D30" s="38" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" s="33" t="s">
-        <v>299</v>
-      </c>
-      <c r="H30" s="46"/>
-      <c r="I30" s="3" t="s">
-        <v>170</v>
-      </c>
-      <c r="J30" s="3" t="s">
-        <v>91</v>
-      </c>
-      <c r="K30" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="L30" s="3" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="31" spans="1:12" ht="24">
-      <c r="A31" s="51"/>
-      <c r="B31" s="39" t="s">
-        <v>300</v>
-      </c>
-      <c r="C31" s="38" t="s">
-        <v>301</v>
-      </c>
-      <c r="D31" s="38" t="s">
-        <v>69</v>
-      </c>
-      <c r="E31" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="H31" s="46"/>
-      <c r="I31" s="3" t="s">
-        <v>171</v>
-      </c>
-      <c r="J31" s="3" t="s">
-        <v>92</v>
-      </c>
-      <c r="K31" s="3" t="s">
-        <v>16</v>
-      </c>
-      <c r="L31" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="32" spans="1:12" ht="24.5" thickBot="1">
-      <c r="A32" s="52"/>
-      <c r="B32" s="40" t="s">
-        <v>303</v>
-      </c>
-      <c r="C32" s="41" t="s">
-        <v>304</v>
-      </c>
-      <c r="D32" s="41" t="s">
-        <v>16</v>
-      </c>
-      <c r="E32" s="35" t="s">
-        <v>305</v>
-      </c>
-      <c r="H32" s="43"/>
-      <c r="I32" s="4" t="s">
-        <v>172</v>
-      </c>
-      <c r="J32" s="4" t="s">
-        <v>93</v>
-      </c>
-      <c r="K32" s="4" t="s">
-        <v>17</v>
-      </c>
-      <c r="L32" s="4" t="s">
-        <v>178</v>
-      </c>
-    </row>
-    <row r="33" spans="1:5" ht="24">
-      <c r="A33" s="50" t="s">
-        <v>306</v>
-      </c>
-      <c r="B33" s="36" t="s">
-        <v>307</v>
-      </c>
-      <c r="C33" s="36" t="s">
-        <v>308</v>
-      </c>
-      <c r="D33" s="36" t="s">
-        <v>15</v>
-      </c>
-      <c r="E33" s="31"/>
-    </row>
-    <row r="34" spans="1:5" ht="24">
-      <c r="A34" s="51"/>
-      <c r="B34" s="38" t="s">
-        <v>309</v>
-      </c>
-      <c r="C34" s="38" t="s">
-        <v>310</v>
-      </c>
-      <c r="D34" s="38" t="s">
-        <v>13</v>
-      </c>
-      <c r="E34" s="33"/>
-    </row>
-    <row r="35" spans="1:5" ht="35.5">
-      <c r="A35" s="51"/>
-      <c r="B35" s="38" t="s">
-        <v>311</v>
-      </c>
-      <c r="C35" s="38" t="s">
-        <v>312</v>
-      </c>
-      <c r="D35" s="38" t="s">
-        <v>11</v>
-      </c>
-      <c r="E35" s="33"/>
-    </row>
-    <row r="36" spans="1:5" ht="35.5">
-      <c r="A36" s="51"/>
-      <c r="B36" s="38" t="s">
-        <v>313</v>
-      </c>
-      <c r="C36" s="38" t="s">
-        <v>314</v>
-      </c>
-      <c r="D36" s="38" t="s">
-        <v>16</v>
-      </c>
-      <c r="E36" s="33"/>
-    </row>
-    <row r="37" spans="1:5" ht="24">
-      <c r="A37" s="51"/>
-      <c r="B37" s="38" t="s">
-        <v>315</v>
-      </c>
-      <c r="C37" s="38" t="s">
-        <v>316</v>
-      </c>
-      <c r="D37" s="38" t="s">
-        <v>14</v>
-      </c>
-      <c r="E37" s="33"/>
-    </row>
-    <row r="38" spans="1:5" ht="24.5" thickBot="1">
-      <c r="A38" s="52"/>
-      <c r="B38" s="41" t="s">
-        <v>317</v>
-      </c>
-      <c r="C38" s="41" t="s">
-        <v>318</v>
-      </c>
-      <c r="D38" s="41" t="s">
-        <v>69</v>
-      </c>
-      <c r="E38" s="35"/>
-    </row>
-  </sheetData>
-  <autoFilter ref="A2:E38"/>
-  <mergeCells count="13">
-    <mergeCell ref="H1:L1"/>
-    <mergeCell ref="A33:A38"/>
-    <mergeCell ref="H3:H8"/>
-    <mergeCell ref="H9:H14"/>
-    <mergeCell ref="H15:H20"/>
-    <mergeCell ref="H21:H26"/>
-    <mergeCell ref="H27:H32"/>
-    <mergeCell ref="A1:E1"/>
-    <mergeCell ref="A3:A8"/>
-    <mergeCell ref="A9:A14"/>
-    <mergeCell ref="A15:A20"/>
-    <mergeCell ref="A21:A26"/>
-    <mergeCell ref="A27:A32"/>
-  </mergeCells>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:G21"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="23.26953125" customWidth="1"/>
     <col min="3" max="3" width="28" customWidth="1"/>
@@ -4061,7 +2342,7 @@
     <col min="5" max="5" width="20.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -4084,11 +2365,11 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:7">
-      <c r="A2" s="45" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A2" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="59" t="s">
+      <c r="B2" s="28" t="s">
         <v>48</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -4107,9 +2388,9 @@
         <v>777410048</v>
       </c>
     </row>
-    <row r="3" spans="1:7">
-      <c r="A3" s="46"/>
-      <c r="B3" s="60"/>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A3" s="27"/>
+      <c r="B3" s="29"/>
       <c r="C3" s="3" t="s">
         <v>52</v>
       </c>
@@ -4126,9 +2407,9 @@
         <v>787656877</v>
       </c>
     </row>
-    <row r="4" spans="1:7">
-      <c r="A4" s="46"/>
-      <c r="B4" s="60"/>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A4" s="27"/>
+      <c r="B4" s="29"/>
       <c r="C4" s="3" t="s">
         <v>53</v>
       </c>
@@ -4145,9 +2426,9 @@
         <v>776019823</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
-      <c r="A5" s="43"/>
-      <c r="B5" s="61"/>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A5" s="24"/>
+      <c r="B5" s="30"/>
       <c r="C5" s="3" t="s">
         <v>55</v>
       </c>
@@ -4164,11 +2445,11 @@
         <v>782981141</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
-      <c r="A6" s="44" t="s">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A6" s="25" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="59" t="s">
+      <c r="B6" s="28" t="s">
         <v>131</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -4187,9 +2468,9 @@
         <v>788255458</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
-      <c r="A7" s="44"/>
-      <c r="B7" s="60" t="s">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A7" s="25"/>
+      <c r="B7" s="29" t="s">
         <v>131</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -4208,9 +2489,9 @@
         <v>789166919</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
-      <c r="A8" s="44"/>
-      <c r="B8" s="60"/>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A8" s="25"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="3" t="s">
         <v>138</v>
       </c>
@@ -4227,9 +2508,9 @@
         <v>789151415</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
-      <c r="A9" s="44"/>
-      <c r="B9" s="61"/>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A9" s="25"/>
+      <c r="B9" s="30"/>
       <c r="C9" s="3" t="s">
         <v>196</v>
       </c>
@@ -4239,18 +2520,18 @@
       <c r="E9" s="3" t="s">
         <v>198</v>
       </c>
-      <c r="F9" s="25">
+      <c r="F9" s="22">
         <v>778113461</v>
       </c>
       <c r="G9" s="3">
         <v>789166945</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
-      <c r="A10" s="44" t="s">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A10" s="25" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="59" t="s">
+      <c r="B10" s="28" t="s">
         <v>132</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -4269,9 +2550,9 @@
         <v>781180310</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
-      <c r="A11" s="44"/>
-      <c r="B11" s="60"/>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A11" s="25"/>
+      <c r="B11" s="29"/>
       <c r="C11" s="3" t="s">
         <v>79</v>
       </c>
@@ -4288,9 +2569,9 @@
         <v>781180552</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
-      <c r="A12" s="44"/>
-      <c r="B12" s="60"/>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A12" s="25"/>
+      <c r="B12" s="29"/>
       <c r="C12" s="3" t="s">
         <v>81</v>
       </c>
@@ -4307,9 +2588,9 @@
         <v>787080588</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
-      <c r="A13" s="44"/>
-      <c r="B13" s="61"/>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A13" s="25"/>
+      <c r="B13" s="30"/>
       <c r="C13" s="3" t="s">
         <v>82</v>
       </c>
@@ -4326,11 +2607,11 @@
         <v>789150567</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
-      <c r="A14" s="44" t="s">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A14" s="25" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="59" t="s">
+      <c r="B14" s="28" t="s">
         <v>179</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -4349,9 +2630,9 @@
         <v>771545210</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
-      <c r="A15" s="44"/>
-      <c r="B15" s="60" t="s">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A15" s="25"/>
+      <c r="B15" s="29" t="s">
         <v>131</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -4370,9 +2651,9 @@
         <v>773958904</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
-      <c r="A16" s="44"/>
-      <c r="B16" s="60"/>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A16" s="25"/>
+      <c r="B16" s="29"/>
       <c r="C16" s="3" t="s">
         <v>183</v>
       </c>
@@ -4389,9 +2670,9 @@
         <v>776950987</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
-      <c r="A17" s="44"/>
-      <c r="B17" s="61"/>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A17" s="25"/>
+      <c r="B17" s="30"/>
       <c r="C17" s="4" t="s">
         <v>185</v>
       </c>
@@ -4408,11 +2689,11 @@
         <v>781825193</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
-      <c r="A18" s="46" t="s">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A18" s="27" t="s">
         <v>94</v>
       </c>
-      <c r="B18" s="59" t="s">
+      <c r="B18" s="28" t="s">
         <v>107</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -4431,9 +2712,9 @@
         <v>786180521</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
-      <c r="A19" s="46"/>
-      <c r="B19" s="60"/>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A19" s="27"/>
+      <c r="B19" s="29"/>
       <c r="C19" s="3" t="s">
         <v>95</v>
       </c>
@@ -4450,9 +2731,9 @@
         <v>786183517</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
-      <c r="A20" s="46"/>
-      <c r="B20" s="60"/>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A20" s="27"/>
+      <c r="B20" s="29"/>
       <c r="C20" s="3" t="s">
         <v>99</v>
       </c>
@@ -4469,9 +2750,9 @@
         <v>772118585</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
-      <c r="A21" s="43"/>
-      <c r="B21" s="61"/>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="A21" s="24"/>
+      <c r="B21" s="30"/>
       <c r="C21" s="4" t="s">
         <v>102</v>
       </c>
@@ -4490,286 +2771,287 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="B10:B13"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D22"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="22.36328125" customWidth="1"/>
     <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1"/>
-    <row r="2" spans="1:4" ht="15" thickBot="1">
-      <c r="A2" s="13"/>
-      <c r="B2" s="7"/>
-      <c r="C2" s="11"/>
-      <c r="D2" s="17" t="s">
+    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="34"/>
+      <c r="B2" s="35"/>
+      <c r="C2" s="36"/>
+      <c r="D2" s="14" t="s">
         <v>57</v>
       </c>
     </row>
-    <row r="3" spans="1:4">
-      <c r="A3" s="62" t="s">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A3" s="31" t="s">
         <v>62</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="7" t="s">
         <v>31</v>
       </c>
-      <c r="C3" s="10" t="s">
+      <c r="C3" s="9" t="s">
         <v>58</v>
       </c>
-      <c r="D3" s="19">
+      <c r="D3" s="16">
         <v>776382705</v>
       </c>
     </row>
-    <row r="4" spans="1:4">
-      <c r="A4" s="62"/>
-      <c r="B4" s="8" t="s">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A4" s="31"/>
+      <c r="B4" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C4" s="14" t="s">
+      <c r="C4" s="11" t="s">
         <v>59</v>
       </c>
-      <c r="D4" s="18">
+      <c r="D4" s="15">
         <v>777401785</v>
       </c>
     </row>
-    <row r="5" spans="1:4">
-      <c r="A5" s="62"/>
-      <c r="B5" s="8" t="s">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A5" s="31"/>
+      <c r="B5" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C5" s="14" t="s">
+      <c r="C5" s="11" t="s">
         <v>60</v>
       </c>
-      <c r="D5" s="18">
+      <c r="D5" s="15">
         <v>772579898</v>
       </c>
     </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1">
-      <c r="A6" s="63"/>
-      <c r="B6" s="9" t="s">
+    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="32"/>
+      <c r="B6" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C6" s="12" t="s">
+      <c r="C6" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="D6" s="20">
+      <c r="D6" s="17">
         <v>781816827</v>
       </c>
     </row>
-    <row r="7" spans="1:4">
-      <c r="A7" s="62" t="s">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A7" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B7" s="16" t="s">
+      <c r="B7" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C7" s="15" t="s">
+      <c r="C7" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="D7" s="19">
+      <c r="D7" s="16">
         <v>778196895</v>
       </c>
     </row>
-    <row r="8" spans="1:4">
-      <c r="A8" s="62"/>
-      <c r="B8" s="8" t="s">
+    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A8" s="31"/>
+      <c r="B8" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C8" s="14" t="s">
+      <c r="C8" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="D8" s="18">
+      <c r="D8" s="15">
         <v>776372229</v>
       </c>
     </row>
-    <row r="9" spans="1:4">
-      <c r="A9" s="62"/>
-      <c r="B9" s="8" t="s">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A9" s="31"/>
+      <c r="B9" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C9" s="14" t="s">
+      <c r="C9" s="11" t="s">
         <v>36</v>
       </c>
-      <c r="D9" s="18">
+      <c r="D9" s="15">
         <v>776665352</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1">
-      <c r="A10" s="62"/>
-      <c r="B10" s="9" t="s">
+    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A10" s="31"/>
+      <c r="B10" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="12" t="s">
+      <c r="C10" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="D10" s="20">
+      <c r="D10" s="17">
         <v>783441820</v>
       </c>
     </row>
-    <row r="11" spans="1:4">
-      <c r="A11" s="64" t="s">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A11" s="33" t="s">
         <v>94</v>
       </c>
-      <c r="B11" s="16" t="s">
+      <c r="B11" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C11" s="15" t="s">
+      <c r="C11" s="12" t="s">
         <v>108</v>
       </c>
-      <c r="D11" s="21"/>
-    </row>
-    <row r="12" spans="1:4">
-      <c r="A12" s="62"/>
-      <c r="B12" s="8" t="s">
+      <c r="D11" s="18"/>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A12" s="31"/>
+      <c r="B12" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C12" s="14" t="s">
+      <c r="C12" s="11" t="s">
         <v>109</v>
       </c>
-      <c r="D12" s="22"/>
-    </row>
-    <row r="13" spans="1:4">
-      <c r="A13" s="62"/>
-      <c r="B13" s="8" t="s">
+      <c r="D12" s="19"/>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A13" s="31"/>
+      <c r="B13" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C13" s="14" t="s">
+      <c r="C13" s="11" t="s">
         <v>110</v>
       </c>
-      <c r="D13" s="22"/>
-    </row>
-    <row r="14" spans="1:4" ht="15" thickBot="1">
-      <c r="A14" s="63"/>
-      <c r="B14" s="9" t="s">
+      <c r="D13" s="19"/>
+    </row>
+    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A14" s="32"/>
+      <c r="B14" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C14" s="12" t="s">
+      <c r="C14" s="10" t="s">
         <v>111</v>
       </c>
-      <c r="D14" s="20">
+      <c r="D14" s="17">
         <v>782402937</v>
       </c>
     </row>
-    <row r="15" spans="1:4">
-      <c r="A15" s="62" t="s">
+    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A15" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="B15" s="16" t="s">
+      <c r="B15" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C15" s="15" t="s">
+      <c r="C15" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="D15" s="15">
+      <c r="D15" s="12">
         <v>775699621</v>
       </c>
     </row>
-    <row r="16" spans="1:4">
-      <c r="A16" s="62"/>
-      <c r="B16" s="8" t="s">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A16" s="31"/>
+      <c r="B16" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C16" s="14" t="s">
+      <c r="C16" s="11" t="s">
         <v>144</v>
       </c>
-      <c r="D16" s="14">
+      <c r="D16" s="11">
         <v>776440917</v>
       </c>
     </row>
-    <row r="17" spans="1:4">
-      <c r="A17" s="62"/>
-      <c r="B17" s="8" t="s">
+    <row r="17" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A17" s="31"/>
+      <c r="B17" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C17" s="14" t="s">
+      <c r="C17" s="11" t="s">
         <v>130</v>
       </c>
-      <c r="D17" s="14">
+      <c r="D17" s="11">
         <v>781287163</v>
       </c>
     </row>
-    <row r="18" spans="1:4" ht="15" thickBot="1">
-      <c r="A18" s="63"/>
-      <c r="B18" s="9" t="s">
+    <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A18" s="32"/>
+      <c r="B18" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C18" s="12" t="s">
+      <c r="C18" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="D18" s="12">
+      <c r="D18" s="10">
         <v>782352114</v>
       </c>
     </row>
-    <row r="19" spans="1:4">
-      <c r="A19" s="62" t="s">
+    <row r="19" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A19" s="31" t="s">
         <v>191</v>
       </c>
-      <c r="B19" s="16" t="s">
+      <c r="B19" s="13" t="s">
         <v>31</v>
       </c>
-      <c r="C19" s="15" t="s">
+      <c r="C19" s="12" t="s">
         <v>192</v>
       </c>
-      <c r="D19" s="15">
+      <c r="D19" s="12">
         <v>773335050</v>
       </c>
     </row>
-    <row r="20" spans="1:4">
-      <c r="A20" s="62"/>
-      <c r="B20" s="8" t="s">
+    <row r="20" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A20" s="31"/>
+      <c r="B20" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="C20" s="14" t="s">
+      <c r="C20" s="11" t="s">
         <v>193</v>
       </c>
-      <c r="D20" s="14">
+      <c r="D20" s="11">
         <v>776441287</v>
       </c>
     </row>
-    <row r="21" spans="1:4">
-      <c r="A21" s="62"/>
-      <c r="B21" s="8" t="s">
+    <row r="21" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="A21" s="31"/>
+      <c r="B21" s="7" t="s">
         <v>35</v>
       </c>
-      <c r="C21" s="14" t="s">
+      <c r="C21" s="11" t="s">
         <v>194</v>
       </c>
-      <c r="D21" s="14">
+      <c r="D21" s="11">
         <v>775451818</v>
       </c>
     </row>
-    <row r="22" spans="1:4" ht="15" thickBot="1">
-      <c r="A22" s="63"/>
-      <c r="B22" s="9" t="s">
+    <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A22" s="32"/>
+      <c r="B22" s="8" t="s">
         <v>37</v>
       </c>
-      <c r="C22" s="23" t="s">
+      <c r="C22" s="20" t="s">
         <v>195</v>
       </c>
-      <c r="D22" s="24">
+      <c r="D22" s="21">
         <v>775277993</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="5">
+  <mergeCells count="6">
+    <mergeCell ref="A2:C2"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="A7:A10"/>
     <mergeCell ref="A11:A14"/>

--- a/LOUMA phase2.xlsx
+++ b/LOUMA phase2.xlsx
@@ -292,9 +292,6 @@
     <t>pvt_sfof0211</t>
   </si>
   <si>
-    <t>pvt_sfof0304</t>
-  </si>
-  <si>
     <t>14.4197869,-16.7078861</t>
   </si>
   <si>
@@ -621,16 +618,19 @@
     <t>BACARY KAMBY</t>
   </si>
   <si>
-    <t xml:space="preserve">OUSMANE </t>
-  </si>
-  <si>
-    <t>DIAGNE</t>
-  </si>
-  <si>
-    <t>Pvt_tdc590060</t>
-  </si>
-  <si>
     <t>12°30’03.9’’N    15°43’15.4’’W</t>
+  </si>
+  <si>
+    <t>BILALY</t>
+  </si>
+  <si>
+    <t>Pvt_tdc590016</t>
+  </si>
+  <si>
+    <t>BASSOUM</t>
+  </si>
+  <si>
+    <t>pvt_sfof0228</t>
   </si>
 </sst>
 </file>
@@ -780,6 +780,7 @@
     </font>
     <font>
       <sz val="11"/>
+      <color theme="9"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -978,7 +979,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="29">
+  <borders count="30">
     <border>
       <left/>
       <right/>
@@ -1340,6 +1341,21 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1416,8 +1432,8 @@
     <xf numFmtId="0" fontId="18" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1445,9 +1461,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="16" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="33" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1456,6 +1469,9 @@
     </xf>
     <xf numFmtId="0" fontId="1" fillId="33" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="42">
@@ -1948,95 +1964,95 @@
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A9" s="25"/>
       <c r="B9" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G9" s="2"/>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A10" s="25"/>
       <c r="B10" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G10" s="3"/>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A11" s="25"/>
       <c r="B11" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="G11" s="3"/>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A12" s="25"/>
       <c r="B12" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="D12" s="3" t="s">
         <v>69</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="G12" s="3"/>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A13" s="25"/>
       <c r="B13" s="4" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="G13" s="3"/>
     </row>
@@ -2054,7 +2070,7 @@
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="G14" s="3"/>
     </row>
@@ -2070,7 +2086,7 @@
         <v>13</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.35">
@@ -2085,7 +2101,7 @@
         <v>14</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
@@ -2100,7 +2116,7 @@
         <v>15</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
@@ -2115,7 +2131,7 @@
         <v>69</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
@@ -2130,7 +2146,7 @@
         <v>16</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -2138,40 +2154,40 @@
         <v>8</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>147</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="25"/>
       <c r="B21" s="3" t="s">
+        <v>148</v>
+      </c>
+      <c r="C21" s="3" t="s">
         <v>149</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>150</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="25"/>
       <c r="B22" s="3" t="s">
-        <v>152</v>
-      </c>
-      <c r="C22" s="23" t="s">
-        <v>199</v>
+        <v>151</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>195</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>13</v>
@@ -2183,46 +2199,46 @@
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="25"/>
       <c r="B23" s="3" t="s">
+        <v>152</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>153</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>154</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="25"/>
       <c r="B24" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="C24" s="3" t="s">
         <v>161</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>162</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="25"/>
       <c r="B25" s="4" t="s">
+        <v>163</v>
+      </c>
+      <c r="C25" s="4" t="s">
         <v>164</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>165</v>
       </c>
       <c r="D25" s="4" t="s">
         <v>69</v>
       </c>
       <c r="E25" s="4" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -2230,91 +2246,91 @@
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="27"/>
       <c r="B27" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="27"/>
       <c r="B28" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="27"/>
       <c r="B29" s="3" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="27"/>
       <c r="B30" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="24"/>
       <c r="B31" s="4" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
     </row>
   </sheetData>
@@ -2333,7 +2349,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G21"/>
+  <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="23.26953125" customWidth="1"/>
@@ -2342,7 +2358,7 @@
     <col min="5" max="5" width="20.36328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -2365,7 +2381,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A2" s="26" t="s">
         <v>5</v>
       </c>
@@ -2388,7 +2404,7 @@
         <v>777410048</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A3" s="27"/>
       <c r="B3" s="29"/>
       <c r="C3" s="3" t="s">
@@ -2407,7 +2423,7 @@
         <v>787656877</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A4" s="27"/>
       <c r="B4" s="29"/>
       <c r="C4" s="3" t="s">
@@ -2426,7 +2442,7 @@
         <v>776019823</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A5" s="24"/>
       <c r="B5" s="30"/>
       <c r="C5" s="3" t="s">
@@ -2445,21 +2461,21 @@
         <v>782981141</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A6" s="25" t="s">
         <v>6</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>136</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F6" s="2">
         <v>777147559</v>
@@ -2468,19 +2484,19 @@
         <v>788255458</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="25"/>
       <c r="B7" s="29" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="F7" s="3">
         <v>777951348</v>
@@ -2489,17 +2505,17 @@
         <v>789166919</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A8" s="25"/>
       <c r="B8" s="29"/>
       <c r="C8" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="F8" s="3">
         <v>782190772</v>
@@ -2508,31 +2524,31 @@
         <v>789151415</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A9" s="25"/>
       <c r="B9" s="30"/>
       <c r="C9" s="3" t="s">
         <v>196</v>
       </c>
       <c r="D9" s="4" t="s">
+        <v>198</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>197</v>
       </c>
-      <c r="E9" s="3" t="s">
-        <v>198</v>
-      </c>
-      <c r="F9" s="22">
-        <v>778113461</v>
+      <c r="F9" s="3">
+        <v>789111270</v>
       </c>
       <c r="G9" s="3">
-        <v>789166945</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+        <v>789166998</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A10" s="25" t="s">
         <v>7</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="C10" s="2" t="s">
         <v>78</v>
@@ -2550,7 +2566,7 @@
         <v>781180310</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A11" s="25"/>
       <c r="B11" s="29"/>
       <c r="C11" s="3" t="s">
@@ -2569,7 +2585,7 @@
         <v>781180552</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A12" s="25"/>
       <c r="B12" s="29"/>
       <c r="C12" s="3" t="s">
@@ -2588,7 +2604,7 @@
         <v>787080588</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A13" s="25"/>
       <c r="B13" s="30"/>
       <c r="C13" s="3" t="s">
@@ -2598,30 +2614,31 @@
         <v>83</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>87</v>
+        <v>199</v>
       </c>
       <c r="F13" s="3">
-        <v>783905048</v>
+        <v>788780692</v>
       </c>
       <c r="G13" s="3">
-        <v>789150567</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+        <v>789150406</v>
+      </c>
+      <c r="J13" s="23"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
         <v>8</v>
       </c>
       <c r="B14" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>179</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>180</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F14" s="2">
         <v>777509848</v>
@@ -2630,19 +2647,19 @@
         <v>771545210</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="25"/>
       <c r="B15" s="29" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>182</v>
-      </c>
       <c r="E15" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F15" s="3">
         <v>776919692</v>
@@ -2651,17 +2668,17 @@
         <v>773958904</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A16" s="25"/>
       <c r="B16" s="29"/>
       <c r="C16" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>184</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F16" s="3">
         <v>783008307</v>
@@ -2674,13 +2691,13 @@
       <c r="A17" s="25"/>
       <c r="B17" s="30"/>
       <c r="C17" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>185</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>186</v>
-      </c>
       <c r="E17" s="4" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F17" s="4">
         <v>780123961</v>
@@ -2691,19 +2708,19 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="27" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="B18" s="28" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="E18" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F18" s="3">
         <v>778679190</v>
@@ -2716,13 +2733,13 @@
       <c r="A19" s="27"/>
       <c r="B19" s="29"/>
       <c r="C19" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F19" s="3">
         <v>771994713</v>
@@ -2735,13 +2752,13 @@
       <c r="A20" s="27"/>
       <c r="B20" s="29"/>
       <c r="C20" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="E20" s="3" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F20" s="3">
         <v>784119644</v>
@@ -2754,13 +2771,13 @@
       <c r="A21" s="24"/>
       <c r="B21" s="30"/>
       <c r="C21" s="4" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F21" s="4">
         <v>787389275</v>
@@ -2798,9 +2815,9 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="34"/>
-      <c r="B2" s="35"/>
-      <c r="C2" s="36"/>
+      <c r="A2" s="33"/>
+      <c r="B2" s="34"/>
+      <c r="C2" s="35"/>
       <c r="D2" s="14" t="s">
         <v>57</v>
       </c>
@@ -2906,14 +2923,14 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="33" t="s">
-        <v>94</v>
+      <c r="A11" s="36" t="s">
+        <v>93</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>31</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D11" s="18"/>
     </row>
@@ -2923,7 +2940,7 @@
         <v>33</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D12" s="19"/>
     </row>
@@ -2933,7 +2950,7 @@
         <v>35</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="D13" s="19"/>
     </row>
@@ -2943,7 +2960,7 @@
         <v>37</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="D14" s="17">
         <v>782402937</v>
@@ -2951,13 +2968,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="31" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>31</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="D15" s="12">
         <v>775699621</v>
@@ -2969,7 +2986,7 @@
         <v>33</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="D16" s="11">
         <v>776440917</v>
@@ -2981,7 +2998,7 @@
         <v>35</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="D17" s="11">
         <v>781287163</v>
@@ -2993,7 +3010,7 @@
         <v>37</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="D18" s="10">
         <v>782352114</v>
@@ -3001,13 +3018,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="31" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>31</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D19" s="12">
         <v>773335050</v>
@@ -3019,7 +3036,7 @@
         <v>33</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D20" s="11">
         <v>776441287</v>
@@ -3031,7 +3048,7 @@
         <v>35</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D21" s="11">
         <v>775451818</v>
@@ -3043,7 +3060,7 @@
         <v>37</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D22" s="21">
         <v>775277993</v>
@@ -3051,12 +3068,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A19:A22"/>
     <mergeCell ref="A2:C2"/>
     <mergeCell ref="A3:A6"/>
     <mergeCell ref="A7:A10"/>
     <mergeCell ref="A11:A14"/>
     <mergeCell ref="A15:A18"/>
-    <mergeCell ref="A19:A22"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>

--- a/LOUMA phase2.xlsx
+++ b/LOUMA phase2.xlsx
@@ -591,9 +591,6 @@
     <t>MANE</t>
   </si>
   <si>
-    <t>pvt_zigtel _ravt _zigt068</t>
-  </si>
-  <si>
     <t>pvt_zigtel0351</t>
   </si>
   <si>
@@ -631,6 +628,9 @@
   </si>
   <si>
     <t>pvt_sfof0228</t>
+  </si>
+  <si>
+    <t>pvt_zigtel_ravt_zig068</t>
   </si>
 </sst>
 </file>
@@ -2187,7 +2187,7 @@
         <v>151</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>13</v>
@@ -2528,13 +2528,13 @@
       <c r="A9" s="25"/>
       <c r="B9" s="30"/>
       <c r="C9" s="3" t="s">
+        <v>195</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>197</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>196</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>198</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>197</v>
       </c>
       <c r="F9" s="3">
         <v>789111270</v>
@@ -2614,7 +2614,7 @@
         <v>83</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F13" s="3">
         <v>788780692</v>
@@ -2638,7 +2638,7 @@
         <v>135</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>186</v>
+        <v>199</v>
       </c>
       <c r="F14" s="2">
         <v>777509848</v>
@@ -2659,7 +2659,7 @@
         <v>181</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F15" s="3">
         <v>776919692</v>
@@ -2678,7 +2678,7 @@
         <v>183</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F16" s="3">
         <v>783008307</v>
@@ -2697,7 +2697,7 @@
         <v>185</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F17" s="4">
         <v>780123961</v>
@@ -2788,16 +2788,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:B13"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="B14:B17"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3018,13 +3018,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="31" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>31</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D19" s="12">
         <v>773335050</v>
@@ -3036,7 +3036,7 @@
         <v>33</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D20" s="11">
         <v>776441287</v>
@@ -3048,7 +3048,7 @@
         <v>35</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="D21" s="11">
         <v>775451818</v>
@@ -3060,7 +3060,7 @@
         <v>37</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="D22" s="21">
         <v>775277993</v>

--- a/LOUMA phase2.xlsx
+++ b/LOUMA phase2.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050"/>
   </bookViews>
   <sheets>
     <sheet name="Liste LOUMAS" sheetId="1" r:id="rId1"/>
@@ -2788,16 +2788,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="B10:B13"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/LOUMA phase2.xlsx
+++ b/LOUMA phase2.xlsx
@@ -29,7 +29,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="255" uniqueCount="200">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="199">
   <si>
     <t>DRV</t>
   </si>
@@ -94,9 +94,6 @@
     <t>DIAMAGADIO</t>
   </si>
   <si>
-    <t>BIRKILANE</t>
-  </si>
-  <si>
     <t>14.27622°N; 14.93132°O</t>
   </si>
   <si>
@@ -110,9 +107,6 @@
   </si>
   <si>
     <t>13,78641°N; 15,42236°O</t>
-  </si>
-  <si>
-    <t>14.12678°N; 15.73993°O</t>
   </si>
   <si>
     <t>77km</t>
@@ -631,6 +625,9 @@
   </si>
   <si>
     <t>pvt_zigtel_ravt_zig068</t>
+  </si>
+  <si>
+    <t>NDIOTÉ SÉANE</t>
   </si>
 </sst>
 </file>
@@ -979,7 +976,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="30">
+  <borders count="31">
     <border>
       <left/>
       <right/>
@@ -1356,6 +1353,15 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="42">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
@@ -1401,7 +1407,7 @@
     <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="37">
+  <cellXfs count="39">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1473,6 +1479,8 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Accent1" xfId="18" builtinId="30" customBuiltin="1"/>
@@ -1841,7 +1849,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:G31"/>
+  <dimension ref="A1:H31"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="2" max="2" width="21.81640625" customWidth="1"/>
@@ -1850,7 +1858,7 @@
     <col min="5" max="5" width="18" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1867,7 +1875,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A2" s="24" t="s">
         <v>5</v>
       </c>
@@ -1875,278 +1883,284 @@
         <v>19</v>
       </c>
       <c r="C2" s="2" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="D2" s="2" t="s">
         <v>15</v>
       </c>
       <c r="E2" s="2" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A3" s="25"/>
       <c r="B3" s="3" t="s">
         <v>20</v>
       </c>
       <c r="C3" s="3" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="D3" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A4" s="25"/>
       <c r="B4" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="C4" s="3" t="s">
-        <v>27</v>
-      </c>
+        <v>198</v>
+      </c>
+      <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
-        <v>17</v>
-      </c>
-      <c r="E4" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.35">
+        <v>67</v>
+      </c>
+      <c r="E4" s="3"/>
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A5" s="25"/>
       <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
       <c r="C5" s="3" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="D5" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.35">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A6" s="25"/>
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
       <c r="C6" s="3" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="D6" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E6" s="3" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.35">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A7" s="25"/>
       <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="D7" s="4" t="s">
         <v>13</v>
       </c>
       <c r="E7" s="4" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.35">
+        <v>27</v>
+      </c>
+      <c r="G7" s="37"/>
+      <c r="H7" s="37"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A8" s="25" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.35">
+        <v>121</v>
+      </c>
+      <c r="G8" s="37"/>
+      <c r="H8" s="37"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A9" s="25"/>
       <c r="B9" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H9" s="37"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A10" s="25"/>
       <c r="B10" s="3" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>125</v>
+        <v>123</v>
       </c>
       <c r="G10" s="3"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H10" s="37"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A11" s="25"/>
       <c r="B11" s="3" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="G11" s="3"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H11" s="37"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A12" s="25"/>
       <c r="B12" s="3" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>69</v>
+        <v>67</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="G12" s="3"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H12" s="37"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A13" s="25"/>
       <c r="B13" s="4" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="G13" s="3"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.35">
+      <c r="H13" s="37"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A14" s="25" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>63</v>
+        <v>61</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>70</v>
+        <v>68</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>154</v>
-      </c>
-      <c r="G14" s="3"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.35">
+        <v>152</v>
+      </c>
+      <c r="G14" s="4"/>
+      <c r="H14" s="38"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A15" s="25"/>
       <c r="B15" s="3" t="s">
-        <v>64</v>
+        <v>62</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.35">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.35">
       <c r="A16" s="25"/>
       <c r="B16" s="3" t="s">
-        <v>65</v>
+        <v>63</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A17" s="25"/>
       <c r="B17" s="3" t="s">
-        <v>66</v>
+        <v>64</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>73</v>
+        <v>71</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A18" s="25"/>
       <c r="B18" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="C18" s="3" t="s">
-        <v>74</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="E18" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A19" s="25"/>
       <c r="B19" s="4" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C19" s="4" t="s">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
@@ -2154,91 +2168,91 @@
         <v>8</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="2" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A21" s="25"/>
       <c r="B21" s="3" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="C21" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A22" s="25"/>
       <c r="B22" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C22" s="22" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>28</v>
+        <v>26</v>
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A23" s="25"/>
       <c r="B23" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C23" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A24" s="25"/>
       <c r="B24" s="3" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="C24" s="3" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A25" s="25"/>
       <c r="B25" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>163</v>
-      </c>
-      <c r="C25" s="4" t="s">
-        <v>164</v>
-      </c>
-      <c r="D25" s="4" t="s">
-        <v>69</v>
-      </c>
-      <c r="E25" s="4" t="s">
-        <v>165</v>
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
@@ -2246,91 +2260,91 @@
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A27" s="27"/>
       <c r="B27" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A28" s="27"/>
       <c r="B28" s="3" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A29" s="27"/>
       <c r="B29" s="3" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A30" s="27"/>
       <c r="B30" s="3" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A31" s="24"/>
       <c r="B31" s="4" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>92</v>
+        <v>90</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
     </row>
   </sheetData>
@@ -2363,22 +2377,22 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C1" s="1" t="s">
+        <v>43</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>44</v>
+      </c>
+      <c r="E1" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D1" s="1" t="s">
-        <v>46</v>
-      </c>
-      <c r="E1" s="1" t="s">
-        <v>47</v>
-      </c>
       <c r="F1" s="1" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="G1" s="1" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
@@ -2386,16 +2400,16 @@
         <v>5</v>
       </c>
       <c r="B2" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="C2" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="C2" s="2" t="s">
-        <v>49</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>50</v>
-      </c>
       <c r="E2" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="F2" s="5">
         <v>773097086</v>
@@ -2408,13 +2422,13 @@
       <c r="A3" s="27"/>
       <c r="B3" s="29"/>
       <c r="C3" s="3" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="D3" s="3" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="E3" s="3" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="F3" s="6">
         <v>775545556</v>
@@ -2427,13 +2441,13 @@
       <c r="A4" s="27"/>
       <c r="B4" s="29"/>
       <c r="C4" s="3" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="D4" s="3" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E4" s="3" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
       <c r="F4" s="6">
         <v>773460373</v>
@@ -2446,13 +2460,13 @@
       <c r="A5" s="24"/>
       <c r="B5" s="30"/>
       <c r="C5" s="3" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="D5" s="3" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="E5" s="3" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="F5" s="6">
         <v>770617096</v>
@@ -2466,16 +2480,16 @@
         <v>6</v>
       </c>
       <c r="B6" s="28" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="F6" s="2">
         <v>777147559</v>
@@ -2487,16 +2501,16 @@
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A7" s="25"/>
       <c r="B7" s="29" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="F7" s="3">
         <v>777951348</v>
@@ -2509,13 +2523,13 @@
       <c r="A8" s="25"/>
       <c r="B8" s="29"/>
       <c r="C8" s="3" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="D8" s="3" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="E8" s="3" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F8" s="3">
         <v>782190772</v>
@@ -2528,13 +2542,13 @@
       <c r="A9" s="25"/>
       <c r="B9" s="30"/>
       <c r="C9" s="3" t="s">
+        <v>193</v>
+      </c>
+      <c r="D9" s="4" t="s">
         <v>195</v>
       </c>
-      <c r="D9" s="4" t="s">
-        <v>197</v>
-      </c>
       <c r="E9" s="3" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="F9" s="3">
         <v>789111270</v>
@@ -2548,16 +2562,16 @@
         <v>7</v>
       </c>
       <c r="B10" s="28" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>78</v>
+        <v>76</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>76</v>
+        <v>74</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="F10" s="2">
         <v>778847933</v>
@@ -2570,13 +2584,13 @@
       <c r="A11" s="25"/>
       <c r="B11" s="29"/>
       <c r="C11" s="3" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>77</v>
+        <v>75</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F11" s="3">
         <v>782651638</v>
@@ -2589,13 +2603,13 @@
       <c r="A12" s="25"/>
       <c r="B12" s="29"/>
       <c r="C12" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="F12" s="3">
         <v>774790213</v>
@@ -2608,13 +2622,13 @@
       <c r="A13" s="25"/>
       <c r="B13" s="30"/>
       <c r="C13" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
       <c r="D13" s="4" t="s">
-        <v>83</v>
+        <v>81</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F13" s="3">
         <v>788780692</v>
@@ -2629,16 +2643,16 @@
         <v>8</v>
       </c>
       <c r="B14" s="28" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F14" s="2">
         <v>777509848</v>
@@ -2650,16 +2664,16 @@
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
       <c r="A15" s="25"/>
       <c r="B15" s="29" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="D15" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F15" s="3">
         <v>776919692</v>
@@ -2672,13 +2686,13 @@
       <c r="A16" s="25"/>
       <c r="B16" s="29"/>
       <c r="C16" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="F16" s="3">
         <v>783008307</v>
@@ -2691,13 +2705,13 @@
       <c r="A17" s="25"/>
       <c r="B17" s="30"/>
       <c r="C17" s="4" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="D17" s="4" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="E17" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F17" s="4">
         <v>780123961</v>
@@ -2708,19 +2722,19 @@
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
       <c r="A18" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="B18" s="28" t="s">
+        <v>104</v>
+      </c>
+      <c r="C18" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="B18" s="28" t="s">
-        <v>106</v>
-      </c>
-      <c r="C18" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="D18" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="F18" s="3">
         <v>778679190</v>
@@ -2733,13 +2747,13 @@
       <c r="A19" s="27"/>
       <c r="B19" s="29"/>
       <c r="C19" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F19" s="3">
         <v>771994713</v>
@@ -2752,13 +2766,13 @@
       <c r="A20" s="27"/>
       <c r="B20" s="29"/>
       <c r="C20" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="F20" s="3">
         <v>784119644</v>
@@ -2771,13 +2785,13 @@
       <c r="A21" s="24"/>
       <c r="B21" s="30"/>
       <c r="C21" s="4" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="F21" s="4">
         <v>787389275</v>
@@ -2788,16 +2802,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:B13"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="B14:B17"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -2819,18 +2833,18 @@
       <c r="B2" s="34"/>
       <c r="C2" s="35"/>
       <c r="D2" s="14" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A3" s="31" t="s">
-        <v>62</v>
+        <v>60</v>
       </c>
       <c r="B3" s="7" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C3" s="9" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="D3" s="16">
         <v>776382705</v>
@@ -2839,10 +2853,10 @@
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A4" s="31"/>
       <c r="B4" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C4" s="11" t="s">
-        <v>59</v>
+        <v>57</v>
       </c>
       <c r="D4" s="15">
         <v>777401785</v>
@@ -2851,10 +2865,10 @@
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A5" s="31"/>
       <c r="B5" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C5" s="11" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="D5" s="15">
         <v>772579898</v>
@@ -2863,10 +2877,10 @@
     <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="32"/>
       <c r="B6" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>61</v>
+        <v>59</v>
       </c>
       <c r="D6" s="17">
         <v>781816827</v>
@@ -2877,10 +2891,10 @@
         <v>5</v>
       </c>
       <c r="B7" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C7" s="12" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="D7" s="16">
         <v>778196895</v>
@@ -2889,10 +2903,10 @@
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A8" s="31"/>
       <c r="B8" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C8" s="11" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="D8" s="15">
         <v>776372229</v>
@@ -2901,10 +2915,10 @@
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A9" s="31"/>
       <c r="B9" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C9" s="11" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="D9" s="15">
         <v>776665352</v>
@@ -2913,10 +2927,10 @@
     <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="31"/>
       <c r="B10" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C10" s="10" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="D10" s="17">
         <v>783441820</v>
@@ -2924,43 +2938,43 @@
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A11" s="36" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="B11" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>107</v>
+        <v>105</v>
       </c>
       <c r="D11" s="18"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A12" s="31"/>
       <c r="B12" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="D12" s="19"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A13" s="31"/>
       <c r="B13" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="D13" s="19"/>
     </row>
     <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="32"/>
       <c r="B14" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D14" s="17">
         <v>782402937</v>
@@ -2968,13 +2982,13 @@
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A15" s="31" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B15" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="D15" s="12">
         <v>775699621</v>
@@ -2983,10 +2997,10 @@
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A16" s="31"/>
       <c r="B16" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D16" s="11">
         <v>776440917</v>
@@ -2995,10 +3009,10 @@
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A17" s="31"/>
       <c r="B17" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="D17" s="11">
         <v>781287163</v>
@@ -3007,10 +3021,10 @@
     <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A18" s="32"/>
       <c r="B18" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="D18" s="10">
         <v>782352114</v>
@@ -3018,13 +3032,13 @@
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A19" s="31" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B19" s="13" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D19" s="12">
         <v>773335050</v>
@@ -3033,10 +3047,10 @@
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A20" s="31"/>
       <c r="B20" s="7" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="D20" s="11">
         <v>776441287</v>
@@ -3045,10 +3059,10 @@
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
       <c r="A21" s="31"/>
       <c r="B21" s="7" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="D21" s="11">
         <v>775451818</v>
@@ -3057,10 +3071,10 @@
     <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A22" s="32"/>
       <c r="B22" s="8" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D22" s="21">
         <v>775277993</v>

--- a/LOUMA phase2.xlsx
+++ b/LOUMA phase2.xlsx
@@ -13,8 +13,9 @@
   </bookViews>
   <sheets>
     <sheet name="Liste LOUMAS" sheetId="1" r:id="rId1"/>
-    <sheet name="Liste VTO" sheetId="2" r:id="rId2"/>
-    <sheet name="Contact" sheetId="3" r:id="rId3"/>
+    <sheet name="Feuil1" sheetId="4" r:id="rId2"/>
+    <sheet name="Liste VTO" sheetId="2" r:id="rId3"/>
+    <sheet name="Contact" sheetId="3" r:id="rId4"/>
   </sheets>
   <definedNames>
     <definedName name="A">'Liste LOUMAS'!$XFD$1</definedName>
@@ -29,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="253" uniqueCount="199">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="214">
   <si>
     <t>DRV</t>
   </si>
@@ -628,13 +629,58 @@
   </si>
   <si>
     <t>NDIOTÉ SÉANE</t>
+  </si>
+  <si>
+    <t>JOUR</t>
+  </si>
+  <si>
+    <t>LOUMA</t>
+  </si>
+  <si>
+    <t>NIAKHAR</t>
+  </si>
+  <si>
+    <t>14.473825, -16.402988</t>
+  </si>
+  <si>
+    <t>NDIENE LAGUANE</t>
+  </si>
+  <si>
+    <t>14.512415,-15.924362</t>
+  </si>
+  <si>
+    <t>SOKONE</t>
+  </si>
+  <si>
+    <t>13.878041,-16.374332</t>
+  </si>
+  <si>
+    <t>DIAKHAO</t>
+  </si>
+  <si>
+    <t>14.463398,-16.286104</t>
+  </si>
+  <si>
+    <t>DAY OFF</t>
+  </si>
+  <si>
+    <t>PASSY</t>
+  </si>
+  <si>
+    <t>13.986325,-16.258516</t>
+  </si>
+  <si>
+    <t>NGOYE (Axe Loul Sessene)</t>
+  </si>
+  <si>
+    <t>14.355134,-16.629496</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="20" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -782,8 +828,27 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF212121"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
   </fonts>
-  <fills count="35">
+  <fills count="37">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -975,6 +1040,18 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
   <borders count="31">
     <border>
@@ -1407,7 +1484,7 @@
     <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="39">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1440,6 +1517,8 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="4" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="19" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1479,8 +1558,27 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Accent1" xfId="18" builtinId="30" customBuiltin="1"/>
@@ -1876,7 +1974,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="24" t="s">
+      <c r="A2" s="26" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1893,7 +1991,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="25"/>
+      <c r="A3" s="27"/>
       <c r="B3" s="3" t="s">
         <v>20</v>
       </c>
@@ -1908,7 +2006,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="25"/>
+      <c r="A4" s="27"/>
       <c r="B4" s="3" t="s">
         <v>198</v>
       </c>
@@ -1919,7 +2017,7 @@
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="25"/>
+      <c r="A5" s="27"/>
       <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
@@ -1934,7 +2032,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="25"/>
+      <c r="A6" s="27"/>
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
@@ -1949,7 +2047,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="25"/>
+      <c r="A7" s="27"/>
       <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
@@ -1962,11 +2060,11 @@
       <c r="E7" s="4" t="s">
         <v>27</v>
       </c>
-      <c r="G7" s="37"/>
-      <c r="H7" s="37"/>
+      <c r="G7" s="24"/>
+      <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="25" t="s">
+      <c r="A8" s="27" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -1981,11 +2079,11 @@
       <c r="E8" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G8" s="37"/>
-      <c r="H8" s="37"/>
+      <c r="G8" s="24"/>
+      <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="25"/>
+      <c r="A9" s="27"/>
       <c r="B9" s="3" t="s">
         <v>110</v>
       </c>
@@ -1999,10 +2097,10 @@
         <v>122</v>
       </c>
       <c r="G9" s="2"/>
-      <c r="H9" s="37"/>
+      <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="25"/>
+      <c r="A10" s="27"/>
       <c r="B10" s="3" t="s">
         <v>111</v>
       </c>
@@ -2016,10 +2114,10 @@
         <v>123</v>
       </c>
       <c r="G10" s="3"/>
-      <c r="H10" s="37"/>
+      <c r="H10" s="24"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="25"/>
+      <c r="A11" s="27"/>
       <c r="B11" s="3" t="s">
         <v>112</v>
       </c>
@@ -2033,10 +2131,10 @@
         <v>124</v>
       </c>
       <c r="G11" s="3"/>
-      <c r="H11" s="37"/>
+      <c r="H11" s="24"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="25"/>
+      <c r="A12" s="27"/>
       <c r="B12" s="3" t="s">
         <v>113</v>
       </c>
@@ -2050,10 +2148,10 @@
         <v>125</v>
       </c>
       <c r="G12" s="3"/>
-      <c r="H12" s="37"/>
+      <c r="H12" s="24"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="25"/>
+      <c r="A13" s="27"/>
       <c r="B13" s="4" t="s">
         <v>114</v>
       </c>
@@ -2067,10 +2165,10 @@
         <v>126</v>
       </c>
       <c r="G13" s="3"/>
-      <c r="H13" s="37"/>
+      <c r="H13" s="24"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="27" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -2086,10 +2184,10 @@
         <v>152</v>
       </c>
       <c r="G14" s="4"/>
-      <c r="H14" s="38"/>
+      <c r="H14" s="25"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="25"/>
+      <c r="A15" s="27"/>
       <c r="B15" s="3" t="s">
         <v>62</v>
       </c>
@@ -2104,7 +2202,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="25"/>
+      <c r="A16" s="27"/>
       <c r="B16" s="3" t="s">
         <v>63</v>
       </c>
@@ -2119,7 +2217,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="25"/>
+      <c r="A17" s="27"/>
       <c r="B17" s="3" t="s">
         <v>64</v>
       </c>
@@ -2134,7 +2232,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="25"/>
+      <c r="A18" s="27"/>
       <c r="B18" s="3" t="s">
         <v>65</v>
       </c>
@@ -2149,7 +2247,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="25"/>
+      <c r="A19" s="27"/>
       <c r="B19" s="4" t="s">
         <v>66</v>
       </c>
@@ -2164,7 +2262,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="25" t="s">
+      <c r="A20" s="27" t="s">
         <v>8</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -2181,7 +2279,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="25"/>
+      <c r="A21" s="27"/>
       <c r="B21" s="3" t="s">
         <v>146</v>
       </c>
@@ -2196,7 +2294,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="25"/>
+      <c r="A22" s="27"/>
       <c r="B22" s="3" t="s">
         <v>149</v>
       </c>
@@ -2211,7 +2309,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="25"/>
+      <c r="A23" s="27"/>
       <c r="B23" s="3" t="s">
         <v>150</v>
       </c>
@@ -2226,7 +2324,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="25"/>
+      <c r="A24" s="27"/>
       <c r="B24" s="3" t="s">
         <v>158</v>
       </c>
@@ -2241,7 +2339,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="25"/>
+      <c r="A25" s="27"/>
       <c r="B25" s="4" t="s">
         <v>161</v>
       </c>
@@ -2256,7 +2354,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="26" t="s">
+      <c r="A26" s="28" t="s">
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -2273,7 +2371,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="27"/>
+      <c r="A27" s="29"/>
       <c r="B27" s="3" t="s">
         <v>165</v>
       </c>
@@ -2288,7 +2386,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="27"/>
+      <c r="A28" s="29"/>
       <c r="B28" s="3" t="s">
         <v>166</v>
       </c>
@@ -2303,7 +2401,7 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="27"/>
+      <c r="A29" s="29"/>
       <c r="B29" s="3" t="s">
         <v>167</v>
       </c>
@@ -2318,7 +2416,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="27"/>
+      <c r="A30" s="29"/>
       <c r="B30" s="3" t="s">
         <v>168</v>
       </c>
@@ -2333,7 +2431,7 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="24"/>
+      <c r="A31" s="26"/>
       <c r="B31" s="4" t="s">
         <v>169</v>
       </c>
@@ -2363,6 +2461,569 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:I31"/>
+  <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <cols>
+    <col min="2" max="2" width="22.36328125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="25" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="13.81640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="10" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.36328125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="24.1796875" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="21.08984375" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A1" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" s="39" t="s">
+        <v>199</v>
+      </c>
+      <c r="H1" s="40" t="s">
+        <v>200</v>
+      </c>
+      <c r="I1" s="40" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A2" s="26" t="s">
+        <v>5</v>
+      </c>
+      <c r="B2" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="C2" s="43" t="s">
+        <v>202</v>
+      </c>
+      <c r="D2" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="E2" s="2"/>
+      <c r="G2" s="41" t="s">
+        <v>11</v>
+      </c>
+      <c r="H2" s="42" t="s">
+        <v>201</v>
+      </c>
+      <c r="I2" s="43" t="s">
+        <v>202</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="27"/>
+      <c r="B3" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="C3" s="43" t="s">
+        <v>204</v>
+      </c>
+      <c r="D3" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="3"/>
+      <c r="G3" s="41" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="42" t="s">
+        <v>203</v>
+      </c>
+      <c r="I3" s="43" t="s">
+        <v>204</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="27"/>
+      <c r="B4" s="42" t="s">
+        <v>205</v>
+      </c>
+      <c r="C4" s="43" t="s">
+        <v>206</v>
+      </c>
+      <c r="D4" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="3"/>
+      <c r="G4" s="41" t="s">
+        <v>14</v>
+      </c>
+      <c r="H4" s="42" t="s">
+        <v>205</v>
+      </c>
+      <c r="I4" s="43" t="s">
+        <v>206</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="27"/>
+      <c r="B5" s="42" t="s">
+        <v>207</v>
+      </c>
+      <c r="C5" s="42" t="s">
+        <v>208</v>
+      </c>
+      <c r="D5" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="E5" s="3"/>
+      <c r="G5" s="41" t="s">
+        <v>15</v>
+      </c>
+      <c r="H5" s="42" t="s">
+        <v>207</v>
+      </c>
+      <c r="I5" s="42" t="s">
+        <v>208</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A6" s="27"/>
+      <c r="B6" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="C6" s="42" t="s">
+        <v>211</v>
+      </c>
+      <c r="D6" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="E6" s="3"/>
+      <c r="G6" s="41" t="s">
+        <v>67</v>
+      </c>
+      <c r="H6" s="44" t="s">
+        <v>209</v>
+      </c>
+      <c r="I6" s="45"/>
+    </row>
+    <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A7" s="27"/>
+      <c r="B7" s="42" t="s">
+        <v>212</v>
+      </c>
+      <c r="C7" s="42" t="s">
+        <v>213</v>
+      </c>
+      <c r="D7" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="4"/>
+      <c r="G7" s="41" t="s">
+        <v>16</v>
+      </c>
+      <c r="H7" s="42" t="s">
+        <v>210</v>
+      </c>
+      <c r="I7" s="42" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A8" s="27" t="s">
+        <v>6</v>
+      </c>
+      <c r="B8" s="2" t="s">
+        <v>109</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>115</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E8" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="G8" s="41" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="42" t="s">
+        <v>212</v>
+      </c>
+      <c r="I8" s="42" t="s">
+        <v>213</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A9" s="27"/>
+      <c r="B9" s="3" t="s">
+        <v>110</v>
+      </c>
+      <c r="C9" s="3" t="s">
+        <v>116</v>
+      </c>
+      <c r="D9" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E9" s="3" t="s">
+        <v>122</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A10" s="27"/>
+      <c r="B10" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="C10" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D10" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E10" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A11" s="27"/>
+      <c r="B11" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C11" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D11" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E11" s="3" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="27"/>
+      <c r="B12" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E12" s="3" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="27"/>
+      <c r="B13" s="4" t="s">
+        <v>114</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>120</v>
+      </c>
+      <c r="D13" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E13" s="3" t="s">
+        <v>126</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A14" s="27" t="s">
+        <v>7</v>
+      </c>
+      <c r="B14" s="2" t="s">
+        <v>61</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>68</v>
+      </c>
+      <c r="D14" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E14" s="2" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A15" s="27"/>
+      <c r="B15" s="3" t="s">
+        <v>62</v>
+      </c>
+      <c r="C15" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="D15" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E15" s="3" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A16" s="27"/>
+      <c r="B16" s="3" t="s">
+        <v>63</v>
+      </c>
+      <c r="C16" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D16" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E16" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="17" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A17" s="27"/>
+      <c r="B17" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C17" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D17" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E17" s="3" t="s">
+        <v>152</v>
+      </c>
+    </row>
+    <row r="18" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A18" s="27"/>
+      <c r="B18" s="3" t="s">
+        <v>65</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="27"/>
+      <c r="B19" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="C19" s="4" t="s">
+        <v>73</v>
+      </c>
+      <c r="D19" s="4" t="s">
+        <v>16</v>
+      </c>
+      <c r="E19" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="20" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A20" s="27" t="s">
+        <v>8</v>
+      </c>
+      <c r="B20" s="2" t="s">
+        <v>143</v>
+      </c>
+      <c r="C20" s="2" t="s">
+        <v>144</v>
+      </c>
+      <c r="D20" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="E20" s="2" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="27"/>
+      <c r="B21" s="3" t="s">
+        <v>146</v>
+      </c>
+      <c r="C21" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="D21" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="E21" s="3" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="27"/>
+      <c r="B22" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C22" s="22" t="s">
+        <v>192</v>
+      </c>
+      <c r="D22" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E22" s="3" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="23" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A23" s="27"/>
+      <c r="B23" s="3" t="s">
+        <v>150</v>
+      </c>
+      <c r="C23" s="3" t="s">
+        <v>151</v>
+      </c>
+      <c r="D23" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E23" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="27"/>
+      <c r="B24" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="C24" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="D24" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="27"/>
+      <c r="B25" s="4" t="s">
+        <v>161</v>
+      </c>
+      <c r="C25" s="4" t="s">
+        <v>162</v>
+      </c>
+      <c r="D25" s="4" t="s">
+        <v>67</v>
+      </c>
+      <c r="E25" s="4" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="28" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="2" t="s">
+        <v>164</v>
+      </c>
+      <c r="C26" s="2" t="s">
+        <v>85</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>11</v>
+      </c>
+      <c r="E26" s="2" t="s">
+        <v>170</v>
+      </c>
+    </row>
+    <row r="27" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A27" s="29"/>
+      <c r="B27" s="3" t="s">
+        <v>165</v>
+      </c>
+      <c r="C27" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D27" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="E27" s="3" t="s">
+        <v>171</v>
+      </c>
+    </row>
+    <row r="28" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A28" s="29"/>
+      <c r="B28" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="C28" s="3" t="s">
+        <v>87</v>
+      </c>
+      <c r="D28" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E28" s="3" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="29" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A29" s="29"/>
+      <c r="B29" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="C29" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D29" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>173</v>
+      </c>
+    </row>
+    <row r="30" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A30" s="29"/>
+      <c r="B30" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="C30" s="3" t="s">
+        <v>89</v>
+      </c>
+      <c r="D30" s="3" t="s">
+        <v>16</v>
+      </c>
+      <c r="E30" s="3" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="31" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A31" s="26"/>
+      <c r="B31" s="4" t="s">
+        <v>169</v>
+      </c>
+      <c r="C31" s="4" t="s">
+        <v>90</v>
+      </c>
+      <c r="D31" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="E31" s="4" t="s">
+        <v>175</v>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="6">
+    <mergeCell ref="A2:A7"/>
+    <mergeCell ref="A8:A13"/>
+    <mergeCell ref="A14:A19"/>
+    <mergeCell ref="A20:A25"/>
+    <mergeCell ref="A26:A31"/>
+    <mergeCell ref="H6:I6"/>
+  </mergeCells>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:J21"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
@@ -2396,10 +3057,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="28" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="28" t="s">
+      <c r="B2" s="30" t="s">
         <v>46</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -2419,8 +3080,8 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="27"/>
-      <c r="B3" s="29"/>
+      <c r="A3" s="29"/>
+      <c r="B3" s="31"/>
       <c r="C3" s="3" t="s">
         <v>50</v>
       </c>
@@ -2438,8 +3099,8 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="27"/>
-      <c r="B4" s="29"/>
+      <c r="A4" s="29"/>
+      <c r="B4" s="31"/>
       <c r="C4" s="3" t="s">
         <v>51</v>
       </c>
@@ -2457,8 +3118,8 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="24"/>
-      <c r="B5" s="30"/>
+      <c r="A5" s="26"/>
+      <c r="B5" s="32"/>
       <c r="C5" s="3" t="s">
         <v>53</v>
       </c>
@@ -2476,10 +3137,10 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="25" t="s">
+      <c r="A6" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="28" t="s">
+      <c r="B6" s="30" t="s">
         <v>128</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -2499,8 +3160,8 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" s="25"/>
-      <c r="B7" s="29" t="s">
+      <c r="A7" s="27"/>
+      <c r="B7" s="31" t="s">
         <v>128</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -2520,8 +3181,8 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" s="25"/>
-      <c r="B8" s="29"/>
+      <c r="A8" s="27"/>
+      <c r="B8" s="31"/>
       <c r="C8" s="3" t="s">
         <v>135</v>
       </c>
@@ -2539,8 +3200,8 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" s="25"/>
-      <c r="B9" s="30"/>
+      <c r="A9" s="27"/>
+      <c r="B9" s="32"/>
       <c r="C9" s="3" t="s">
         <v>193</v>
       </c>
@@ -2558,10 +3219,10 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" s="25" t="s">
+      <c r="A10" s="27" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="28" t="s">
+      <c r="B10" s="30" t="s">
         <v>129</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -2581,8 +3242,8 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="25"/>
-      <c r="B11" s="29"/>
+      <c r="A11" s="27"/>
+      <c r="B11" s="31"/>
       <c r="C11" s="3" t="s">
         <v>77</v>
       </c>
@@ -2600,8 +3261,8 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="25"/>
-      <c r="B12" s="29"/>
+      <c r="A12" s="27"/>
+      <c r="B12" s="31"/>
       <c r="C12" s="3" t="s">
         <v>79</v>
       </c>
@@ -2619,8 +3280,8 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="25"/>
-      <c r="B13" s="30"/>
+      <c r="A13" s="27"/>
+      <c r="B13" s="32"/>
       <c r="C13" s="3" t="s">
         <v>80</v>
       </c>
@@ -2639,10 +3300,10 @@
       <c r="J13" s="23"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" s="25" t="s">
+      <c r="A14" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="28" t="s">
+      <c r="B14" s="30" t="s">
         <v>176</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -2662,8 +3323,8 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="25"/>
-      <c r="B15" s="29" t="s">
+      <c r="A15" s="27"/>
+      <c r="B15" s="31" t="s">
         <v>128</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -2683,8 +3344,8 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="25"/>
-      <c r="B16" s="29"/>
+      <c r="A16" s="27"/>
+      <c r="B16" s="31"/>
       <c r="C16" s="3" t="s">
         <v>180</v>
       </c>
@@ -2702,8 +3363,8 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="25"/>
-      <c r="B17" s="30"/>
+      <c r="A17" s="27"/>
+      <c r="B17" s="32"/>
       <c r="C17" s="4" t="s">
         <v>182</v>
       </c>
@@ -2721,10 +3382,10 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="27" t="s">
+      <c r="A18" s="29" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="28" t="s">
+      <c r="B18" s="30" t="s">
         <v>104</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -2744,8 +3405,8 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="27"/>
-      <c r="B19" s="29"/>
+      <c r="A19" s="29"/>
+      <c r="B19" s="31"/>
       <c r="C19" s="3" t="s">
         <v>92</v>
       </c>
@@ -2763,8 +3424,8 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="27"/>
-      <c r="B20" s="29"/>
+      <c r="A20" s="29"/>
+      <c r="B20" s="31"/>
       <c r="C20" s="3" t="s">
         <v>96</v>
       </c>
@@ -2782,8 +3443,8 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="24"/>
-      <c r="B21" s="30"/>
+      <c r="A21" s="26"/>
+      <c r="B21" s="32"/>
       <c r="C21" s="4" t="s">
         <v>99</v>
       </c>
@@ -2802,23 +3463,23 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="B10:B13"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:D22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
@@ -2829,15 +3490,15 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="33"/>
-      <c r="B2" s="34"/>
-      <c r="C2" s="35"/>
+      <c r="A2" s="35"/>
+      <c r="B2" s="36"/>
+      <c r="C2" s="37"/>
       <c r="D2" s="14" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="31" t="s">
+      <c r="A3" s="33" t="s">
         <v>60</v>
       </c>
       <c r="B3" s="7" t="s">
@@ -2851,7 +3512,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="31"/>
+      <c r="A4" s="33"/>
       <c r="B4" s="7" t="s">
         <v>31</v>
       </c>
@@ -2863,7 +3524,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="31"/>
+      <c r="A5" s="33"/>
       <c r="B5" s="7" t="s">
         <v>33</v>
       </c>
@@ -2875,7 +3536,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="32"/>
+      <c r="A6" s="34"/>
       <c r="B6" s="8" t="s">
         <v>35</v>
       </c>
@@ -2887,7 +3548,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="31" t="s">
+      <c r="A7" s="33" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="13" t="s">
@@ -2901,7 +3562,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="31"/>
+      <c r="A8" s="33"/>
       <c r="B8" s="7" t="s">
         <v>31</v>
       </c>
@@ -2913,7 +3574,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="31"/>
+      <c r="A9" s="33"/>
       <c r="B9" s="7" t="s">
         <v>33</v>
       </c>
@@ -2925,7 +3586,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="31"/>
+      <c r="A10" s="33"/>
       <c r="B10" s="8" t="s">
         <v>35</v>
       </c>
@@ -2937,7 +3598,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="36" t="s">
+      <c r="A11" s="38" t="s">
         <v>91</v>
       </c>
       <c r="B11" s="13" t="s">
@@ -2949,7 +3610,7 @@
       <c r="D11" s="18"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="31"/>
+      <c r="A12" s="33"/>
       <c r="B12" s="7" t="s">
         <v>31</v>
       </c>
@@ -2959,7 +3620,7 @@
       <c r="D12" s="19"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="31"/>
+      <c r="A13" s="33"/>
       <c r="B13" s="7" t="s">
         <v>33</v>
       </c>
@@ -2969,7 +3630,7 @@
       <c r="D13" s="19"/>
     </row>
     <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="32"/>
+      <c r="A14" s="34"/>
       <c r="B14" s="8" t="s">
         <v>35</v>
       </c>
@@ -2981,7 +3642,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="31" t="s">
+      <c r="A15" s="33" t="s">
         <v>130</v>
       </c>
       <c r="B15" s="13" t="s">
@@ -2995,7 +3656,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="31"/>
+      <c r="A16" s="33"/>
       <c r="B16" s="7" t="s">
         <v>31</v>
       </c>
@@ -3007,7 +3668,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="31"/>
+      <c r="A17" s="33"/>
       <c r="B17" s="7" t="s">
         <v>33</v>
       </c>
@@ -3019,7 +3680,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="32"/>
+      <c r="A18" s="34"/>
       <c r="B18" s="8" t="s">
         <v>35</v>
       </c>
@@ -3031,7 +3692,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="31" t="s">
+      <c r="A19" s="33" t="s">
         <v>187</v>
       </c>
       <c r="B19" s="13" t="s">
@@ -3045,7 +3706,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="31"/>
+      <c r="A20" s="33"/>
       <c r="B20" s="7" t="s">
         <v>31</v>
       </c>
@@ -3057,7 +3718,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="31"/>
+      <c r="A21" s="33"/>
       <c r="B21" s="7" t="s">
         <v>33</v>
       </c>
@@ -3069,7 +3730,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="32"/>
+      <c r="A22" s="34"/>
       <c r="B22" s="8" t="s">
         <v>35</v>
       </c>

--- a/LOUMA phase2.xlsx
+++ b/LOUMA phase2.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="Liste LOUMAS" sheetId="1" r:id="rId1"/>
@@ -1519,6 +1519,21 @@
     <xf numFmtId="0" fontId="19" fillId="0" borderId="29" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="30" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="36" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="35" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1529,6 +1544,12 @@
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="35" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
@@ -1556,27 +1577,6 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="17" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="36" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="16" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="35" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="35" borderId="26" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -1974,7 +1974,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="31" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -1991,7 +1991,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="27"/>
+      <c r="A3" s="32"/>
       <c r="B3" s="3" t="s">
         <v>20</v>
       </c>
@@ -2006,7 +2006,7 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="27"/>
+      <c r="A4" s="32"/>
       <c r="B4" s="3" t="s">
         <v>198</v>
       </c>
@@ -2017,7 +2017,7 @@
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="27"/>
+      <c r="A5" s="32"/>
       <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
@@ -2032,7 +2032,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="27"/>
+      <c r="A6" s="32"/>
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
@@ -2047,7 +2047,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="27"/>
+      <c r="A7" s="32"/>
       <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
@@ -2064,7 +2064,7 @@
       <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="32" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -2083,7 +2083,7 @@
       <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="27"/>
+      <c r="A9" s="32"/>
       <c r="B9" s="3" t="s">
         <v>110</v>
       </c>
@@ -2100,7 +2100,7 @@
       <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="27"/>
+      <c r="A10" s="32"/>
       <c r="B10" s="3" t="s">
         <v>111</v>
       </c>
@@ -2117,7 +2117,7 @@
       <c r="H10" s="24"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="27"/>
+      <c r="A11" s="32"/>
       <c r="B11" s="3" t="s">
         <v>112</v>
       </c>
@@ -2134,7 +2134,7 @@
       <c r="H11" s="24"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="27"/>
+      <c r="A12" s="32"/>
       <c r="B12" s="3" t="s">
         <v>113</v>
       </c>
@@ -2151,7 +2151,7 @@
       <c r="H12" s="24"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="27"/>
+      <c r="A13" s="32"/>
       <c r="B13" s="4" t="s">
         <v>114</v>
       </c>
@@ -2168,7 +2168,7 @@
       <c r="H13" s="24"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="32" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -2187,7 +2187,7 @@
       <c r="H14" s="25"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="27"/>
+      <c r="A15" s="32"/>
       <c r="B15" s="3" t="s">
         <v>62</v>
       </c>
@@ -2202,7 +2202,7 @@
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="27"/>
+      <c r="A16" s="32"/>
       <c r="B16" s="3" t="s">
         <v>63</v>
       </c>
@@ -2217,7 +2217,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="27"/>
+      <c r="A17" s="32"/>
       <c r="B17" s="3" t="s">
         <v>64</v>
       </c>
@@ -2232,7 +2232,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="27"/>
+      <c r="A18" s="32"/>
       <c r="B18" s="3" t="s">
         <v>65</v>
       </c>
@@ -2247,7 +2247,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="27"/>
+      <c r="A19" s="32"/>
       <c r="B19" s="4" t="s">
         <v>66</v>
       </c>
@@ -2262,7 +2262,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="32" t="s">
         <v>8</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -2279,7 +2279,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="27"/>
+      <c r="A21" s="32"/>
       <c r="B21" s="3" t="s">
         <v>146</v>
       </c>
@@ -2294,7 +2294,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="27"/>
+      <c r="A22" s="32"/>
       <c r="B22" s="3" t="s">
         <v>149</v>
       </c>
@@ -2309,7 +2309,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="27"/>
+      <c r="A23" s="32"/>
       <c r="B23" s="3" t="s">
         <v>150</v>
       </c>
@@ -2324,7 +2324,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="27"/>
+      <c r="A24" s="32"/>
       <c r="B24" s="3" t="s">
         <v>158</v>
       </c>
@@ -2339,7 +2339,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="27"/>
+      <c r="A25" s="32"/>
       <c r="B25" s="4" t="s">
         <v>161</v>
       </c>
@@ -2354,7 +2354,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="33" t="s">
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -2371,7 +2371,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="29"/>
+      <c r="A27" s="34"/>
       <c r="B27" s="3" t="s">
         <v>165</v>
       </c>
@@ -2386,7 +2386,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="29"/>
+      <c r="A28" s="34"/>
       <c r="B28" s="3" t="s">
         <v>166</v>
       </c>
@@ -2401,7 +2401,7 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="29"/>
+      <c r="A29" s="34"/>
       <c r="B29" s="3" t="s">
         <v>167</v>
       </c>
@@ -2416,7 +2416,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="29"/>
+      <c r="A30" s="34"/>
       <c r="B30" s="3" t="s">
         <v>168</v>
       </c>
@@ -2431,7 +2431,7 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="26"/>
+      <c r="A31" s="31"/>
       <c r="B31" s="4" t="s">
         <v>169</v>
       </c>
@@ -2489,150 +2489,150 @@
       <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="G1" s="39" t="s">
+      <c r="G1" s="26" t="s">
         <v>199</v>
       </c>
-      <c r="H1" s="40" t="s">
+      <c r="H1" s="27" t="s">
         <v>200</v>
       </c>
-      <c r="I1" s="40" t="s">
+      <c r="I1" s="27" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="26" t="s">
+      <c r="A2" s="31" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="42" t="s">
+      <c r="B2" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="C2" s="43" t="s">
+      <c r="C2" s="30" t="s">
         <v>202</v>
       </c>
-      <c r="D2" s="41" t="s">
+      <c r="D2" s="28" t="s">
         <v>11</v>
       </c>
       <c r="E2" s="2"/>
-      <c r="G2" s="41" t="s">
+      <c r="G2" s="28" t="s">
         <v>11</v>
       </c>
-      <c r="H2" s="42" t="s">
+      <c r="H2" s="29" t="s">
         <v>201</v>
       </c>
-      <c r="I2" s="43" t="s">
+      <c r="I2" s="30" t="s">
         <v>202</v>
       </c>
     </row>
     <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="27"/>
-      <c r="B3" s="42" t="s">
+      <c r="A3" s="32"/>
+      <c r="B3" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="C3" s="43" t="s">
+      <c r="C3" s="30" t="s">
         <v>204</v>
       </c>
-      <c r="D3" s="41" t="s">
+      <c r="D3" s="28" t="s">
         <v>13</v>
       </c>
       <c r="E3" s="3"/>
-      <c r="G3" s="41" t="s">
+      <c r="G3" s="28" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="42" t="s">
+      <c r="H3" s="29" t="s">
         <v>203</v>
       </c>
-      <c r="I3" s="43" t="s">
+      <c r="I3" s="30" t="s">
         <v>204</v>
       </c>
     </row>
     <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="27"/>
-      <c r="B4" s="42" t="s">
+      <c r="A4" s="32"/>
+      <c r="B4" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="C4" s="43" t="s">
+      <c r="C4" s="30" t="s">
         <v>206</v>
       </c>
-      <c r="D4" s="41" t="s">
+      <c r="D4" s="28" t="s">
         <v>14</v>
       </c>
       <c r="E4" s="3"/>
-      <c r="G4" s="41" t="s">
+      <c r="G4" s="28" t="s">
         <v>14</v>
       </c>
-      <c r="H4" s="42" t="s">
+      <c r="H4" s="29" t="s">
         <v>205</v>
       </c>
-      <c r="I4" s="43" t="s">
+      <c r="I4" s="30" t="s">
         <v>206</v>
       </c>
     </row>
     <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="27"/>
-      <c r="B5" s="42" t="s">
+      <c r="A5" s="32"/>
+      <c r="B5" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="C5" s="42" t="s">
+      <c r="C5" s="29" t="s">
         <v>208</v>
       </c>
-      <c r="D5" s="41" t="s">
+      <c r="D5" s="28" t="s">
         <v>15</v>
       </c>
       <c r="E5" s="3"/>
-      <c r="G5" s="41" t="s">
+      <c r="G5" s="28" t="s">
         <v>15</v>
       </c>
-      <c r="H5" s="42" t="s">
+      <c r="H5" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="I5" s="42" t="s">
+      <c r="I5" s="29" t="s">
         <v>208</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="27"/>
-      <c r="B6" s="42" t="s">
+      <c r="A6" s="32"/>
+      <c r="B6" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="C6" s="42" t="s">
+      <c r="C6" s="29" t="s">
         <v>211</v>
       </c>
-      <c r="D6" s="41" t="s">
+      <c r="D6" s="28" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="3"/>
-      <c r="G6" s="41" t="s">
+      <c r="G6" s="28" t="s">
         <v>67</v>
       </c>
-      <c r="H6" s="44" t="s">
+      <c r="H6" s="35" t="s">
         <v>209</v>
       </c>
-      <c r="I6" s="45"/>
+      <c r="I6" s="36"/>
     </row>
     <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="27"/>
-      <c r="B7" s="42" t="s">
+      <c r="A7" s="32"/>
+      <c r="B7" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="C7" s="42" t="s">
+      <c r="C7" s="29" t="s">
         <v>213</v>
       </c>
-      <c r="D7" s="41" t="s">
+      <c r="D7" s="28" t="s">
         <v>17</v>
       </c>
       <c r="E7" s="4"/>
-      <c r="G7" s="41" t="s">
+      <c r="G7" s="28" t="s">
         <v>16</v>
       </c>
-      <c r="H7" s="42" t="s">
+      <c r="H7" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="I7" s="42" t="s">
+      <c r="I7" s="29" t="s">
         <v>211</v>
       </c>
     </row>
     <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="27" t="s">
+      <c r="A8" s="32" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
@@ -2647,18 +2647,18 @@
       <c r="E8" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="G8" s="41" t="s">
+      <c r="G8" s="28" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="42" t="s">
+      <c r="H8" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="I8" s="42" t="s">
+      <c r="I8" s="29" t="s">
         <v>213</v>
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="27"/>
+      <c r="A9" s="32"/>
       <c r="B9" s="3" t="s">
         <v>110</v>
       </c>
@@ -2673,7 +2673,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="27"/>
+      <c r="A10" s="32"/>
       <c r="B10" s="3" t="s">
         <v>111</v>
       </c>
@@ -2688,7 +2688,7 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="27"/>
+      <c r="A11" s="32"/>
       <c r="B11" s="3" t="s">
         <v>112</v>
       </c>
@@ -2703,7 +2703,7 @@
       </c>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="27"/>
+      <c r="A12" s="32"/>
       <c r="B12" s="3" t="s">
         <v>113</v>
       </c>
@@ -2718,7 +2718,7 @@
       </c>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="27"/>
+      <c r="A13" s="32"/>
       <c r="B13" s="4" t="s">
         <v>114</v>
       </c>
@@ -2733,7 +2733,7 @@
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="32" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
@@ -2750,7 +2750,7 @@
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="27"/>
+      <c r="A15" s="32"/>
       <c r="B15" s="3" t="s">
         <v>62</v>
       </c>
@@ -2765,7 +2765,7 @@
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="27"/>
+      <c r="A16" s="32"/>
       <c r="B16" s="3" t="s">
         <v>63</v>
       </c>
@@ -2780,7 +2780,7 @@
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="27"/>
+      <c r="A17" s="32"/>
       <c r="B17" s="3" t="s">
         <v>64</v>
       </c>
@@ -2795,7 +2795,7 @@
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="27"/>
+      <c r="A18" s="32"/>
       <c r="B18" s="3" t="s">
         <v>65</v>
       </c>
@@ -2810,7 +2810,7 @@
       </c>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="27"/>
+      <c r="A19" s="32"/>
       <c r="B19" s="4" t="s">
         <v>66</v>
       </c>
@@ -2825,7 +2825,7 @@
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="27" t="s">
+      <c r="A20" s="32" t="s">
         <v>8</v>
       </c>
       <c r="B20" s="2" t="s">
@@ -2842,7 +2842,7 @@
       </c>
     </row>
     <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="27"/>
+      <c r="A21" s="32"/>
       <c r="B21" s="3" t="s">
         <v>146</v>
       </c>
@@ -2857,7 +2857,7 @@
       </c>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="27"/>
+      <c r="A22" s="32"/>
       <c r="B22" s="3" t="s">
         <v>149</v>
       </c>
@@ -2872,7 +2872,7 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="27"/>
+      <c r="A23" s="32"/>
       <c r="B23" s="3" t="s">
         <v>150</v>
       </c>
@@ -2887,7 +2887,7 @@
       </c>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="27"/>
+      <c r="A24" s="32"/>
       <c r="B24" s="3" t="s">
         <v>158</v>
       </c>
@@ -2902,7 +2902,7 @@
       </c>
     </row>
     <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="27"/>
+      <c r="A25" s="32"/>
       <c r="B25" s="4" t="s">
         <v>161</v>
       </c>
@@ -2917,7 +2917,7 @@
       </c>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="28" t="s">
+      <c r="A26" s="33" t="s">
         <v>9</v>
       </c>
       <c r="B26" s="2" t="s">
@@ -2934,7 +2934,7 @@
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="29"/>
+      <c r="A27" s="34"/>
       <c r="B27" s="3" t="s">
         <v>165</v>
       </c>
@@ -2949,7 +2949,7 @@
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="29"/>
+      <c r="A28" s="34"/>
       <c r="B28" s="3" t="s">
         <v>166</v>
       </c>
@@ -2964,7 +2964,7 @@
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="29"/>
+      <c r="A29" s="34"/>
       <c r="B29" s="3" t="s">
         <v>167</v>
       </c>
@@ -2979,7 +2979,7 @@
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="29"/>
+      <c r="A30" s="34"/>
       <c r="B30" s="3" t="s">
         <v>168</v>
       </c>
@@ -2994,7 +2994,7 @@
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="26"/>
+      <c r="A31" s="31"/>
       <c r="B31" s="4" t="s">
         <v>169</v>
       </c>
@@ -3010,12 +3010,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="H6:I6"/>
     <mergeCell ref="A2:A7"/>
     <mergeCell ref="A8:A13"/>
     <mergeCell ref="A14:A19"/>
     <mergeCell ref="A20:A25"/>
     <mergeCell ref="A26:A31"/>
-    <mergeCell ref="H6:I6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3057,10 +3057,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="28" t="s">
+      <c r="A2" s="33" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="30" t="s">
+      <c r="B2" s="37" t="s">
         <v>46</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3080,8 +3080,8 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="29"/>
-      <c r="B3" s="31"/>
+      <c r="A3" s="34"/>
+      <c r="B3" s="38"/>
       <c r="C3" s="3" t="s">
         <v>50</v>
       </c>
@@ -3099,8 +3099,8 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="29"/>
-      <c r="B4" s="31"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="38"/>
       <c r="C4" s="3" t="s">
         <v>51</v>
       </c>
@@ -3118,8 +3118,8 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="26"/>
-      <c r="B5" s="32"/>
+      <c r="A5" s="31"/>
+      <c r="B5" s="39"/>
       <c r="C5" s="3" t="s">
         <v>53</v>
       </c>
@@ -3137,10 +3137,10 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="27" t="s">
+      <c r="A6" s="32" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="30" t="s">
+      <c r="B6" s="37" t="s">
         <v>128</v>
       </c>
       <c r="C6" s="2" t="s">
@@ -3160,8 +3160,8 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" s="27"/>
-      <c r="B7" s="31" t="s">
+      <c r="A7" s="32"/>
+      <c r="B7" s="38" t="s">
         <v>128</v>
       </c>
       <c r="C7" s="3" t="s">
@@ -3181,8 +3181,8 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" s="27"/>
-      <c r="B8" s="31"/>
+      <c r="A8" s="32"/>
+      <c r="B8" s="38"/>
       <c r="C8" s="3" t="s">
         <v>135</v>
       </c>
@@ -3200,8 +3200,8 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" s="27"/>
-      <c r="B9" s="32"/>
+      <c r="A9" s="32"/>
+      <c r="B9" s="39"/>
       <c r="C9" s="3" t="s">
         <v>193</v>
       </c>
@@ -3219,10 +3219,10 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" s="27" t="s">
+      <c r="A10" s="32" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="30" t="s">
+      <c r="B10" s="37" t="s">
         <v>129</v>
       </c>
       <c r="C10" s="2" t="s">
@@ -3242,8 +3242,8 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="27"/>
-      <c r="B11" s="31"/>
+      <c r="A11" s="32"/>
+      <c r="B11" s="38"/>
       <c r="C11" s="3" t="s">
         <v>77</v>
       </c>
@@ -3261,8 +3261,8 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="27"/>
-      <c r="B12" s="31"/>
+      <c r="A12" s="32"/>
+      <c r="B12" s="38"/>
       <c r="C12" s="3" t="s">
         <v>79</v>
       </c>
@@ -3280,8 +3280,8 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="27"/>
-      <c r="B13" s="32"/>
+      <c r="A13" s="32"/>
+      <c r="B13" s="39"/>
       <c r="C13" s="3" t="s">
         <v>80</v>
       </c>
@@ -3300,10 +3300,10 @@
       <c r="J13" s="23"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" s="27" t="s">
+      <c r="A14" s="32" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="30" t="s">
+      <c r="B14" s="37" t="s">
         <v>176</v>
       </c>
       <c r="C14" s="2" t="s">
@@ -3323,8 +3323,8 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="27"/>
-      <c r="B15" s="31" t="s">
+      <c r="A15" s="32"/>
+      <c r="B15" s="38" t="s">
         <v>128</v>
       </c>
       <c r="C15" s="3" t="s">
@@ -3344,8 +3344,8 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="27"/>
-      <c r="B16" s="31"/>
+      <c r="A16" s="32"/>
+      <c r="B16" s="38"/>
       <c r="C16" s="3" t="s">
         <v>180</v>
       </c>
@@ -3363,8 +3363,8 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="27"/>
-      <c r="B17" s="32"/>
+      <c r="A17" s="32"/>
+      <c r="B17" s="39"/>
       <c r="C17" s="4" t="s">
         <v>182</v>
       </c>
@@ -3382,10 +3382,10 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="29" t="s">
+      <c r="A18" s="34" t="s">
         <v>91</v>
       </c>
-      <c r="B18" s="30" t="s">
+      <c r="B18" s="37" t="s">
         <v>104</v>
       </c>
       <c r="C18" s="3" t="s">
@@ -3405,8 +3405,8 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="29"/>
-      <c r="B19" s="31"/>
+      <c r="A19" s="34"/>
+      <c r="B19" s="38"/>
       <c r="C19" s="3" t="s">
         <v>92</v>
       </c>
@@ -3424,8 +3424,8 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="29"/>
-      <c r="B20" s="31"/>
+      <c r="A20" s="34"/>
+      <c r="B20" s="38"/>
       <c r="C20" s="3" t="s">
         <v>96</v>
       </c>
@@ -3443,8 +3443,8 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="26"/>
-      <c r="B21" s="32"/>
+      <c r="A21" s="31"/>
+      <c r="B21" s="39"/>
       <c r="C21" s="4" t="s">
         <v>99</v>
       </c>
@@ -3463,16 +3463,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:B13"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="B14:B17"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3490,15 +3490,15 @@
   <sheetData>
     <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="35"/>
-      <c r="B2" s="36"/>
-      <c r="C2" s="37"/>
+      <c r="A2" s="42"/>
+      <c r="B2" s="43"/>
+      <c r="C2" s="44"/>
       <c r="D2" s="14" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="3" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A3" s="33" t="s">
+      <c r="A3" s="40" t="s">
         <v>60</v>
       </c>
       <c r="B3" s="7" t="s">
@@ -3512,7 +3512,7 @@
       </c>
     </row>
     <row r="4" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A4" s="33"/>
+      <c r="A4" s="40"/>
       <c r="B4" s="7" t="s">
         <v>31</v>
       </c>
@@ -3524,7 +3524,7 @@
       </c>
     </row>
     <row r="5" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A5" s="33"/>
+      <c r="A5" s="40"/>
       <c r="B5" s="7" t="s">
         <v>33</v>
       </c>
@@ -3536,7 +3536,7 @@
       </c>
     </row>
     <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="34"/>
+      <c r="A6" s="41"/>
       <c r="B6" s="8" t="s">
         <v>35</v>
       </c>
@@ -3548,7 +3548,7 @@
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A7" s="33" t="s">
+      <c r="A7" s="40" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="13" t="s">
@@ -3562,7 +3562,7 @@
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A8" s="33"/>
+      <c r="A8" s="40"/>
       <c r="B8" s="7" t="s">
         <v>31</v>
       </c>
@@ -3574,7 +3574,7 @@
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A9" s="33"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="7" t="s">
         <v>33</v>
       </c>
@@ -3586,7 +3586,7 @@
       </c>
     </row>
     <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="33"/>
+      <c r="A10" s="40"/>
       <c r="B10" s="8" t="s">
         <v>35</v>
       </c>
@@ -3598,7 +3598,7 @@
       </c>
     </row>
     <row r="11" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A11" s="38" t="s">
+      <c r="A11" s="45" t="s">
         <v>91</v>
       </c>
       <c r="B11" s="13" t="s">
@@ -3610,7 +3610,7 @@
       <c r="D11" s="18"/>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A12" s="33"/>
+      <c r="A12" s="40"/>
       <c r="B12" s="7" t="s">
         <v>31</v>
       </c>
@@ -3620,7 +3620,7 @@
       <c r="D12" s="19"/>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A13" s="33"/>
+      <c r="A13" s="40"/>
       <c r="B13" s="7" t="s">
         <v>33</v>
       </c>
@@ -3630,7 +3630,7 @@
       <c r="D13" s="19"/>
     </row>
     <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="34"/>
+      <c r="A14" s="41"/>
       <c r="B14" s="8" t="s">
         <v>35</v>
       </c>
@@ -3642,7 +3642,7 @@
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A15" s="33" t="s">
+      <c r="A15" s="40" t="s">
         <v>130</v>
       </c>
       <c r="B15" s="13" t="s">
@@ -3656,7 +3656,7 @@
       </c>
     </row>
     <row r="16" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A16" s="33"/>
+      <c r="A16" s="40"/>
       <c r="B16" s="7" t="s">
         <v>31</v>
       </c>
@@ -3668,7 +3668,7 @@
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="33"/>
+      <c r="A17" s="40"/>
       <c r="B17" s="7" t="s">
         <v>33</v>
       </c>
@@ -3680,7 +3680,7 @@
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="34"/>
+      <c r="A18" s="41"/>
       <c r="B18" s="8" t="s">
         <v>35</v>
       </c>
@@ -3692,7 +3692,7 @@
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="33" t="s">
+      <c r="A19" s="40" t="s">
         <v>187</v>
       </c>
       <c r="B19" s="13" t="s">
@@ -3706,7 +3706,7 @@
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="33"/>
+      <c r="A20" s="40"/>
       <c r="B20" s="7" t="s">
         <v>31</v>
       </c>
@@ -3718,7 +3718,7 @@
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="33"/>
+      <c r="A21" s="40"/>
       <c r="B21" s="7" t="s">
         <v>33</v>
       </c>
@@ -3730,7 +3730,7 @@
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="34"/>
+      <c r="A22" s="41"/>
       <c r="B22" s="8" t="s">
         <v>35</v>
       </c>

--- a/LOUMA phase2.xlsx
+++ b/LOUMA phase2.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="2"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7050" activeTab="3"/>
   </bookViews>
   <sheets>
     <sheet name="Liste LOUMAS" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="400" uniqueCount="214">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="413" uniqueCount="222">
   <si>
     <t>DRV</t>
   </si>
@@ -674,13 +674,37 @@
   </si>
   <si>
     <t>14.355134,-16.629496</t>
+  </si>
+  <si>
+    <t>DR</t>
+  </si>
+  <si>
+    <t>ND PARTENAIRE</t>
+  </si>
+  <si>
+    <t>DRC</t>
+  </si>
+  <si>
+    <t>DRE</t>
+  </si>
+  <si>
+    <t>DRS</t>
+  </si>
+  <si>
+    <t>DRSE</t>
+  </si>
+  <si>
+    <t>DRN</t>
+  </si>
+  <si>
+    <t>TOUBA BOGO</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
-  <fonts count="23" x14ac:knownFonts="1">
+  <fonts count="24" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -846,6 +870,12 @@
       <color rgb="FF212121"/>
       <name val="Times New Roman"/>
       <family val="1"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="37">
@@ -1484,7 +1514,7 @@
     <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="46">
+  <cellXfs count="54">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
@@ -1579,6 +1609,24 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Accent1" xfId="18" builtinId="30" customBuiltin="1"/>
@@ -3010,12 +3058,12 @@
     </row>
   </sheetData>
   <mergeCells count="6">
+    <mergeCell ref="A26:A31"/>
     <mergeCell ref="H6:I6"/>
     <mergeCell ref="A2:A7"/>
     <mergeCell ref="A8:A13"/>
     <mergeCell ref="A14:A19"/>
     <mergeCell ref="A20:A25"/>
-    <mergeCell ref="A26:A31"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3463,16 +3511,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B18:B21"/>
+    <mergeCell ref="B14:B17"/>
+    <mergeCell ref="B6:B9"/>
+    <mergeCell ref="A14:A17"/>
+    <mergeCell ref="A18:A21"/>
     <mergeCell ref="B2:B5"/>
     <mergeCell ref="A2:A5"/>
     <mergeCell ref="A6:A9"/>
     <mergeCell ref="A10:A13"/>
     <mergeCell ref="B10:B13"/>
-    <mergeCell ref="B18:B21"/>
-    <mergeCell ref="B14:B17"/>
-    <mergeCell ref="B6:B9"/>
-    <mergeCell ref="A14:A17"/>
-    <mergeCell ref="A18:A21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3481,23 +3529,34 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D22"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="3" max="3" width="22.36328125" customWidth="1"/>
     <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="60.26953125" style="51" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
-    <row r="2" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
+    <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A2" s="42"/>
       <c r="B2" s="43"/>
       <c r="C2" s="44"/>
       <c r="D2" s="14" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="G2" s="47" t="s">
+        <v>214</v>
+      </c>
+      <c r="H2" s="52" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="47" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A3" s="40" t="s">
         <v>60</v>
       </c>
@@ -3510,8 +3569,17 @@
       <c r="D3" s="16">
         <v>776382705</v>
       </c>
-    </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="G3" s="46" t="s">
+        <v>216</v>
+      </c>
+      <c r="H3" s="53" t="s">
+        <v>221</v>
+      </c>
+      <c r="I3" s="48">
+        <v>775945699</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A4" s="40"/>
       <c r="B4" s="7" t="s">
         <v>31</v>
@@ -3522,8 +3590,17 @@
       <c r="D4" s="15">
         <v>777401785</v>
       </c>
-    </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="G4" s="46" t="s">
+        <v>217</v>
+      </c>
+      <c r="H4" s="53" t="s">
+        <v>34</v>
+      </c>
+      <c r="I4" s="49">
+        <v>776665352</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A5" s="40"/>
       <c r="B5" s="7" t="s">
         <v>33</v>
@@ -3534,8 +3611,17 @@
       <c r="D5" s="15">
         <v>772579898</v>
       </c>
-    </row>
-    <row r="6" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="G5" s="46" t="s">
+        <v>218</v>
+      </c>
+      <c r="H5" s="53" t="s">
+        <v>190</v>
+      </c>
+      <c r="I5" s="50">
+        <v>775451818</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A6" s="41"/>
       <c r="B6" s="8" t="s">
         <v>35</v>
@@ -3546,8 +3632,17 @@
       <c r="D6" s="17">
         <v>781816827</v>
       </c>
-    </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="G6" s="46" t="s">
+        <v>219</v>
+      </c>
+      <c r="H6" s="53" t="s">
+        <v>58</v>
+      </c>
+      <c r="I6" s="49">
+        <v>772579898</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A7" s="40" t="s">
         <v>5</v>
       </c>
@@ -3560,8 +3655,17 @@
       <c r="D7" s="16">
         <v>778196895</v>
       </c>
-    </row>
-    <row r="8" spans="1:4" x14ac:dyDescent="0.35">
+      <c r="G7" s="46" t="s">
+        <v>220</v>
+      </c>
+      <c r="H7" s="53" t="s">
+        <v>127</v>
+      </c>
+      <c r="I7" s="50">
+        <v>781287163</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A8" s="40"/>
       <c r="B8" s="7" t="s">
         <v>31</v>
@@ -3573,7 +3677,7 @@
         <v>776372229</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A9" s="40"/>
       <c r="B9" s="7" t="s">
         <v>33</v>
@@ -3585,7 +3689,7 @@
         <v>776665352</v>
       </c>
     </row>
-    <row r="10" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A10" s="40"/>
       <c r="B10" s="8" t="s">
         <v>35</v>
@@ -3597,7 +3701,7 @@
         <v>783441820</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A11" s="45" t="s">
         <v>91</v>
       </c>
@@ -3609,7 +3713,7 @@
       </c>
       <c r="D11" s="18"/>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A12" s="40"/>
       <c r="B12" s="7" t="s">
         <v>31</v>
@@ -3619,7 +3723,7 @@
       </c>
       <c r="D12" s="19"/>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A13" s="40"/>
       <c r="B13" s="7" t="s">
         <v>33</v>
@@ -3629,7 +3733,7 @@
       </c>
       <c r="D13" s="19"/>
     </row>
-    <row r="14" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
       <c r="A14" s="41"/>
       <c r="B14" s="8" t="s">
         <v>35</v>
@@ -3641,7 +3745,7 @@
         <v>782402937</v>
       </c>
     </row>
-    <row r="15" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A15" s="40" t="s">
         <v>130</v>
       </c>
@@ -3655,7 +3759,7 @@
         <v>775699621</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:9" x14ac:dyDescent="0.35">
       <c r="A16" s="40"/>
       <c r="B16" s="7" t="s">
         <v>31</v>
@@ -3751,5 +3855,6 @@
     <mergeCell ref="A15:A18"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
 </worksheet>
 </file>
--- a/LOUMA phase2.xlsx
+++ b/LOUMA phase2.xlsx
@@ -209,9 +209,6 @@
     <t>SORIKE FOFANA</t>
   </si>
   <si>
-    <t>ASSANE BA</t>
-  </si>
-  <si>
     <t>DR  SUD EST</t>
   </si>
   <si>
@@ -698,6 +695,9 @@
   </si>
   <si>
     <t>TOUBA BOGO</t>
+  </si>
+  <si>
+    <t>PAPA AMETH FALL</t>
   </si>
 </sst>
 </file>
@@ -1564,6 +1564,24 @@
     <xf numFmtId="0" fontId="22" fillId="35" borderId="27" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -1609,24 +1627,6 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="18" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="22" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="23" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="23" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20 % - Accent1" xfId="18" builtinId="30" customBuiltin="1"/>
@@ -2022,7 +2022,7 @@
       </c>
     </row>
     <row r="2" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="39" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="2" t="s">
@@ -2039,7 +2039,7 @@
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A3" s="32"/>
+      <c r="A3" s="40"/>
       <c r="B3" s="3" t="s">
         <v>20</v>
       </c>
@@ -2054,18 +2054,18 @@
       </c>
     </row>
     <row r="4" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A4" s="32"/>
+      <c r="A4" s="40"/>
       <c r="B4" s="3" t="s">
-        <v>198</v>
+        <v>197</v>
       </c>
       <c r="C4" s="3"/>
       <c r="D4" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E4" s="3"/>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A5" s="32"/>
+      <c r="A5" s="40"/>
       <c r="B5" s="3" t="s">
         <v>18</v>
       </c>
@@ -2080,7 +2080,7 @@
       </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A6" s="32"/>
+      <c r="A6" s="40"/>
       <c r="B6" s="3" t="s">
         <v>10</v>
       </c>
@@ -2095,7 +2095,7 @@
       </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A7" s="32"/>
+      <c r="A7" s="40"/>
       <c r="B7" s="4" t="s">
         <v>12</v>
       </c>
@@ -2112,242 +2112,242 @@
       <c r="H7" s="24"/>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="40" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G8" s="24"/>
       <c r="H8" s="24"/>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A9" s="32"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="G9" s="2"/>
       <c r="H9" s="24"/>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A10" s="32"/>
+      <c r="A10" s="40"/>
       <c r="B10" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="G10" s="3"/>
       <c r="H10" s="24"/>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A11" s="32"/>
+      <c r="A11" s="40"/>
       <c r="B11" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="G11" s="3"/>
       <c r="H11" s="24"/>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A12" s="32"/>
+      <c r="A12" s="40"/>
       <c r="B12" s="3" t="s">
-        <v>113</v>
+        <v>112</v>
       </c>
       <c r="C12" s="3" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G12" s="3"/>
       <c r="H12" s="24"/>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A13" s="32"/>
+      <c r="A13" s="40"/>
       <c r="B13" s="4" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="C13" s="4" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="G13" s="3"/>
       <c r="H13" s="24"/>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="40" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="G14" s="4"/>
       <c r="H14" s="25"/>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A15" s="32"/>
+      <c r="A15" s="40"/>
       <c r="B15" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.35">
-      <c r="A16" s="32"/>
+      <c r="A16" s="40"/>
       <c r="B16" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="32"/>
+      <c r="A17" s="40"/>
       <c r="B17" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="32"/>
+      <c r="A18" s="40"/>
       <c r="B18" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="40"/>
+      <c r="B19" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="32"/>
-      <c r="B19" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="32" t="s">
+      <c r="A20" s="40" t="s">
         <v>8</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="40"/>
+      <c r="B21" s="3" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="32"/>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>147</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E21" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="40"/>
+      <c r="B22" s="3" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="32"/>
-      <c r="B22" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="C22" s="22" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>13</v>
@@ -2357,140 +2357,140 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="32"/>
+      <c r="A23" s="40"/>
       <c r="B23" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="40"/>
+      <c r="B24" s="3" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="32"/>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>159</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="40"/>
+      <c r="B25" s="4" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="32"/>
-      <c r="B25" s="4" t="s">
+      <c r="C25" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="D25" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E25" s="4" t="s">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="C26" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="34"/>
+      <c r="A27" s="42"/>
       <c r="B27" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="34"/>
+      <c r="A28" s="42"/>
       <c r="B28" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="34"/>
+      <c r="A29" s="42"/>
       <c r="B29" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="34"/>
+      <c r="A30" s="42"/>
       <c r="B30" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="31"/>
+      <c r="A31" s="39"/>
       <c r="B31" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -2538,24 +2538,24 @@
         <v>4</v>
       </c>
       <c r="G1" s="26" t="s">
+        <v>198</v>
+      </c>
+      <c r="H1" s="27" t="s">
         <v>199</v>
-      </c>
-      <c r="H1" s="27" t="s">
-        <v>200</v>
       </c>
       <c r="I1" s="27" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="31" t="s">
+      <c r="A2" s="39" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="C2" s="30" t="s">
         <v>201</v>
-      </c>
-      <c r="C2" s="30" t="s">
-        <v>202</v>
       </c>
       <c r="D2" s="28" t="s">
         <v>11</v>
@@ -2565,19 +2565,19 @@
         <v>11</v>
       </c>
       <c r="H2" s="29" t="s">
+        <v>200</v>
+      </c>
+      <c r="I2" s="30" t="s">
         <v>201</v>
       </c>
-      <c r="I2" s="30" t="s">
+    </row>
+    <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A3" s="40"/>
+      <c r="B3" s="29" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="3" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A3" s="32"/>
-      <c r="B3" s="29" t="s">
+      <c r="C3" s="30" t="s">
         <v>203</v>
-      </c>
-      <c r="C3" s="30" t="s">
-        <v>204</v>
       </c>
       <c r="D3" s="28" t="s">
         <v>13</v>
@@ -2587,19 +2587,19 @@
         <v>13</v>
       </c>
       <c r="H3" s="29" t="s">
+        <v>202</v>
+      </c>
+      <c r="I3" s="30" t="s">
         <v>203</v>
       </c>
-      <c r="I3" s="30" t="s">
+    </row>
+    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A4" s="40"/>
+      <c r="B4" s="29" t="s">
         <v>204</v>
       </c>
-    </row>
-    <row r="4" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A4" s="32"/>
-      <c r="B4" s="29" t="s">
+      <c r="C4" s="30" t="s">
         <v>205</v>
-      </c>
-      <c r="C4" s="30" t="s">
-        <v>206</v>
       </c>
       <c r="D4" s="28" t="s">
         <v>14</v>
@@ -2609,19 +2609,19 @@
         <v>14</v>
       </c>
       <c r="H4" s="29" t="s">
+        <v>204</v>
+      </c>
+      <c r="I4" s="30" t="s">
         <v>205</v>
       </c>
-      <c r="I4" s="30" t="s">
+    </row>
+    <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
+      <c r="A5" s="40"/>
+      <c r="B5" s="29" t="s">
         <v>206</v>
       </c>
-    </row>
-    <row r="5" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A5" s="32"/>
-      <c r="B5" s="29" t="s">
+      <c r="C5" s="29" t="s">
         <v>207</v>
-      </c>
-      <c r="C5" s="29" t="s">
-        <v>208</v>
       </c>
       <c r="D5" s="28" t="s">
         <v>15</v>
@@ -2631,39 +2631,39 @@
         <v>15</v>
       </c>
       <c r="H5" s="29" t="s">
+        <v>206</v>
+      </c>
+      <c r="I5" s="29" t="s">
         <v>207</v>
       </c>
-      <c r="I5" s="29" t="s">
-        <v>208</v>
-      </c>
     </row>
     <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="32"/>
+      <c r="A6" s="40"/>
       <c r="B6" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="C6" s="29" t="s">
         <v>210</v>
-      </c>
-      <c r="C6" s="29" t="s">
-        <v>211</v>
       </c>
       <c r="D6" s="28" t="s">
         <v>16</v>
       </c>
       <c r="E6" s="3"/>
       <c r="G6" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="H6" s="35" t="s">
-        <v>209</v>
-      </c>
-      <c r="I6" s="36"/>
+        <v>66</v>
+      </c>
+      <c r="H6" s="43" t="s">
+        <v>208</v>
+      </c>
+      <c r="I6" s="44"/>
     </row>
     <row r="7" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A7" s="32"/>
+      <c r="A7" s="40"/>
       <c r="B7" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="C7" s="29" t="s">
         <v>212</v>
-      </c>
-      <c r="C7" s="29" t="s">
-        <v>213</v>
       </c>
       <c r="D7" s="28" t="s">
         <v>17</v>
@@ -2673,244 +2673,244 @@
         <v>16</v>
       </c>
       <c r="H7" s="29" t="s">
+        <v>209</v>
+      </c>
+      <c r="I7" s="29" t="s">
         <v>210</v>
       </c>
-      <c r="I7" s="29" t="s">
-        <v>211</v>
-      </c>
     </row>
     <row r="8" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A8" s="32" t="s">
+      <c r="A8" s="40" t="s">
         <v>6</v>
       </c>
       <c r="B8" s="2" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="D8" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="G8" s="28" t="s">
         <v>17</v>
       </c>
       <c r="H8" s="29" t="s">
+        <v>211</v>
+      </c>
+      <c r="I8" s="29" t="s">
         <v>212</v>
       </c>
-      <c r="I8" s="29" t="s">
-        <v>213</v>
-      </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="32"/>
+      <c r="A9" s="40"/>
       <c r="B9" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="C9" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="D9" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E9" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="10" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A10" s="32"/>
+      <c r="A10" s="40"/>
       <c r="B10" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="C10" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="D10" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E10" s="3" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="32"/>
+      <c r="A11" s="40"/>
       <c r="B11" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
       <c r="C11" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="D11" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E11" s="3" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A12" s="40"/>
+      <c r="B12" s="3" t="s">
+        <v>112</v>
+      </c>
+      <c r="C12" s="3" t="s">
+        <v>118</v>
+      </c>
+      <c r="D12" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E12" s="3" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="32"/>
-      <c r="B12" s="3" t="s">
+    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A13" s="40"/>
+      <c r="B13" s="4" t="s">
         <v>113</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C13" s="4" t="s">
         <v>119</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E12" s="3" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="32"/>
-      <c r="B13" s="4" t="s">
-        <v>114</v>
-      </c>
-      <c r="C13" s="4" t="s">
-        <v>120</v>
       </c>
       <c r="D13" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E13" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="14" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="40" t="s">
         <v>7</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="D14" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="32"/>
+      <c r="A15" s="40"/>
       <c r="B15" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="C15" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="D15" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="32"/>
+      <c r="A16" s="40"/>
       <c r="B16" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D16" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E16" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
     </row>
     <row r="17" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A17" s="32"/>
+      <c r="A17" s="40"/>
       <c r="B17" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="D17" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E17" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="32"/>
+      <c r="A18" s="40"/>
       <c r="B18" s="3" t="s">
+        <v>64</v>
+      </c>
+      <c r="C18" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D18" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E18" s="3" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A19" s="40"/>
+      <c r="B19" s="4" t="s">
         <v>65</v>
       </c>
-      <c r="C18" s="3" t="s">
+      <c r="C19" s="4" t="s">
         <v>72</v>
-      </c>
-      <c r="D18" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E18" s="3" t="s">
-        <v>155</v>
-      </c>
-    </row>
-    <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="32"/>
-      <c r="B19" s="4" t="s">
-        <v>66</v>
-      </c>
-      <c r="C19" s="4" t="s">
-        <v>73</v>
       </c>
       <c r="D19" s="4" t="s">
         <v>16</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="32" t="s">
+      <c r="A20" s="40" t="s">
         <v>8</v>
       </c>
       <c r="B20" s="2" t="s">
+        <v>142</v>
+      </c>
+      <c r="C20" s="2" t="s">
         <v>143</v>
-      </c>
-      <c r="C20" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="D20" s="2" t="s">
         <v>16</v>
       </c>
       <c r="E20" s="2" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A21" s="40"/>
+      <c r="B21" s="3" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="21" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A21" s="32"/>
-      <c r="B21" s="3" t="s">
+      <c r="C21" s="3" t="s">
         <v>146</v>
-      </c>
-      <c r="C21" s="3" t="s">
-        <v>147</v>
       </c>
       <c r="D21" s="3" t="s">
         <v>11</v>
       </c>
       <c r="E21" s="3" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A22" s="40"/>
+      <c r="B22" s="3" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="32"/>
-      <c r="B22" s="3" t="s">
-        <v>149</v>
-      </c>
       <c r="C22" s="22" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="D22" s="3" t="s">
         <v>13</v>
@@ -2920,140 +2920,140 @@
       </c>
     </row>
     <row r="23" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A23" s="32"/>
+      <c r="A23" s="40"/>
       <c r="B23" s="3" t="s">
+        <v>149</v>
+      </c>
+      <c r="C23" s="3" t="s">
         <v>150</v>
-      </c>
-      <c r="C23" s="3" t="s">
-        <v>151</v>
       </c>
       <c r="D23" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E23" s="3" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A24" s="40"/>
+      <c r="B24" s="3" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="32"/>
-      <c r="B24" s="3" t="s">
+      <c r="C24" s="3" t="s">
         <v>158</v>
-      </c>
-      <c r="C24" s="3" t="s">
-        <v>159</v>
       </c>
       <c r="D24" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E24" s="3" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A25" s="40"/>
+      <c r="B25" s="4" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="25" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A25" s="32"/>
-      <c r="B25" s="4" t="s">
+      <c r="C25" s="4" t="s">
         <v>161</v>
       </c>
-      <c r="C25" s="4" t="s">
+      <c r="D25" s="4" t="s">
+        <v>66</v>
+      </c>
+      <c r="E25" s="4" t="s">
         <v>162</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>67</v>
-      </c>
-      <c r="E25" s="4" t="s">
+    </row>
+    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
+      <c r="A26" s="41" t="s">
+        <v>9</v>
+      </c>
+      <c r="B26" s="2" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="33" t="s">
-        <v>9</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>164</v>
-      </c>
       <c r="C26" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="D26" s="2" t="s">
         <v>11</v>
       </c>
       <c r="E26" s="2" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
     </row>
     <row r="27" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A27" s="34"/>
+      <c r="A27" s="42"/>
       <c r="B27" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D27" s="3" t="s">
         <v>13</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="28" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A28" s="34"/>
+      <c r="A28" s="42"/>
       <c r="B28" s="3" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="D28" s="3" t="s">
         <v>14</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
     </row>
     <row r="29" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A29" s="34"/>
+      <c r="A29" s="42"/>
       <c r="B29" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>15</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="30" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A30" s="34"/>
+      <c r="A30" s="42"/>
       <c r="B30" s="3" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="D30" s="3" t="s">
         <v>16</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
     </row>
     <row r="31" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A31" s="31"/>
+      <c r="A31" s="39"/>
       <c r="B31" s="4" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="C31" s="4" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="D31" s="4" t="s">
         <v>17</v>
       </c>
       <c r="E31" s="4" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
   </sheetData>
@@ -3105,10 +3105,10 @@
       </c>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A2" s="33" t="s">
+      <c r="A2" s="41" t="s">
         <v>5</v>
       </c>
-      <c r="B2" s="37" t="s">
+      <c r="B2" s="45" t="s">
         <v>46</v>
       </c>
       <c r="C2" s="2" t="s">
@@ -3128,8 +3128,8 @@
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A3" s="34"/>
-      <c r="B3" s="38"/>
+      <c r="A3" s="42"/>
+      <c r="B3" s="46"/>
       <c r="C3" s="3" t="s">
         <v>50</v>
       </c>
@@ -3147,8 +3147,8 @@
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A4" s="34"/>
-      <c r="B4" s="38"/>
+      <c r="A4" s="42"/>
+      <c r="B4" s="46"/>
       <c r="C4" s="3" t="s">
         <v>51</v>
       </c>
@@ -3166,8 +3166,8 @@
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A5" s="31"/>
-      <c r="B5" s="39"/>
+      <c r="A5" s="39"/>
+      <c r="B5" s="47"/>
       <c r="C5" s="3" t="s">
         <v>53</v>
       </c>
@@ -3185,20 +3185,20 @@
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A6" s="32" t="s">
+      <c r="A6" s="40" t="s">
         <v>6</v>
       </c>
-      <c r="B6" s="37" t="s">
-        <v>128</v>
+      <c r="B6" s="45" t="s">
+        <v>127</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>131</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>132</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>133</v>
-      </c>
       <c r="E6" s="2" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="F6" s="2">
         <v>777147559</v>
@@ -3208,18 +3208,18 @@
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A7" s="32"/>
-      <c r="B7" s="38" t="s">
-        <v>128</v>
+      <c r="A7" s="40"/>
+      <c r="B7" s="46" t="s">
+        <v>127</v>
       </c>
       <c r="C7" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="D7" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E7" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F7" s="3">
         <v>777951348</v>
@@ -3229,16 +3229,16 @@
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A8" s="32"/>
-      <c r="B8" s="38"/>
+      <c r="A8" s="40"/>
+      <c r="B8" s="46"/>
       <c r="C8" s="3" t="s">
+        <v>134</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>135</v>
       </c>
-      <c r="D8" s="3" t="s">
-        <v>136</v>
-      </c>
       <c r="E8" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F8" s="3">
         <v>782190772</v>
@@ -3248,16 +3248,16 @@
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A9" s="32"/>
-      <c r="B9" s="39"/>
+      <c r="A9" s="40"/>
+      <c r="B9" s="47"/>
       <c r="C9" s="3" t="s">
+        <v>192</v>
+      </c>
+      <c r="D9" s="4" t="s">
+        <v>194</v>
+      </c>
+      <c r="E9" s="3" t="s">
         <v>193</v>
-      </c>
-      <c r="D9" s="4" t="s">
-        <v>195</v>
-      </c>
-      <c r="E9" s="3" t="s">
-        <v>194</v>
       </c>
       <c r="F9" s="3">
         <v>789111270</v>
@@ -3267,20 +3267,20 @@
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A10" s="32" t="s">
+      <c r="A10" s="40" t="s">
         <v>7</v>
       </c>
-      <c r="B10" s="37" t="s">
-        <v>129</v>
+      <c r="B10" s="45" t="s">
+        <v>128</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="D10" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
       <c r="F10" s="2">
         <v>778847933</v>
@@ -3290,16 +3290,16 @@
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A11" s="32"/>
-      <c r="B11" s="38"/>
+      <c r="A11" s="40"/>
+      <c r="B11" s="46"/>
       <c r="C11" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="D11" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="E11" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F11" s="3">
         <v>782651638</v>
@@ -3309,16 +3309,16 @@
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A12" s="32"/>
-      <c r="B12" s="38"/>
+      <c r="A12" s="40"/>
+      <c r="B12" s="46"/>
       <c r="C12" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="D12" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="E12" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F12" s="3">
         <v>774790213</v>
@@ -3328,16 +3328,16 @@
       </c>
     </row>
     <row r="13" spans="1:10" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A13" s="32"/>
-      <c r="B13" s="39"/>
+      <c r="A13" s="40"/>
+      <c r="B13" s="47"/>
       <c r="C13" s="3" t="s">
+        <v>79</v>
+      </c>
+      <c r="D13" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="D13" s="4" t="s">
-        <v>81</v>
-      </c>
       <c r="E13" s="3" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="F13" s="3">
         <v>788780692</v>
@@ -3348,20 +3348,20 @@
       <c r="J13" s="23"/>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A14" s="32" t="s">
+      <c r="A14" s="40" t="s">
         <v>8</v>
       </c>
-      <c r="B14" s="37" t="s">
+      <c r="B14" s="45" t="s">
+        <v>175</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="C14" s="2" t="s">
-        <v>177</v>
-      </c>
       <c r="D14" s="2" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="F14" s="2">
         <v>777509848</v>
@@ -3371,18 +3371,18 @@
       </c>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A15" s="32"/>
-      <c r="B15" s="38" t="s">
-        <v>128</v>
+      <c r="A15" s="40"/>
+      <c r="B15" s="46" t="s">
+        <v>127</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>177</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>179</v>
-      </c>
       <c r="E15" s="3" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F15" s="3">
         <v>776919692</v>
@@ -3392,16 +3392,16 @@
       </c>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.35">
-      <c r="A16" s="32"/>
-      <c r="B16" s="38"/>
+      <c r="A16" s="40"/>
+      <c r="B16" s="46"/>
       <c r="C16" s="3" t="s">
+        <v>179</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>181</v>
-      </c>
       <c r="E16" s="3" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F16" s="3">
         <v>783008307</v>
@@ -3411,16 +3411,16 @@
       </c>
     </row>
     <row r="17" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A17" s="32"/>
-      <c r="B17" s="39"/>
+      <c r="A17" s="40"/>
+      <c r="B17" s="47"/>
       <c r="C17" s="4" t="s">
+        <v>181</v>
+      </c>
+      <c r="D17" s="4" t="s">
         <v>182</v>
       </c>
-      <c r="D17" s="4" t="s">
-        <v>183</v>
-      </c>
       <c r="E17" s="4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F17" s="4">
         <v>780123961</v>
@@ -3430,20 +3430,20 @@
       </c>
     </row>
     <row r="18" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A18" s="34" t="s">
-        <v>91</v>
-      </c>
-      <c r="B18" s="37" t="s">
-        <v>104</v>
+      <c r="A18" s="42" t="s">
+        <v>90</v>
+      </c>
+      <c r="B18" s="45" t="s">
+        <v>103</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="E18" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F18" s="3">
         <v>778679190</v>
@@ -3453,16 +3453,16 @@
       </c>
     </row>
     <row r="19" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A19" s="34"/>
-      <c r="B19" s="38"/>
+      <c r="A19" s="42"/>
+      <c r="B19" s="46"/>
       <c r="C19" s="3" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F19" s="3">
         <v>771994713</v>
@@ -3472,16 +3472,16 @@
       </c>
     </row>
     <row r="20" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A20" s="34"/>
-      <c r="B20" s="38"/>
+      <c r="A20" s="42"/>
+      <c r="B20" s="46"/>
       <c r="C20" s="3" t="s">
+        <v>95</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>96</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>97</v>
-      </c>
       <c r="E20" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F20" s="3">
         <v>784119644</v>
@@ -3491,16 +3491,16 @@
       </c>
     </row>
     <row r="21" spans="1:7" x14ac:dyDescent="0.35">
-      <c r="A21" s="31"/>
-      <c r="B21" s="39"/>
+      <c r="A21" s="39"/>
+      <c r="B21" s="47"/>
       <c r="C21" s="4" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="D21" s="4" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E21" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F21" s="4">
         <v>787389275</v>
@@ -3511,16 +3511,16 @@
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="B2:B5"/>
+    <mergeCell ref="A2:A5"/>
+    <mergeCell ref="A6:A9"/>
+    <mergeCell ref="A10:A13"/>
+    <mergeCell ref="B10:B13"/>
     <mergeCell ref="B18:B21"/>
     <mergeCell ref="B14:B17"/>
     <mergeCell ref="B6:B9"/>
     <mergeCell ref="A14:A17"/>
     <mergeCell ref="A18:A21"/>
-    <mergeCell ref="B2:B5"/>
-    <mergeCell ref="A2:A5"/>
-    <mergeCell ref="A6:A9"/>
-    <mergeCell ref="A10:A13"/>
-    <mergeCell ref="B10:B13"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -3534,31 +3534,31 @@
   <cols>
     <col min="3" max="3" width="22.36328125" customWidth="1"/>
     <col min="4" max="4" width="11.54296875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="60.26953125" style="51" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="60.26953125" style="36" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="14.81640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4"/>
     <row r="2" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A2" s="42"/>
-      <c r="B2" s="43"/>
-      <c r="C2" s="44"/>
+      <c r="A2" s="50"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="52"/>
       <c r="D2" s="14" t="s">
         <v>55</v>
       </c>
-      <c r="G2" s="47" t="s">
+      <c r="G2" s="32" t="s">
+        <v>213</v>
+      </c>
+      <c r="H2" s="37" t="s">
+        <v>33</v>
+      </c>
+      <c r="I2" s="32" t="s">
         <v>214</v>
       </c>
-      <c r="H2" s="52" t="s">
-        <v>33</v>
-      </c>
-      <c r="I2" s="47" t="s">
-        <v>215</v>
-      </c>
     </row>
     <row r="3" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A3" s="40" t="s">
-        <v>60</v>
+      <c r="A3" s="48" t="s">
+        <v>59</v>
       </c>
       <c r="B3" s="7" t="s">
         <v>29</v>
@@ -3569,18 +3569,18 @@
       <c r="D3" s="16">
         <v>776382705</v>
       </c>
-      <c r="G3" s="46" t="s">
-        <v>216</v>
-      </c>
-      <c r="H3" s="53" t="s">
-        <v>221</v>
-      </c>
-      <c r="I3" s="48">
+      <c r="G3" s="31" t="s">
+        <v>215</v>
+      </c>
+      <c r="H3" s="38" t="s">
+        <v>220</v>
+      </c>
+      <c r="I3" s="33">
         <v>775945699</v>
       </c>
     </row>
     <row r="4" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A4" s="40"/>
+      <c r="A4" s="48"/>
       <c r="B4" s="7" t="s">
         <v>31</v>
       </c>
@@ -3590,18 +3590,18 @@
       <c r="D4" s="15">
         <v>777401785</v>
       </c>
-      <c r="G4" s="46" t="s">
-        <v>217</v>
-      </c>
-      <c r="H4" s="53" t="s">
+      <c r="G4" s="31" t="s">
+        <v>216</v>
+      </c>
+      <c r="H4" s="38" t="s">
         <v>34</v>
       </c>
-      <c r="I4" s="49">
+      <c r="I4" s="34">
         <v>776665352</v>
       </c>
     </row>
     <row r="5" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A5" s="40"/>
+      <c r="A5" s="48"/>
       <c r="B5" s="7" t="s">
         <v>33</v>
       </c>
@@ -3611,39 +3611,39 @@
       <c r="D5" s="15">
         <v>772579898</v>
       </c>
-      <c r="G5" s="46" t="s">
-        <v>218</v>
-      </c>
-      <c r="H5" s="53" t="s">
-        <v>190</v>
-      </c>
-      <c r="I5" s="50">
+      <c r="G5" s="31" t="s">
+        <v>217</v>
+      </c>
+      <c r="H5" s="38" t="s">
+        <v>189</v>
+      </c>
+      <c r="I5" s="35">
         <v>775451818</v>
       </c>
     </row>
     <row r="6" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A6" s="41"/>
+      <c r="A6" s="49"/>
       <c r="B6" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C6" s="10" t="s">
-        <v>59</v>
+        <v>221</v>
       </c>
       <c r="D6" s="17">
-        <v>781816827</v>
-      </c>
-      <c r="G6" s="46" t="s">
-        <v>219</v>
-      </c>
-      <c r="H6" s="53" t="s">
+        <v>776281358</v>
+      </c>
+      <c r="G6" s="31" t="s">
+        <v>218</v>
+      </c>
+      <c r="H6" s="38" t="s">
         <v>58</v>
       </c>
-      <c r="I6" s="49">
+      <c r="I6" s="34">
         <v>772579898</v>
       </c>
     </row>
     <row r="7" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A7" s="40" t="s">
+      <c r="A7" s="48" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="13" t="s">
@@ -3655,18 +3655,18 @@
       <c r="D7" s="16">
         <v>778196895</v>
       </c>
-      <c r="G7" s="46" t="s">
-        <v>220</v>
-      </c>
-      <c r="H7" s="53" t="s">
-        <v>127</v>
-      </c>
-      <c r="I7" s="50">
+      <c r="G7" s="31" t="s">
+        <v>219</v>
+      </c>
+      <c r="H7" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="I7" s="35">
         <v>781287163</v>
       </c>
     </row>
     <row r="8" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A8" s="40"/>
+      <c r="A8" s="48"/>
       <c r="B8" s="7" t="s">
         <v>31</v>
       </c>
@@ -3678,7 +3678,7 @@
       </c>
     </row>
     <row r="9" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A9" s="40"/>
+      <c r="A9" s="48"/>
       <c r="B9" s="7" t="s">
         <v>33</v>
       </c>
@@ -3690,7 +3690,7 @@
       </c>
     </row>
     <row r="10" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A10" s="40"/>
+      <c r="A10" s="48"/>
       <c r="B10" s="8" t="s">
         <v>35</v>
       </c>
@@ -3702,144 +3702,144 @@
       </c>
     </row>
     <row r="11" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A11" s="45" t="s">
-        <v>91</v>
+      <c r="A11" s="53" t="s">
+        <v>90</v>
       </c>
       <c r="B11" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C11" s="12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="D11" s="18"/>
     </row>
     <row r="12" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A12" s="40"/>
+      <c r="A12" s="48"/>
       <c r="B12" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C12" s="11" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="D12" s="19"/>
     </row>
     <row r="13" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A13" s="40"/>
+      <c r="A13" s="48"/>
       <c r="B13" s="7" t="s">
         <v>33</v>
       </c>
       <c r="C13" s="11" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="D13" s="19"/>
     </row>
     <row r="14" spans="1:9" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A14" s="41"/>
+      <c r="A14" s="49"/>
       <c r="B14" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C14" s="10" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D14" s="17">
         <v>782402937</v>
       </c>
     </row>
     <row r="15" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A15" s="40" t="s">
-        <v>130</v>
+      <c r="A15" s="48" t="s">
+        <v>129</v>
       </c>
       <c r="B15" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C15" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="D15" s="12">
         <v>775699621</v>
       </c>
     </row>
     <row r="16" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A16" s="40"/>
+      <c r="A16" s="48"/>
       <c r="B16" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C16" s="11" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="D16" s="11">
         <v>776440917</v>
       </c>
     </row>
     <row r="17" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A17" s="40"/>
+      <c r="A17" s="48"/>
       <c r="B17" s="7" t="s">
         <v>33</v>
       </c>
       <c r="C17" s="11" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="D17" s="11">
         <v>781287163</v>
       </c>
     </row>
     <row r="18" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A18" s="41"/>
+      <c r="A18" s="49"/>
       <c r="B18" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C18" s="10" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D18" s="10">
         <v>782352114</v>
       </c>
     </row>
     <row r="19" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A19" s="40" t="s">
-        <v>187</v>
+      <c r="A19" s="48" t="s">
+        <v>186</v>
       </c>
       <c r="B19" s="13" t="s">
         <v>29</v>
       </c>
       <c r="C19" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="D19" s="12">
         <v>773335050</v>
       </c>
     </row>
     <row r="20" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A20" s="40"/>
+      <c r="A20" s="48"/>
       <c r="B20" s="7" t="s">
         <v>31</v>
       </c>
       <c r="C20" s="11" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="D20" s="11">
         <v>776441287</v>
       </c>
     </row>
     <row r="21" spans="1:4" x14ac:dyDescent="0.35">
-      <c r="A21" s="40"/>
+      <c r="A21" s="48"/>
       <c r="B21" s="7" t="s">
         <v>33</v>
       </c>
       <c r="C21" s="11" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="D21" s="11">
         <v>775451818</v>
       </c>
     </row>
     <row r="22" spans="1:4" ht="15" thickBot="1" x14ac:dyDescent="0.4">
-      <c r="A22" s="41"/>
+      <c r="A22" s="49"/>
       <c r="B22" s="8" t="s">
         <v>35</v>
       </c>
       <c r="C22" s="20" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="D22" s="21">
         <v>775277993</v>
